--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-18.xlsx
@@ -857,55 +857,55 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="H2" t="n">
         <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
         <v>2.28</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>2.62</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
         <v>3.9</v>
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q3" t="n">
         <v>1.58</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G7" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H7" t="n">
         <v>2.94</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="K7" t="n">
         <v>4.4</v>
@@ -2160,7 +2160,7 @@
         <v>2.78</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>1.44</v>
       </c>
       <c r="G8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H8" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="I8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J8" t="n">
         <v>4.9</v>
@@ -2414,7 +2414,7 @@
         <v>2.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
         <v>3.35</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J9" t="n">
         <v>3.65</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="n">
         <v>9.800000000000001</v>
@@ -3045,7 +3045,7 @@
         <v>4.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG10" t="n">
         <v>16.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
         <v>2.88</v>
       </c>
       <c r="H12" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I12" t="n">
         <v>2.8</v>
@@ -3412,7 +3412,7 @@
         <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3430,7 +3430,7 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G14" t="n">
         <v>3.5</v>
@@ -3938,7 +3938,7 @@
         <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
         <v>21</v>
       </c>
       <c r="Y14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z14" t="n">
         <v>18.5</v>
@@ -3986,10 +3986,10 @@
         <v>29</v>
       </c>
       <c r="AG14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
         <v>38</v>
@@ -4001,7 +4001,7 @@
         <v>42</v>
       </c>
       <c r="AL14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM14" t="n">
         <v>85</v>
@@ -4016,13 +4016,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR14" t="n">
         <v>12</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AT14" t="n">
         <v>11.5</v>
@@ -4061,7 +4061,7 @@
         <v>4.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>21</v>
+        <v>4.4</v>
       </c>
       <c r="BG14" t="n">
         <v>11.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4189,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q15" t="n">
         <v>1.7</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q16" t="n">
         <v>1.66</v>
@@ -4482,7 +4482,7 @@
         <v>19</v>
       </c>
       <c r="AC16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD16" t="n">
         <v>13.5</v>
@@ -4503,7 +4503,7 @@
         <v>36</v>
       </c>
       <c r="AJ16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK16" t="n">
         <v>38</v>
@@ -4521,7 +4521,7 @@
         <v>15.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>10</v>
@@ -4530,7 +4530,7 @@
         <v>12.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT16" t="n">
         <v>12.5</v>
@@ -4554,22 +4554,22 @@
         <v>12</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG16" t="n">
         <v>10</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -4667,16 +4667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G17" t="n">
         <v>3.6</v>
       </c>
       <c r="H17" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I17" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="J17" t="n">
         <v>3.15</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -4921,16 +4921,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="G18" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H18" t="n">
         <v>1.82</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="J18" t="n">
         <v>3.55</v>
@@ -4954,7 +4954,7 @@
         <v>1.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
         <v>1.33</v>
       </c>
       <c r="G21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="H21" t="n">
         <v>9.199999999999999</v>
@@ -5713,10 +5713,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -6191,19 +6191,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H23" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I23" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K23" t="n">
         <v>3.6</v>
@@ -6221,10 +6221,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="H26" t="n">
-        <v>12</v>
+        <v>3.55</v>
       </c>
       <c r="I26" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="K26" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -6986,7 +6986,7 @@
         <v>1.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G28" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J28" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -7491,10 +7491,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -7972,10 +7972,10 @@
         <v>1.45</v>
       </c>
       <c r="G30" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H30" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
         <v>10.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="G39" t="n">
         <v>1.41</v>
@@ -10285,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="Q39" t="n">
         <v>1.71</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -10509,22 +10509,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="G40" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="H40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J40" t="n">
         <v>2.96</v>
       </c>
-      <c r="I40" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J40" t="n">
-        <v>3.55</v>
-      </c>
       <c r="K40" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -10539,10 +10539,10 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-18.xlsx
@@ -863,7 +863,7 @@
         <v>1.78</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I2" t="n">
         <v>5.9</v>
@@ -878,28 +878,28 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R2" t="n">
         <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="U2" t="n">
         <v>2.08</v>
@@ -911,112 +911,112 @@
         <v>2.28</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>16</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="BA2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB2" t="n">
         <v>14.5</v>
       </c>
-      <c r="AR2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB2" t="n">
+      <c r="BC2" t="n">
         <v>14</v>
       </c>
-      <c r="BC2" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BD2" t="n">
-        <v>22</v>
+        <v>4.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>40</v>
+        <v>4.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="G3" t="n">
         <v>3.3</v>
@@ -1120,10 +1120,10 @@
         <v>2.38</v>
       </c>
       <c r="I3" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
         <v>3.9</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>2.34</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H7" t="n">
         <v>2.94</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K7" t="n">
         <v>4.4</v>
@@ -2160,7 +2160,7 @@
         <v>2.78</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="G8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H8" t="n">
-        <v>5.8</v>
+        <v>1.21</v>
       </c>
       <c r="I8" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="J8" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
         <v>5.6</v>
@@ -2414,7 +2414,7 @@
         <v>2.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -2638,13 +2638,13 @@
         <v>2.1</v>
       </c>
       <c r="G9" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="H9" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J9" t="n">
         <v>3.65</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="G10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H10" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I10" t="n">
         <v>2.46</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
         <v>3.45</v>
@@ -2922,7 +2922,7 @@
         <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2943,10 +2943,10 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="Z10" t="n">
         <v>18</v>
@@ -2967,10 +2967,10 @@
         <v>34</v>
       </c>
       <c r="AF10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH10" t="n">
         <v>22</v>
@@ -2982,7 +2982,7 @@
         <v>85</v>
       </c>
       <c r="AK10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL10" t="n">
         <v>70</v>
@@ -2991,10 +2991,10 @@
         <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AO10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -3006,10 +3006,10 @@
         <v>12.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU10" t="n">
         <v>6.4</v>
@@ -3018,7 +3018,7 @@
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AX10" t="n">
         <v>21</v>
@@ -3030,25 +3030,25 @@
         <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BG10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -3651,157 +3651,157 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.12</v>
+        <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="H13" t="n">
-        <v>1.12</v>
+        <v>2.22</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X13" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP13" t="n">
         <v>1.01</v>
       </c>
-      <c r="M13" t="n">
+      <c r="AQ13" t="n">
         <v>1.01</v>
       </c>
-      <c r="N13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="AR13" t="n">
         <v>1.01</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AS13" t="n">
         <v>1.01</v>
       </c>
-      <c r="V13" t="n">
+      <c r="AT13" t="n">
         <v>1.01</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AU13" t="n">
         <v>1.01</v>
       </c>
-      <c r="X13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
         <v>1.03</v>
@@ -3813,13 +3813,13 @@
         <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK13" t="n">
         <v>1.01</v>
@@ -3831,7 +3831,7 @@
         <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO13" t="n">
         <v>1.01</v>
@@ -3849,7 +3849,7 @@
         <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G14" t="n">
         <v>3.5</v>
@@ -3914,7 +3914,7 @@
         <v>2.22</v>
       </c>
       <c r="I14" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J14" t="n">
         <v>3.65</v>
@@ -3938,7 +3938,7 @@
         <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
         <v>21</v>
       </c>
       <c r="Y14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z14" t="n">
         <v>18.5</v>
@@ -4016,7 +4016,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR14" t="n">
         <v>12</v>
@@ -4025,13 +4025,13 @@
         <v>4.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW14" t="n">
         <v>17.5</v>
@@ -4046,22 +4046,22 @@
         <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.7</v>
+        <v>40</v>
       </c>
       <c r="BC14" t="n">
         <v>4.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="BG14" t="n">
         <v>11.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G15" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H15" t="n">
         <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4234,7 +4234,7 @@
         <v>23</v>
       </c>
       <c r="AE15" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF15" t="n">
         <v>13.5</v>
@@ -4249,7 +4249,7 @@
         <v>70</v>
       </c>
       <c r="AJ15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK15" t="n">
         <v>20</v>
@@ -4276,7 +4276,7 @@
         <v>5</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AT15" t="n">
         <v>8.800000000000001</v>
@@ -4288,7 +4288,7 @@
         <v>16.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
@@ -4315,7 +4315,7 @@
         <v>5.3</v>
       </c>
       <c r="BF15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BG15" t="n">
         <v>5.1</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G16" t="n">
         <v>3.4</v>
@@ -4422,10 +4422,10 @@
         <v>2.2</v>
       </c>
       <c r="I16" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
         <v>4.2</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4467,25 +4467,25 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA16" t="n">
         <v>34</v>
       </c>
       <c r="AB16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC16" t="n">
         <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>26</v>
@@ -4524,49 +4524,49 @@
         <v>17.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT16" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW16" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC16" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC16" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD16" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF16" t="n">
         <v>18</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G17" t="n">
         <v>3.6</v>
@@ -4676,13 +4676,13 @@
         <v>2.34</v>
       </c>
       <c r="I17" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="J17" t="n">
         <v>3.15</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="Q18" t="n">
         <v>2.04</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5435,7 @@
         <v>2.18</v>
       </c>
       <c r="H20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I20" t="n">
         <v>3.55</v>
@@ -5495,7 +5495,7 @@
         <v>70</v>
       </c>
       <c r="AB20" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC20" t="n">
         <v>12</v>
@@ -5507,7 +5507,7 @@
         <v>40</v>
       </c>
       <c r="AF20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="n">
         <v>14</v>
@@ -5543,10 +5543,10 @@
         <v>16.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT20" t="n">
         <v>12.5</v>
@@ -5558,10 +5558,10 @@
         <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY20" t="n">
         <v>10</v>
@@ -5573,22 +5573,22 @@
         <v>4</v>
       </c>
       <c r="BB20" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BC20" t="n">
-        <v>3.7</v>
+        <v>17.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BH20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
         <v>1.33</v>
       </c>
       <c r="G21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="H21" t="n">
         <v>9.199999999999999</v>
@@ -5695,7 +5695,7 @@
         <v>10.5</v>
       </c>
       <c r="J21" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="K21" t="n">
         <v>6.8</v>
@@ -5713,7 +5713,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q21" t="n">
         <v>1.33</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>1.27</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -5967,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
         <v>4.6</v>
       </c>
       <c r="H23" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I23" t="n">
         <v>2.18</v>
@@ -6224,7 +6224,7 @@
         <v>1.68</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G26" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="H26" t="n">
-        <v>3.55</v>
+        <v>12</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="J26" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -7467,16 +7467,16 @@
         <v>1.51</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="I28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J28" t="n">
         <v>4</v>
       </c>
       <c r="K28" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
         <v>1.57</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="I30" t="n">
         <v>10.5</v>
@@ -7999,10 +7999,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -8223,22 +8223,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="G31" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="H31" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="I31" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="J31" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K31" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8253,10 +8253,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -8477,22 +8477,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="G32" t="n">
-        <v>1000</v>
+        <v>1.54</v>
       </c>
       <c r="H32" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="J32" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="K32" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -8507,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.24</v>
+        <v>1.96</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -10255,22 +10255,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="G39" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="H39" t="n">
-        <v>9.4</v>
+        <v>5.5</v>
       </c>
       <c r="I39" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="J39" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="K39" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -10285,10 +10285,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -10512,19 +10512,19 @@
         <v>2.36</v>
       </c>
       <c r="G40" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="H40" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="I40" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
-        <v>2.96</v>
+        <v>3.55</v>
       </c>
       <c r="K40" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -10539,10 +10539,10 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-18.xlsx
@@ -863,7 +863,7 @@
         <v>1.78</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
         <v>5.9</v>
@@ -890,19 +890,19 @@
         <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="R2" t="n">
         <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T2" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="U2" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="V2" t="n">
         <v>1.2</v>
@@ -914,7 +914,7 @@
         <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Z2" t="n">
         <v>55</v>
@@ -929,13 +929,13 @@
         <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
         <v>80</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -947,10 +947,10 @@
         <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL2" t="n">
         <v>36</v>
@@ -959,10 +959,10 @@
         <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP2" t="n">
         <v>16.5</v>
@@ -974,7 +974,7 @@
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AT2" t="n">
         <v>8.4</v>
@@ -986,7 +986,7 @@
         <v>17.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX2" t="n">
         <v>9.4</v>
@@ -998,7 +998,7 @@
         <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BB2" t="n">
         <v>14.5</v>
@@ -1007,16 +1007,16 @@
         <v>14</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BF2" t="n">
         <v>6.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
         <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="G5" t="n">
         <v>3.7</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>3.2</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
         <v>4.4</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="G8" t="n">
         <v>1.53</v>
       </c>
       <c r="H8" t="n">
-        <v>1.21</v>
+        <v>6.6</v>
       </c>
       <c r="I8" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="K8" t="n">
         <v>5.6</v>
@@ -2414,7 +2414,7 @@
         <v>2.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
         <v>12.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AT10" t="n">
         <v>10.5</v>
@@ -3018,7 +3018,7 @@
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AX10" t="n">
         <v>21</v>
@@ -3030,19 +3030,19 @@
         <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC10" t="n">
         <v>4</v>
       </c>
       <c r="BD10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF10" t="n">
         <v>4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2.28</v>
       </c>
       <c r="G11" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="H11" t="n">
         <v>3.1</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -3651,169 +3651,169 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>3.45</v>
       </c>
       <c r="H13" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I13" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>2.54</v>
+        <v>2.92</v>
       </c>
       <c r="T13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U13" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="W13" t="n">
         <v>1.4</v>
       </c>
       <c r="X13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AA13" t="n">
         <v>38</v>
       </c>
       <c r="AB13" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
       </c>
       <c r="AF13" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AG13" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AH13" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI13" t="n">
         <v>40</v>
       </c>
       <c r="AJ13" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL13" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM13" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AN13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO13" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI13" t="n">
         <v>3</v>
@@ -3822,49 +3822,49 @@
         <v>9</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BN13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BT13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
         <v>3.65</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3986,10 +3986,10 @@
         <v>29</v>
       </c>
       <c r="AG14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI14" t="n">
         <v>38</v>
@@ -4001,7 +4001,7 @@
         <v>42</v>
       </c>
       <c r="AL14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM14" t="n">
         <v>85</v>
@@ -4013,7 +4013,7 @@
         <v>17.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>9.199999999999999</v>
@@ -4022,16 +4022,16 @@
         <v>12</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AU14" t="n">
         <v>7.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW14" t="n">
         <v>17.5</v>
@@ -4046,7 +4046,7 @@
         <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB14" t="n">
         <v>40</v>
@@ -4055,10 +4055,10 @@
         <v>4.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.5</v>
+        <v>30</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF14" t="n">
         <v>21</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
         <v>28</v>
       </c>
       <c r="AO16" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP16" t="n">
         <v>17.5</v>
@@ -4554,16 +4554,16 @@
         <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC16" t="n">
         <v>4.8</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE16" t="n">
         <v>5.1</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v>2.62</v>
       </c>
       <c r="J17" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K17" t="n">
         <v>3.55</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G20" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I20" t="n">
         <v>3.55</v>
@@ -5498,7 +5498,7 @@
         <v>17</v>
       </c>
       <c r="AC20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD20" t="n">
         <v>18</v>
@@ -5513,7 +5513,7 @@
         <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI20" t="n">
         <v>44</v>
@@ -5543,10 +5543,10 @@
         <v>16.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT20" t="n">
         <v>12.5</v>
@@ -5558,7 +5558,7 @@
         <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AX20" t="n">
         <v>15</v>
@@ -5570,22 +5570,22 @@
         <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BC20" t="n">
         <v>17.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG20" t="n">
         <v>15.5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
         <v>6</v>
       </c>
       <c r="K21" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -5716,7 +5716,7 @@
         <v>3.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="G22" t="n">
         <v>1.27</v>
       </c>
       <c r="H22" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="I22" t="n">
         <v>18</v>
@@ -5952,7 +5952,7 @@
         <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -5970,7 +5970,7 @@
         <v>1.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -6194,13 +6194,13 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="H23" t="n">
         <v>2.02</v>
       </c>
       <c r="I23" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="J23" t="n">
         <v>3.2</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -6445,19 +6445,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G24" t="n">
         <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I24" t="n">
         <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -6699,19 +6699,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G25" t="n">
         <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I25" t="n">
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
         <v>11.5</v>
       </c>
       <c r="J28" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="K28" t="n">
         <v>5</v>
@@ -7494,7 +7494,7 @@
         <v>1.92</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
         <v>1.57</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
         <v>10.5</v>
@@ -8002,7 +8002,7 @@
         <v>1.88</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
         <v>2.7</v>
       </c>
       <c r="G31" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="H31" t="n">
         <v>2.58</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -8480,16 +8480,16 @@
         <v>1.39</v>
       </c>
       <c r="G32" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="H32" t="n">
-        <v>5.8</v>
+        <v>1.21</v>
       </c>
       <c r="I32" t="n">
         <v>11.5</v>
       </c>
       <c r="J32" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K32" t="n">
         <v>5.6</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
         <v>1000</v>
       </c>
       <c r="J35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -10255,22 +10255,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="G39" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="H39" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="I39" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="J39" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K39" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -10288,7 +10288,7 @@
         <v>1.81</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -10524,7 +10524,7 @@
         <v>3.55</v>
       </c>
       <c r="K40" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -10542,7 +10542,7 @@
         <v>2.06</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-18.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="G2" t="n">
         <v>1.76</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I2" t="n">
         <v>5.9</v>
@@ -872,7 +872,7 @@
         <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -884,13 +884,13 @@
         <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
         <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R2" t="n">
         <v>1.44</v>
@@ -902,7 +902,7 @@
         <v>1.77</v>
       </c>
       <c r="U2" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="V2" t="n">
         <v>1.2</v>
@@ -914,7 +914,7 @@
         <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Z2" t="n">
         <v>55</v>
@@ -929,7 +929,7 @@
         <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
         <v>80</v>
@@ -971,10 +971,10 @@
         <v>17.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT2" t="n">
         <v>8.4</v>
@@ -986,7 +986,7 @@
         <v>17.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX2" t="n">
         <v>9.4</v>
@@ -998,7 +998,7 @@
         <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BB2" t="n">
         <v>14.5</v>
@@ -1007,16 +1007,16 @@
         <v>13</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF2" t="n">
         <v>6.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
         <v>1.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R3" t="n">
         <v>1.38</v>
@@ -1153,10 +1153,10 @@
         <v>3.15</v>
       </c>
       <c r="T3" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="V3" t="n">
         <v>1.54</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
         <v>1.35</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>2.48</v>
       </c>
       <c r="G7" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H7" t="n">
         <v>2.92</v>
@@ -2142,7 +2142,7 @@
         <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
         <v>1.35</v>
@@ -2160,10 +2160,10 @@
         <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
         <v>3.35</v>
@@ -2172,13 +2172,13 @@
         <v>1.75</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X7" t="n">
         <v>18</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>2.38</v>
       </c>
       <c r="I8" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
@@ -2414,7 +2414,7 @@
         <v>1.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
         <v>1.24</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G9" t="n">
         <v>3.35</v>
       </c>
       <c r="H9" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I9" t="n">
         <v>2.76</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G10" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H10" t="n">
         <v>4.5</v>
@@ -2919,13 +2919,13 @@
         <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q10" t="n">
         <v>2.02</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
         <v>3.65</v>
@@ -2961,10 +2961,10 @@
         <v>8.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF10" t="n">
         <v>14</v>
@@ -3003,10 +3003,10 @@
         <v>11.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AT10" t="n">
         <v>7.4</v>
@@ -3018,7 +3018,7 @@
         <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3030,7 +3030,7 @@
         <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BB10" t="n">
         <v>18</v>
@@ -3039,19 +3039,19 @@
         <v>17.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF10" t="n">
         <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI10" t="n">
         <v>2.64</v>
@@ -3060,13 +3060,13 @@
         <v>12.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BL10" t="n">
         <v>170</v>
       </c>
       <c r="BM10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BN10" t="n">
         <v>5.3</v>
@@ -3078,7 +3078,7 @@
         <v>16.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BR10" t="n">
         <v>36</v>
@@ -3096,23 +3096,23 @@
         <v>50</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BX10" t="n">
         <v>65</v>
       </c>
       <c r="BY10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>32</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G11" t="n">
         <v>3.2</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G12" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H12" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="J12" t="n">
         <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
         <v>1.36</v>
@@ -3427,10 +3427,10 @@
         <v>1.28</v>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="R12" t="n">
         <v>1.39</v>
@@ -3439,16 +3439,16 @@
         <v>3.15</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="U12" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W12" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="X12" t="n">
         <v>19</v>
@@ -3466,7 +3466,7 @@
         <v>13.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>14.5</v>
@@ -3487,7 +3487,7 @@
         <v>48</v>
       </c>
       <c r="AJ12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK12" t="n">
         <v>30</v>
@@ -3505,13 +3505,13 @@
         <v>34</v>
       </c>
       <c r="AP12" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>10.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AS12" t="n">
         <v>5.1</v>
@@ -3520,13 +3520,13 @@
         <v>9</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
         <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX12" t="n">
         <v>12.5</v>
@@ -3538,10 +3538,10 @@
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB12" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>4.8</v>
       </c>
       <c r="BC12" t="n">
         <v>21</v>
@@ -3568,13 +3568,13 @@
         <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BL12" t="n">
         <v>120</v>
       </c>
       <c r="BM12" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BN12" t="n">
         <v>6.2</v>
@@ -3583,7 +3583,7 @@
         <v>4.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BQ12" t="n">
         <v>4.7</v>
@@ -3592,7 +3592,7 @@
         <v>34</v>
       </c>
       <c r="BS12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BT12" t="n">
         <v>6.6</v>
@@ -3604,23 +3604,23 @@
         <v>27</v>
       </c>
       <c r="BW12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BX12" t="n">
         <v>38</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BZ12" t="n">
         <v>27</v>
       </c>
       <c r="CA12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -3693,10 +3693,10 @@
         <v>3.15</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="U13" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="V13" t="n">
         <v>1.8</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G14" t="n">
         <v>3.7</v>
@@ -3920,7 +3920,7 @@
         <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L14" t="n">
         <v>1.28</v>
@@ -3929,25 +3929,25 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
         <v>1.82</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="T14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U14" t="n">
         <v>2.2</v>
@@ -3962,10 +3962,10 @@
         <v>19</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA14" t="n">
         <v>36</v>
@@ -3992,7 +3992,7 @@
         <v>19</v>
       </c>
       <c r="AI14" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ14" t="n">
         <v>65</v>
@@ -4007,10 +4007,10 @@
         <v>90</v>
       </c>
       <c r="AN14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AP14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>3.85</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K15" t="n">
         <v>3.55</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>2.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="R16" t="n">
         <v>1.72</v>
@@ -4518,7 +4518,7 @@
         <v>12.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP16" t="n">
         <v>3.8</v>
@@ -4530,7 +4530,7 @@
         <v>19</v>
       </c>
       <c r="AS16" t="n">
-        <v>40</v>
+        <v>3.95</v>
       </c>
       <c r="AT16" t="n">
         <v>15</v>
@@ -4584,7 +4584,7 @@
         <v>10</v>
       </c>
       <c r="BK16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BL16" t="n">
         <v>80</v>
@@ -4596,7 +4596,7 @@
         <v>7</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP16" t="n">
         <v>18</v>
@@ -4608,10 +4608,10 @@
         <v>26</v>
       </c>
       <c r="BS16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BT16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU16" t="n">
         <v>5.1</v>
@@ -4620,7 +4620,7 @@
         <v>24</v>
       </c>
       <c r="BW16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BX16" t="n">
         <v>30</v>
@@ -4632,11 +4632,11 @@
         <v>16.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4700,7 @@
         <v>2.62</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="R17" t="n">
         <v>1.65</v>
@@ -4823,7 +4823,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BG17" t="n">
         <v>8.6</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -4924,19 +4924,19 @@
         <v>3.6</v>
       </c>
       <c r="G18" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="H18" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I18" t="n">
         <v>2.36</v>
       </c>
       <c r="J18" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L18" t="n">
         <v>1.43</v>
@@ -4951,7 +4951,7 @@
         <v>1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q18" t="n">
         <v>2.1</v>
@@ -4969,7 +4969,7 @@
         <v>2.04</v>
       </c>
       <c r="V18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W18" t="n">
         <v>1.29</v>
@@ -4981,7 +4981,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z18" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA18" t="n">
         <v>38</v>
@@ -5065,7 +5065,7 @@
         <v>4.7</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC18" t="n">
         <v>4.7</v>
@@ -5074,7 +5074,7 @@
         <v>4.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF18" t="n">
         <v>4.7</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -5175,19 +5175,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="G19" t="n">
         <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="I19" t="n">
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="G20" t="n">
         <v>2.46</v>
@@ -5447,7 +5447,7 @@
         <v>4.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -5456,31 +5456,31 @@
         <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P20" t="n">
         <v>2.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T20" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="U20" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="V20" t="n">
         <v>1.41</v>
       </c>
       <c r="W20" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X20" t="n">
         <v>20</v>
@@ -5489,7 +5489,7 @@
         <v>16</v>
       </c>
       <c r="Z20" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA20" t="n">
         <v>55</v>
@@ -5546,7 +5546,7 @@
         <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT20" t="n">
         <v>10</v>
@@ -5558,7 +5558,7 @@
         <v>12</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX20" t="n">
         <v>11.5</v>
@@ -5570,7 +5570,7 @@
         <v>13.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -5582,7 +5582,7 @@
         <v>26</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF20" t="n">
         <v>12.5</v>
@@ -5594,65 +5594,65 @@
         <v>4.5</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ20" t="n">
         <v>11</v>
       </c>
       <c r="BK20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BL20" t="n">
         <v>110</v>
       </c>
       <c r="BM20" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BN20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP20" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BR20" t="n">
         <v>32</v>
       </c>
       <c r="BS20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BT20" t="n">
         <v>7.8</v>
       </c>
       <c r="BU20" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW20" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BX20" t="n">
         <v>38</v>
       </c>
       <c r="BY20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BZ20" t="n">
         <v>25</v>
       </c>
       <c r="CA20" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
         <v>3.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="M21" t="n">
         <v>1.08</v>
@@ -5725,10 +5725,10 @@
         <v>3.7</v>
       </c>
       <c r="T21" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="V21" t="n">
         <v>1.37</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -5955,13 +5955,13 @@
         <v>4.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
         <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O22" t="n">
         <v>1.21</v>
@@ -5970,7 +5970,7 @@
         <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="R22" t="n">
         <v>1.56</v>
@@ -6042,10 +6042,10 @@
         <v>12</v>
       </c>
       <c r="AO22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AQ22" t="n">
         <v>16.5</v>
@@ -6054,7 +6054,7 @@
         <v>3.85</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT22" t="n">
         <v>11</v>
@@ -6090,7 +6090,7 @@
         <v>20</v>
       </c>
       <c r="BE22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF22" t="n">
         <v>7.4</v>
@@ -6099,7 +6099,7 @@
         <v>3.85</v>
       </c>
       <c r="BH22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI22" t="n">
         <v>3.3</v>
@@ -6123,10 +6123,10 @@
         <v>4.5</v>
       </c>
       <c r="BP22" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BR22" t="n">
         <v>27</v>
@@ -6153,14 +6153,14 @@
         <v>4.2</v>
       </c>
       <c r="BZ22" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA22" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G25" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H25" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I25" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J25" t="n">
         <v>3.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -6723,31 +6723,31 @@
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O25" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T25" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="U25" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V25" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W25" t="n">
         <v>1.54</v>
@@ -6768,13 +6768,13 @@
         <v>13</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF25" t="n">
         <v>19.5</v>
@@ -6801,10 +6801,10 @@
         <v>100</v>
       </c>
       <c r="AN25" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AO25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP25" t="n">
         <v>13</v>
@@ -6816,7 +6816,7 @@
         <v>13</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT25" t="n">
         <v>10.5</v>
@@ -6834,25 +6834,25 @@
         <v>13.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="AZ25" t="n">
         <v>14.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BC25" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF25" t="n">
         <v>18</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
         <v>2.12</v>
       </c>
       <c r="G26" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H26" t="n">
         <v>3.45</v>
@@ -6971,7 +6971,7 @@
         <v>3.9</v>
       </c>
       <c r="L26" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
@@ -7007,13 +7007,13 @@
         <v>1.8</v>
       </c>
       <c r="X26" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y26" t="n">
         <v>18</v>
       </c>
       <c r="Z26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA26" t="n">
         <v>80</v>
@@ -7022,10 +7022,10 @@
         <v>13</v>
       </c>
       <c r="AC26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD26" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE26" t="n">
         <v>50</v>
@@ -7037,7 +7037,7 @@
         <v>13.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI26" t="n">
         <v>60</v>
@@ -7070,7 +7070,7 @@
         <v>19.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AT26" t="n">
         <v>9.199999999999999</v>
@@ -7082,7 +7082,7 @@
         <v>11</v>
       </c>
       <c r="AW26" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AX26" t="n">
         <v>10.5</v>
@@ -7094,7 +7094,7 @@
         <v>14</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BB26" t="n">
         <v>19.5</v>
@@ -7103,16 +7103,16 @@
         <v>19</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BE26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF26" t="n">
         <v>11</v>
       </c>
       <c r="BG26" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BH26" t="n">
         <v>4.2</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G27" t="n">
         <v>3.5</v>
@@ -7267,7 +7267,7 @@
         <v>12</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA27" t="n">
         <v>38</v>
@@ -7315,58 +7315,58 @@
         <v>16.5</v>
       </c>
       <c r="AP27" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AR27" t="n">
         <v>5</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT27" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AX27" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AY27" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AZ27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG27" t="n">
         <v>5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>4.8</v>
       </c>
       <c r="BH27" t="n">
         <v>3.7</v>
@@ -7408,7 +7408,7 @@
         <v>5.4</v>
       </c>
       <c r="BU27" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BV27" t="n">
         <v>16.5</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -7497,7 +7497,7 @@
         <v>1.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
         <v>3.25</v>
@@ -7578,7 +7578,7 @@
         <v>21</v>
       </c>
       <c r="AS28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT28" t="n">
         <v>9.4</v>
@@ -7614,7 +7614,7 @@
         <v>26</v>
       </c>
       <c r="BE28" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF28" t="n">
         <v>15.5</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G29" t="n">
         <v>3.4</v>
@@ -7733,7 +7733,7 @@
         <v>4.2</v>
       </c>
       <c r="L29" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M29" t="n">
         <v>1.04</v>
@@ -7760,7 +7760,7 @@
         <v>1.58</v>
       </c>
       <c r="U29" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V29" t="n">
         <v>1.73</v>
@@ -7883,19 +7883,19 @@
         <v>3.25</v>
       </c>
       <c r="BJ29" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BK29" t="n">
-        <v>6.4</v>
+        <v>3.45</v>
       </c>
       <c r="BL29" t="n">
         <v>95</v>
       </c>
       <c r="BM29" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BN29" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BO29" t="n">
         <v>4.4</v>
@@ -7904,7 +7904,7 @@
         <v>27</v>
       </c>
       <c r="BQ29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR29" t="n">
         <v>36</v>
@@ -7913,7 +7913,7 @@
         <v>5</v>
       </c>
       <c r="BT29" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BU29" t="n">
         <v>5</v>
@@ -7928,17 +7928,17 @@
         <v>29</v>
       </c>
       <c r="BY29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BZ29" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="CA29" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
         <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K30" t="n">
         <v>1000</v>
@@ -7996,7 +7996,7 @@
         <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="P30" t="n">
         <v>1.25</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -8477,10 +8477,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G32" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H32" t="n">
         <v>5</v>
@@ -8570,7 +8570,7 @@
         <v>21</v>
       </c>
       <c r="AK32" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL32" t="n">
         <v>36</v>
@@ -8627,7 +8627,7 @@
         <v>14.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE32" t="n">
         <v>5.3</v>
@@ -8636,7 +8636,7 @@
         <v>7</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH32" t="n">
         <v>4.5</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -8749,13 +8749,13 @@
         <v>4.4</v>
       </c>
       <c r="L33" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="M33" t="n">
         <v>1.04</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O33" t="n">
         <v>1.21</v>
@@ -8764,7 +8764,7 @@
         <v>2.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R33" t="n">
         <v>1.55</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -9006,7 +9006,7 @@
         <v>1.44</v>
       </c>
       <c r="M34" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N34" t="n">
         <v>2.62</v>
@@ -9024,7 +9024,7 @@
         <v>1.21</v>
       </c>
       <c r="S34" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T34" t="n">
         <v>1.94</v>
@@ -9147,7 +9147,7 @@
         <v>1.01</v>
       </c>
       <c r="BH34" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI34" t="n">
         <v>2.34</v>
@@ -9156,37 +9156,37 @@
         <v>13</v>
       </c>
       <c r="BK34" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BL34" t="n">
         <v>210</v>
       </c>
       <c r="BM34" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN34" t="n">
         <v>7.2</v>
       </c>
       <c r="BO34" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BP34" t="n">
         <v>34</v>
       </c>
       <c r="BQ34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BR34" t="n">
         <v>60</v>
       </c>
       <c r="BS34" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BT34" t="n">
         <v>6.6</v>
       </c>
       <c r="BU34" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BV34" t="n">
         <v>29</v>
@@ -9198,17 +9198,17 @@
         <v>55</v>
       </c>
       <c r="BY34" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BZ34" t="n">
         <v>55</v>
       </c>
       <c r="CA34" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -9251,10 +9251,10 @@
         <v>1000</v>
       </c>
       <c r="J35" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="K35" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -9523,22 +9523,22 @@
         <v>1.17</v>
       </c>
       <c r="P36" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="R36" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="S36" t="n">
         <v>2.24</v>
       </c>
       <c r="T36" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U36" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="V36" t="n">
         <v>1.42</v>
@@ -9658,7 +9658,7 @@
         <v>1000</v>
       </c>
       <c r="BI36" t="n">
-        <v>2.08</v>
+        <v>1.56</v>
       </c>
       <c r="BJ36" t="n">
         <v>11.5</v>
@@ -9670,25 +9670,25 @@
         <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>2.08</v>
+        <v>1.56</v>
       </c>
       <c r="BN36" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO36" t="n">
-        <v>3.85</v>
+        <v>1.56</v>
       </c>
       <c r="BP36" t="n">
         <v>20</v>
       </c>
       <c r="BQ36" t="n">
-        <v>1.89</v>
+        <v>1.45</v>
       </c>
       <c r="BR36" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS36" t="n">
-        <v>1.95</v>
+        <v>1.56</v>
       </c>
       <c r="BT36" t="n">
         <v>9.6</v>
@@ -9700,23 +9700,23 @@
         <v>29</v>
       </c>
       <c r="BW36" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="BX36" t="n">
         <v>34</v>
       </c>
       <c r="BY36" t="n">
-        <v>1.97</v>
+        <v>1.49</v>
       </c>
       <c r="BZ36" t="n">
         <v>18.5</v>
       </c>
       <c r="CA36" t="n">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
         <v>1.76</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R37" t="n">
         <v>1.29</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
         <v>3.15</v>
       </c>
       <c r="K38" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L38" t="n">
         <v>1.35</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
         <v>2.98</v>
       </c>
       <c r="G39" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="H39" t="n">
         <v>2.34</v>
@@ -10306,7 +10306,7 @@
         <v>1.59</v>
       </c>
       <c r="W39" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G40" t="n">
         <v>2.24</v>
@@ -10524,7 +10524,7 @@
         <v>3.95</v>
       </c>
       <c r="K40" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G41" t="n">
         <v>1.33</v>
@@ -10772,43 +10772,43 @@
         <v>10</v>
       </c>
       <c r="I41" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J41" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="K41" t="n">
         <v>7.2</v>
       </c>
       <c r="L41" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="M41" t="n">
         <v>1.02</v>
       </c>
       <c r="N41" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="O41" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P41" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="R41" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="S41" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="T41" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="U41" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="V41" t="n">
         <v>1.01</v>
@@ -10817,7 +10817,7 @@
         <v>1.01</v>
       </c>
       <c r="X41" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Y41" t="n">
         <v>60</v>
@@ -10829,10 +10829,10 @@
         <v>360</v>
       </c>
       <c r="AB41" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AD41" t="n">
         <v>46</v>
@@ -10841,7 +10841,7 @@
         <v>160</v>
       </c>
       <c r="AF41" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG41" t="n">
         <v>14</v>
@@ -10865,46 +10865,46 @@
         <v>120</v>
       </c>
       <c r="AN41" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AO41" t="n">
         <v>140</v>
       </c>
       <c r="AP41" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ41" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV41" t="n">
         <v>5.1</v>
       </c>
-      <c r="AR41" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AW41" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX41" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY41" t="n">
         <v>10</v>
       </c>
       <c r="AZ41" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB41" t="n">
         <v>10</v>
@@ -10913,16 +10913,16 @@
         <v>11.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF41" t="n">
         <v>3.3</v>
       </c>
       <c r="BG41" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BH41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
         <v>2.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="R42" t="n">
         <v>1.57</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
         <v>2.22</v>
       </c>
       <c r="G43" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="H43" t="n">
         <v>3.55</v>
@@ -11304,7 +11304,7 @@
         <v>1.58</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R43" t="n">
         <v>1.2</v>
@@ -11316,13 +11316,13 @@
         <v>1.84</v>
       </c>
       <c r="U43" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="V43" t="n">
         <v>1.32</v>
       </c>
       <c r="W43" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11549,7 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="O44" t="n">
         <v>1.06</v>
@@ -11558,10 +11558,10 @@
         <v>4.9</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="R44" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="S44" t="n">
         <v>1.52</v>
@@ -11570,7 +11570,7 @@
         <v>1.72</v>
       </c>
       <c r="U44" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V44" t="n">
         <v>6.2</v>
@@ -11582,7 +11582,7 @@
         <v>90</v>
       </c>
       <c r="Y44" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z44" t="n">
         <v>14.5</v>
@@ -11657,76 +11657,76 @@
         <v>10.5</v>
       </c>
       <c r="AX44" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY44" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ44" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA44" t="n">
         <v>23</v>
       </c>
       <c r="BB44" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC44" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BD44" t="n">
         <v>8.4</v>
       </c>
       <c r="BE44" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF44" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG44" t="n">
         <v>2.04</v>
       </c>
       <c r="BH44" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BI44" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BJ44" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK44" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL44" t="n">
         <v>1000</v>
       </c>
       <c r="BM44" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BN44" t="n">
         <v>21</v>
       </c>
       <c r="BO44" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BP44" t="n">
         <v>1000</v>
       </c>
       <c r="BQ44" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR44" t="n">
         <v>1000</v>
       </c>
       <c r="BS44" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT44" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BU44" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BV44" t="n">
         <v>6.4</v>
@@ -11735,20 +11735,20 @@
         <v>4.8</v>
       </c>
       <c r="BX44" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BY44" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BZ44" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="CA44" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -11782,13 +11782,13 @@
         <v>1.2</v>
       </c>
       <c r="G45" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="H45" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="J45" t="n">
         <v>7</v>
@@ -11830,7 +11830,7 @@
         <v>1.05</v>
       </c>
       <c r="W45" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -12057,10 +12057,10 @@
         <v>1.1</v>
       </c>
       <c r="N46" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="O46" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P46" t="n">
         <v>1.66</v>
@@ -12069,10 +12069,10 @@
         <v>2.28</v>
       </c>
       <c r="R46" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S46" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T46" t="n">
         <v>1.92</v>
@@ -12087,112 +12087,112 @@
         <v>1.32</v>
       </c>
       <c r="X46" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y46" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="Z46" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB46" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD46" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE46" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF46" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG46" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH46" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI46" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL46" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM46" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN46" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO46" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.28</v>
+        <v>9</v>
       </c>
       <c r="AQ46" t="n">
         <v>7.2</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.28</v>
+        <v>11.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.28</v>
+        <v>5.3</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.28</v>
+        <v>10</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.11</v>
+        <v>6.4</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.28</v>
+        <v>10</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.28</v>
+        <v>5.2</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.28</v>
+        <v>5.2</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.28</v>
+        <v>14</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.28</v>
+        <v>17</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.28</v>
+        <v>5.6</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.28</v>
+        <v>5.8</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.28</v>
+        <v>5.7</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.28</v>
+        <v>5.8</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.28</v>
+        <v>6</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.28</v>
+        <v>5.8</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.28</v>
+        <v>19</v>
       </c>
       <c r="BH46" t="n">
         <v>1000</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
         <v>1000</v>
       </c>
       <c r="J47" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="K47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -12574,7 +12574,7 @@
         <v>1.56</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="R48" t="n">
         <v>1.15</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -12795,22 +12795,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.08</v>
+        <v>2.02</v>
       </c>
       <c r="G49" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="H49" t="n">
-        <v>1.91</v>
+        <v>3.65</v>
       </c>
       <c r="I49" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="J49" t="n">
         <v>3</v>
       </c>
       <c r="K49" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L49" t="n">
         <v>1.01</v>
@@ -12819,22 +12819,22 @@
         <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O49" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="P49" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R49" t="n">
         <v>1.08</v>
       </c>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T49" t="n">
         <v>1.04</v>
@@ -12843,118 +12843,118 @@
         <v>1.01</v>
       </c>
       <c r="V49" t="n">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="W49" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="X49" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z49" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA49" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AB49" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC49" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD49" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE49" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AF49" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG49" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH49" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AI49" t="n">
         <v>1000</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK49" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL49" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM49" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AN49" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO49" t="n">
-        <v>1000</v>
+        <v>760</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AS49" t="n">
         <v>1.01</v>
       </c>
       <c r="AT49" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA49" t="n">
         <v>1.01</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD49" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BE49" t="n">
         <v>1.01</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG49" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BH49" t="n">
         <v>1000</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -13073,13 +13073,13 @@
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O50" t="n">
         <v>1.01</v>
       </c>
       <c r="P50" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q50" t="n">
         <v>1.01</v>
@@ -13088,7 +13088,7 @@
         <v>1.12</v>
       </c>
       <c r="S50" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="T50" t="n">
         <v>1.01</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -13327,13 +13327,13 @@
         <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O51" t="n">
         <v>1.01</v>
       </c>
       <c r="P51" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q51" t="n">
         <v>1.02</v>
@@ -13342,7 +13342,7 @@
         <v>1.12</v>
       </c>
       <c r="S51" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="T51" t="n">
         <v>1.01</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -13560,22 +13560,22 @@
         <v>2.82</v>
       </c>
       <c r="G52" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="H52" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I52" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="J52" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="K52" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="L52" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M52" t="n">
         <v>1.01</v>
@@ -13584,10 +13584,10 @@
         <v>3.1</v>
       </c>
       <c r="O52" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P52" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="Q52" t="n">
         <v>2.04</v>
@@ -13596,7 +13596,7 @@
         <v>1.24</v>
       </c>
       <c r="S52" t="n">
-        <v>2.28</v>
+        <v>3.4</v>
       </c>
       <c r="T52" t="n">
         <v>1.01</v>
@@ -13605,10 +13605,10 @@
         <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W52" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="X52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -13844,13 +13844,13 @@
         <v>1.07</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="R53" t="n">
         <v>1.07</v>
       </c>
       <c r="S53" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="T53" t="n">
         <v>1.01</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
         <v>2.34</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I54" t="n">
         <v>4.5</v>
@@ -14080,7 +14080,7 @@
         <v>3.25</v>
       </c>
       <c r="K54" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -14101,7 +14101,7 @@
         <v>1.53</v>
       </c>
       <c r="R54" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S54" t="n">
         <v>2.32</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -14349,7 +14349,7 @@
         <v>1.32</v>
       </c>
       <c r="P55" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q55" t="n">
         <v>1.9</v>
@@ -14397,7 +14397,7 @@
         <v>190</v>
       </c>
       <c r="AF55" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG55" t="n">
         <v>12</v>
@@ -14409,10 +14409,10 @@
         <v>170</v>
       </c>
       <c r="AJ55" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK55" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL55" t="n">
         <v>50</v>
@@ -14421,7 +14421,7 @@
         <v>210</v>
       </c>
       <c r="AN55" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO55" t="n">
         <v>300</v>
@@ -14433,10 +14433,10 @@
         <v>20</v>
       </c>
       <c r="AR55" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AS55" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT55" t="n">
         <v>6.2</v>
@@ -14445,10 +14445,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV55" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AW55" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX55" t="n">
         <v>7.2</v>
@@ -14457,10 +14457,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ55" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BA55" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB55" t="n">
         <v>10.5</v>
@@ -14469,16 +14469,16 @@
         <v>14.5</v>
       </c>
       <c r="BD55" t="n">
-        <v>5.4</v>
+        <v>34</v>
       </c>
       <c r="BE55" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF55" t="n">
         <v>6.4</v>
       </c>
       <c r="BG55" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH55" t="n">
         <v>1000</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -14579,7 +14579,7 @@
         <v>3.8</v>
       </c>
       <c r="H56" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="I56" t="n">
         <v>2.78</v>
@@ -14588,10 +14588,10 @@
         <v>2.64</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="L56" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M56" t="n">
         <v>1.01</v>
@@ -14606,7 +14606,7 @@
         <v>1.69</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="R56" t="n">
         <v>1.22</v>
@@ -14615,10 +14615,10 @@
         <v>3.05</v>
       </c>
       <c r="T56" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="U56" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V56" t="n">
         <v>1.56</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -14842,10 +14842,10 @@
         <v>5.5</v>
       </c>
       <c r="K57" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="L57" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M57" t="n">
         <v>1.01</v>
@@ -14929,64 +14929,64 @@
         <v>1000</v>
       </c>
       <c r="AN57" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AO57" t="n">
         <v>1000</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AT57" t="n">
         <v>7</v>
       </c>
       <c r="AU57" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AV57" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AY57" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AZ57" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="BA57" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="BB57" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="BC57" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="BD57" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="BF57" t="n">
         <v>1.28</v>
       </c>
       <c r="BG57" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="BH57" t="n">
         <v>1000</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -15111,13 +15111,13 @@
         <v>1.04</v>
       </c>
       <c r="P58" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="R58" t="n">
-        <v>1.64</v>
+        <v>1.18</v>
       </c>
       <c r="S58" t="n">
         <v>1.04</v>
@@ -15189,52 +15189,52 @@
         <v>1000</v>
       </c>
       <c r="AP58" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AQ58" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AR58" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AS58" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT58" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU58" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AV58" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AW58" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX58" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY58" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ58" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BA58" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB58" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC58" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD58" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE58" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF58" t="n">
         <v>1.01</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -15335,31 +15335,31 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="G59" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="H59" t="n">
         <v>5.9</v>
       </c>
       <c r="I59" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J59" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="K59" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="L59" t="n">
         <v>1.4</v>
       </c>
       <c r="M59" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N59" t="n">
-        <v>1.63</v>
+        <v>2.92</v>
       </c>
       <c r="O59" t="n">
         <v>1.45</v>
@@ -15371,76 +15371,76 @@
         <v>2.28</v>
       </c>
       <c r="R59" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S59" t="n">
         <v>4.4</v>
       </c>
       <c r="T59" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U59" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V59" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W59" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="X59" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y59" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z59" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA59" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB59" t="n">
         <v>7</v>
       </c>
       <c r="AC59" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD59" t="n">
         <v>27</v>
       </c>
       <c r="AE59" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF59" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG59" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH59" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI59" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ59" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK59" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL59" t="n">
         <v>55</v>
       </c>
       <c r="AM59" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN59" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO59" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AP59" t="n">
         <v>9.199999999999999</v>
@@ -15449,10 +15449,10 @@
         <v>14</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.24</v>
+        <v>4.5</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.24</v>
+        <v>4.7</v>
       </c>
       <c r="AT59" t="n">
         <v>5.7</v>
@@ -15464,7 +15464,7 @@
         <v>21</v>
       </c>
       <c r="AW59" t="n">
-        <v>1.24</v>
+        <v>4.7</v>
       </c>
       <c r="AX59" t="n">
         <v>7.8</v>
@@ -15476,7 +15476,7 @@
         <v>21</v>
       </c>
       <c r="BA59" t="n">
-        <v>1.24</v>
+        <v>4.7</v>
       </c>
       <c r="BB59" t="n">
         <v>15.5</v>
@@ -15485,16 +15485,16 @@
         <v>18.5</v>
       </c>
       <c r="BD59" t="n">
-        <v>1.22</v>
+        <v>4.4</v>
       </c>
       <c r="BE59" t="n">
-        <v>1.24</v>
+        <v>4.7</v>
       </c>
       <c r="BF59" t="n">
         <v>11.5</v>
       </c>
       <c r="BG59" t="n">
-        <v>1.24</v>
+        <v>4.7</v>
       </c>
       <c r="BH59" t="n">
         <v>1000</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -15589,230 +15589,230 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="G60" t="n">
-        <v>110</v>
+        <v>2.06</v>
       </c>
       <c r="H60" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="I60" t="n">
-        <v>220</v>
+        <v>5.4</v>
       </c>
       <c r="J60" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="K60" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L60" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M60" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N60" t="n">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="O60" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P60" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="Q60" t="n">
         <v>2.2</v>
       </c>
       <c r="R60" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="S60" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="T60" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="U60" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V60" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W60" t="n">
         <v>1.94</v>
       </c>
       <c r="X60" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y60" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z60" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA60" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB60" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC60" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD60" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE60" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF60" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG60" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH60" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI60" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ60" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK60" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL60" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM60" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN60" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO60" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP60" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY60" t="n">
         <v>9.4</v>
       </c>
-      <c r="AQ60" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR60" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS60" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT60" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU60" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV60" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW60" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX60" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY60" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AZ60" t="n">
-        <v>17</v>
+        <v>3.7</v>
       </c>
       <c r="BA60" t="n">
-        <v>48</v>
+        <v>4.1</v>
       </c>
       <c r="BB60" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BC60" t="n">
-        <v>18.5</v>
+        <v>3.75</v>
       </c>
       <c r="BD60" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="BE60" t="n">
-        <v>90</v>
+        <v>4.2</v>
       </c>
       <c r="BF60" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG60" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH60" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI60" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BJ60" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK60" t="n">
         <v>1.01</v>
       </c>
       <c r="BL60" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="BM60" t="n">
         <v>1.01</v>
       </c>
       <c r="BN60" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO60" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP60" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ60" t="n">
         <v>1.01</v>
       </c>
       <c r="BR60" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS60" t="n">
         <v>1.01</v>
       </c>
       <c r="BT60" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU60" t="n">
         <v>1.01</v>
       </c>
       <c r="BV60" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW60" t="n">
         <v>1.01</v>
       </c>
       <c r="BX60" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY60" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ60" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA60" t="n">
         <v>1.01</v>
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -15843,7 +15843,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="G61" t="n">
         <v>6.2</v>
@@ -15852,16 +15852,16 @@
         <v>1.78</v>
       </c>
       <c r="I61" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J61" t="n">
         <v>3.4</v>
       </c>
       <c r="K61" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L61" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M61" t="n">
         <v>1.08</v>
@@ -15873,22 +15873,22 @@
         <v>1.45</v>
       </c>
       <c r="P61" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.32</v>
+        <v>1.02</v>
       </c>
       <c r="R61" t="n">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="S61" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T61" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U61" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V61" t="n">
         <v>2.12</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="G64" t="n">
         <v>1000</v>
       </c>
       <c r="H64" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="I64" t="n">
         <v>1000</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -16862,16 +16862,16 @@
         <v>1.39</v>
       </c>
       <c r="G65" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="H65" t="n">
-        <v>8.4</v>
+        <v>2.24</v>
       </c>
       <c r="I65" t="n">
         <v>11.5</v>
       </c>
       <c r="J65" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K65" t="n">
         <v>5.6</v>
@@ -16886,7 +16886,7 @@
         <v>2.08</v>
       </c>
       <c r="O65" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P65" t="n">
         <v>2.06</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -17122,7 +17122,7 @@
         <v>2.58</v>
       </c>
       <c r="I66" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
         <v>3.15</v>
@@ -17131,13 +17131,13 @@
         <v>3.7</v>
       </c>
       <c r="L66" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M66" t="n">
         <v>1.01</v>
       </c>
       <c r="N66" t="n">
-        <v>1.79</v>
+        <v>2.82</v>
       </c>
       <c r="O66" t="n">
         <v>1.34</v>
@@ -17152,7 +17152,7 @@
         <v>1.18</v>
       </c>
       <c r="S66" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="T66" t="n">
         <v>1.01</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -17367,13 +17367,13 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="G67" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="H67" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I67" t="n">
         <v>7.8</v>
@@ -17382,43 +17382,43 @@
         <v>3.9</v>
       </c>
       <c r="K67" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L67" t="n">
         <v>1.01</v>
       </c>
       <c r="M67" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N67" t="n">
-        <v>1.84</v>
+        <v>3.1</v>
       </c>
       <c r="O67" t="n">
         <v>1.32</v>
       </c>
       <c r="P67" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R67" t="n">
         <v>1.14</v>
       </c>
       <c r="S67" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="T67" t="n">
         <v>1.01</v>
       </c>
       <c r="U67" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V67" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W67" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="X67" t="n">
         <v>1000</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -17639,202 +17639,202 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="P68" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ68" t="n">
         <v>0</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -17875,230 +17875,230 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P69" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI69" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AK69" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL69" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM69" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN69" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AO69" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AP69" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AS69" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AT69" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU69" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV69" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AW69" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AX69" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY69" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ69" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA69" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BB69" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC69" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE69" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF69" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG69" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BH69" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BI69" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BJ69" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK69" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BL69" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="BM69" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN69" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BO69" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BP69" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BQ69" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BR69" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BS69" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BT69" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU69" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BV69" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BW69" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BX69" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BY69" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BZ69" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="CA69" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -18129,230 +18129,230 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P70" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK70" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL70" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP70" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR70" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AS70" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT70" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU70" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV70" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW70" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AX70" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AY70" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AZ70" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BA70" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BB70" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BC70" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BD70" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BE70" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BF70" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BG70" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BH70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -18398,7 +18398,7 @@
         <v>4.7</v>
       </c>
       <c r="K71" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-18.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="G2" t="n">
         <v>1.76</v>
@@ -866,13 +866,13 @@
         <v>5.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
         <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -884,22 +884,22 @@
         <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
         <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S2" t="n">
         <v>2.86</v>
       </c>
       <c r="T2" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="U2" t="n">
         <v>1.98</v>
@@ -914,7 +914,7 @@
         <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z2" t="n">
         <v>55</v>
@@ -929,13 +929,13 @@
         <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
         <v>80</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -947,19 +947,19 @@
         <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AO2" t="n">
         <v>75</v>
@@ -971,22 +971,22 @@
         <v>17.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="AT2" t="n">
         <v>8.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2" t="n">
         <v>17.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX2" t="n">
         <v>9.4</v>
@@ -995,28 +995,28 @@
         <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
         <v>14.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BF2" t="n">
         <v>6.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1040,7 +1040,7 @@
         <v>5.9</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
         <v>15</v>
@@ -1073,14 +1073,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA2" t="n">
         <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -1120,13 +1120,13 @@
         <v>2.5</v>
       </c>
       <c r="I3" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.32</v>
@@ -1135,7 +1135,7 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.29</v>
@@ -1144,28 +1144,28 @@
         <v>1.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="U3" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="V3" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y3" t="n">
         <v>14</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>3.45</v>
       </c>
       <c r="H4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I4" t="n">
         <v>2.6</v>
@@ -1389,16 +1389,16 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R4" t="n">
         <v>1.32</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G5" t="n">
         <v>3.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I5" t="n">
         <v>2.6</v>
@@ -1643,22 +1643,22 @@
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.78</v>
+        <v>1.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P5" t="n">
         <v>1.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1802,7 +1802,7 @@
         <v>8.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BP5" t="n">
         <v>38</v>
@@ -1820,7 +1820,7 @@
         <v>7</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BV5" t="n">
         <v>28</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -1876,16 +1876,16 @@
         <v>2.9</v>
       </c>
       <c r="G6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H6" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I6" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
         <v>4.2</v>
@@ -1894,7 +1894,7 @@
         <v>1.29</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
         <v>4.5</v>
@@ -1903,28 +1903,28 @@
         <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="R6" t="n">
         <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="U6" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="V6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X6" t="n">
         <v>23</v>
@@ -1945,16 +1945,16 @@
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AF6" t="n">
         <v>27</v>
       </c>
       <c r="AG6" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
         <v>18</v>
@@ -1963,22 +1963,22 @@
         <v>34</v>
       </c>
       <c r="AJ6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL6" t="n">
         <v>44</v>
       </c>
       <c r="AM6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AO6" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
@@ -1987,22 +1987,22 @@
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT6" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
         <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
         <v>20</v>
@@ -2017,19 +2017,19 @@
         <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BC6" t="n">
         <v>23</v>
       </c>
       <c r="BD6" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BE6" t="n">
         <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG6" t="n">
         <v>12.5</v>
@@ -2038,19 +2038,19 @@
         <v>4.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ6" t="n">
         <v>10</v>
       </c>
       <c r="BK6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BL6" t="n">
         <v>100</v>
       </c>
       <c r="BM6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BN6" t="n">
         <v>7.4</v>
@@ -2077,7 +2077,7 @@
         <v>4.4</v>
       </c>
       <c r="BV6" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BW6" t="n">
         <v>4.3</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H7" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I7" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.35</v>
@@ -2151,22 +2151,22 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
         <v>1.32</v>
       </c>
       <c r="P7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="R7" t="n">
         <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
         <v>1.75</v>
@@ -2175,7 +2175,7 @@
         <v>2.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
         <v>1.6</v>
@@ -2187,7 +2187,7 @@
         <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
         <v>50</v>
@@ -2205,13 +2205,13 @@
         <v>34</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AI7" t="n">
         <v>44</v>
@@ -2220,7 +2220,7 @@
         <v>38</v>
       </c>
       <c r="AK7" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL7" t="n">
         <v>40</v>
@@ -2232,22 +2232,22 @@
         <v>23</v>
       </c>
       <c r="AO7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>7.4</v>
+        <v>16.5</v>
       </c>
       <c r="AS7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
         <v>7.2</v>
@@ -2274,7 +2274,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD7" t="n">
         <v>8.800000000000001</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -2384,49 +2384,49 @@
         <v>3.3</v>
       </c>
       <c r="G8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H8" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I8" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.5</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U8" t="n">
         <v>1.94</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.92</v>
       </c>
       <c r="V8" t="n">
         <v>1.64</v>
@@ -2495,10 +2495,10 @@
         <v>7.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT8" t="n">
         <v>9.6</v>
@@ -2510,34 +2510,34 @@
         <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BC8" t="n">
         <v>38</v>
       </c>
       <c r="BD8" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BG8" t="n">
         <v>21</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>3.1</v>
       </c>
       <c r="G9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H9" t="n">
         <v>2.58</v>
@@ -2647,40 +2647,40 @@
         <v>2.76</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L9" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
         <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="O9" t="n">
         <v>1.51</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V9" t="n">
         <v>1.57</v>
@@ -2689,19 +2689,19 @@
         <v>1.42</v>
       </c>
       <c r="X9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y9" t="n">
         <v>8.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA9" t="n">
         <v>55</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC9" t="n">
         <v>7.4</v>
@@ -2710,7 +2710,7 @@
         <v>13.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF9" t="n">
         <v>21</v>
@@ -2722,7 +2722,7 @@
         <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ9" t="n">
         <v>75</v>
@@ -2731,7 +2731,7 @@
         <v>60</v>
       </c>
       <c r="AL9" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM9" t="n">
         <v>200</v>
@@ -2740,7 +2740,7 @@
         <v>75</v>
       </c>
       <c r="AO9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP9" t="n">
         <v>8.199999999999999</v>
@@ -2752,7 +2752,7 @@
         <v>13.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>32</v>
+        <v>7.4</v>
       </c>
       <c r="AT9" t="n">
         <v>8.4</v>
@@ -2764,7 +2764,7 @@
         <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX9" t="n">
         <v>17</v>
@@ -2776,89 +2776,89 @@
         <v>18.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>36</v>
+        <v>7.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BE9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG9" t="n">
         <v>7.4</v>
       </c>
-      <c r="BF9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH9" t="n">
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.49</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.59</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G10" t="n">
         <v>1.97</v>
@@ -2898,25 +2898,25 @@
         <v>4.5</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
         <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P10" t="n">
         <v>1.86</v>
@@ -2925,10 +2925,10 @@
         <v>2.02</v>
       </c>
       <c r="R10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T10" t="n">
         <v>1.89</v>
@@ -2943,10 +2943,10 @@
         <v>2.02</v>
       </c>
       <c r="X10" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="Z10" t="n">
         <v>44</v>
@@ -2955,7 +2955,7 @@
         <v>140</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC10" t="n">
         <v>8.4</v>
@@ -2967,19 +2967,19 @@
         <v>80</v>
       </c>
       <c r="AF10" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI10" t="n">
         <v>90</v>
       </c>
       <c r="AJ10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK10" t="n">
         <v>26</v>
@@ -2991,22 +2991,22 @@
         <v>150</v>
       </c>
       <c r="AN10" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AO10" t="n">
         <v>100</v>
       </c>
       <c r="AP10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AT10" t="n">
         <v>7.4</v>
@@ -3015,10 +3015,10 @@
         <v>7.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3027,10 +3027,10 @@
         <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB10" t="n">
         <v>18</v>
@@ -3039,16 +3039,16 @@
         <v>17.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BF10" t="n">
         <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH10" t="n">
         <v>3.8</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G11" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="I11" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J11" t="n">
         <v>3.65</v>
@@ -3164,37 +3164,37 @@
         <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
         <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R11" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S11" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U11" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X11" t="n">
         <v>24</v>
@@ -3203,28 +3203,28 @@
         <v>14</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
         <v>42</v>
       </c>
       <c r="AB11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC11" t="n">
         <v>9.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF11" t="n">
         <v>27</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
         <v>16</v>
@@ -3233,19 +3233,19 @@
         <v>40</v>
       </c>
       <c r="AJ11" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AK11" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AL11" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM11" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AN11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AO11" t="n">
         <v>16</v>
@@ -3254,13 +3254,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AR11" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="AT11" t="n">
         <v>13</v>
@@ -3269,40 +3269,40 @@
         <v>7.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>13</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BH11" t="n">
         <v>4.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -3427,10 +3427,10 @@
         <v>1.28</v>
       </c>
       <c r="P12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="R12" t="n">
         <v>1.39</v>
@@ -3439,13 +3439,13 @@
         <v>3.15</v>
       </c>
       <c r="T12" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U12" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
         <v>1.66</v>
@@ -3454,7 +3454,7 @@
         <v>19</v>
       </c>
       <c r="Y12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z12" t="n">
         <v>26</v>
@@ -3466,7 +3466,7 @@
         <v>13.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
         <v>14.5</v>
@@ -3487,7 +3487,7 @@
         <v>48</v>
       </c>
       <c r="AJ12" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK12" t="n">
         <v>30</v>
@@ -3514,7 +3514,7 @@
         <v>17</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT12" t="n">
         <v>9</v>
@@ -3526,7 +3526,7 @@
         <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX12" t="n">
         <v>12.5</v>
@@ -3538,19 +3538,19 @@
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB12" t="n">
         <v>5</v>
       </c>
-      <c r="BB12" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BC12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF12" t="n">
         <v>14</v>
@@ -3568,13 +3568,13 @@
         <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="BL12" t="n">
         <v>120</v>
       </c>
       <c r="BM12" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BN12" t="n">
         <v>6.2</v>
@@ -3583,19 +3583,19 @@
         <v>4.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BR12" t="n">
         <v>34</v>
       </c>
       <c r="BS12" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BT12" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU12" t="n">
         <v>5</v>
@@ -3604,23 +3604,23 @@
         <v>27</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BX12" t="n">
         <v>38</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BZ12" t="n">
         <v>27</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -3693,10 +3693,10 @@
         <v>3.15</v>
       </c>
       <c r="T13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.83</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.99</v>
       </c>
       <c r="V13" t="n">
         <v>1.8</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
         <v>1.69</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V14" t="n">
         <v>1.7</v>
@@ -3971,25 +3971,25 @@
         <v>36</v>
       </c>
       <c r="AB14" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AF14" t="n">
         <v>28</v>
       </c>
       <c r="AG14" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI14" t="n">
         <v>36</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>2.22</v>
       </c>
       <c r="G15" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H15" t="n">
         <v>3.3</v>
@@ -4210,7 +4210,7 @@
         <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X15" t="n">
         <v>13.5</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -4413,16 +4413,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="G16" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="H16" t="n">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="I16" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>4.1</v>
@@ -4446,31 +4446,31 @@
         <v>2.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="R16" t="n">
         <v>1.72</v>
       </c>
       <c r="S16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T16" t="n">
         <v>1.48</v>
       </c>
       <c r="U16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V16" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="X16" t="n">
         <v>36</v>
       </c>
       <c r="Y16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z16" t="n">
         <v>34</v>
@@ -4485,7 +4485,7 @@
         <v>13</v>
       </c>
       <c r="AD16" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE16" t="n">
         <v>34</v>
@@ -4518,19 +4518,19 @@
         <v>12.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR16" t="n">
         <v>19</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AT16" t="n">
         <v>15</v>
@@ -4554,19 +4554,19 @@
         <v>10.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BB16" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BC16" t="n">
         <v>18</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BF16" t="n">
         <v>9</v>
@@ -4578,13 +4578,13 @@
         <v>5.6</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BJ16" t="n">
         <v>10</v>
       </c>
       <c r="BK16" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BL16" t="n">
         <v>80</v>
@@ -4599,7 +4599,7 @@
         <v>4.5</v>
       </c>
       <c r="BP16" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ16" t="n">
         <v>3.7</v>
@@ -4608,19 +4608,19 @@
         <v>26</v>
       </c>
       <c r="BS16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BT16" t="n">
         <v>8</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV16" t="n">
         <v>24</v>
       </c>
       <c r="BW16" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BX16" t="n">
         <v>30</v>
@@ -4629,14 +4629,14 @@
         <v>4</v>
       </c>
       <c r="BZ16" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="CA16" t="n">
         <v>3.65</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -4667,16 +4667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="G17" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I17" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J17" t="n">
         <v>4.9</v>
@@ -4697,28 +4697,28 @@
         <v>1.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R17" t="n">
         <v>1.65</v>
       </c>
       <c r="S17" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T17" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U17" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V17" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W17" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="X17" t="n">
         <v>29</v>
@@ -4733,10 +4733,10 @@
         <v>230</v>
       </c>
       <c r="AB17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC17" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>13</v>
       </c>
       <c r="AD17" t="n">
         <v>28</v>
@@ -4751,13 +4751,13 @@
         <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI17" t="n">
         <v>100</v>
       </c>
       <c r="AJ17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK17" t="n">
         <v>15</v>
@@ -4769,7 +4769,7 @@
         <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AO17" t="n">
         <v>100</v>
@@ -4781,10 +4781,10 @@
         <v>23</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AT17" t="n">
         <v>10</v>
@@ -4796,7 +4796,7 @@
         <v>20</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX17" t="n">
         <v>9.4</v>
@@ -4808,7 +4808,7 @@
         <v>17.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB17" t="n">
         <v>12</v>
@@ -4820,13 +4820,13 @@
         <v>21</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF17" t="n">
         <v>4.7</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH17" t="n">
         <v>5.4</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -4921,16 +4921,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H18" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I18" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="J18" t="n">
         <v>3.3</v>
@@ -4954,7 +4954,7 @@
         <v>1.78</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R18" t="n">
         <v>1.3</v>
@@ -4969,7 +4969,7 @@
         <v>2.04</v>
       </c>
       <c r="V18" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W18" t="n">
         <v>1.29</v>
@@ -4978,7 +4978,7 @@
         <v>14.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="Z18" t="n">
         <v>17.5</v>
@@ -4987,10 +4987,10 @@
         <v>38</v>
       </c>
       <c r="AB18" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AD18" t="n">
         <v>14</v>
@@ -5002,7 +5002,7 @@
         <v>32</v>
       </c>
       <c r="AG18" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH18" t="n">
         <v>22</v>
@@ -5011,7 +5011,7 @@
         <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK18" t="n">
         <v>60</v>
@@ -5023,22 +5023,22 @@
         <v>130</v>
       </c>
       <c r="AN18" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AO18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP18" t="n">
         <v>10</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR18" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="AT18" t="n">
         <v>10.5</v>
@@ -5047,46 +5047,46 @@
         <v>6.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>19.5</v>
+        <v>3.8</v>
       </c>
       <c r="AX18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ18" t="n">
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BE18" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BG18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BH18" t="n">
         <v>3.7</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ18" t="n">
         <v>12</v>
@@ -5101,7 +5101,7 @@
         <v>4.7</v>
       </c>
       <c r="BN18" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BO18" t="n">
         <v>5.1</v>
@@ -5116,7 +5116,7 @@
         <v>55</v>
       </c>
       <c r="BS18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT18" t="n">
         <v>5.9</v>
@@ -5128,7 +5128,7 @@
         <v>21</v>
       </c>
       <c r="BW18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BX18" t="n">
         <v>40</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -5441,13 +5441,13 @@
         <v>3.45</v>
       </c>
       <c r="J20" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
         <v>4.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -5462,19 +5462,19 @@
         <v>2.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
         <v>2.82</v>
       </c>
       <c r="T20" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="U20" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="V20" t="n">
         <v>1.41</v>
@@ -5591,68 +5591,68 @@
         <v>20</v>
       </c>
       <c r="BH20" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BI20" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ20" t="n">
         <v>11</v>
       </c>
       <c r="BK20" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BL20" t="n">
         <v>110</v>
       </c>
       <c r="BM20" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BN20" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BR20" t="n">
         <v>32</v>
       </c>
       <c r="BS20" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BT20" t="n">
         <v>7.8</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BW20" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BX20" t="n">
         <v>38</v>
       </c>
       <c r="BY20" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BZ20" t="n">
         <v>25</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -5725,10 +5725,10 @@
         <v>3.7</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>1.37</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
         <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H22" t="n">
         <v>3.65</v>
@@ -5952,7 +5952,7 @@
         <v>4.1</v>
       </c>
       <c r="K22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L22" t="n">
         <v>1.3</v>
@@ -5970,7 +5970,7 @@
         <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="R22" t="n">
         <v>1.56</v>
@@ -5985,10 +5985,10 @@
         <v>2.44</v>
       </c>
       <c r="V22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X22" t="n">
         <v>28</v>
@@ -6108,22 +6108,22 @@
         <v>10.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BL22" t="n">
         <v>100</v>
       </c>
       <c r="BM22" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BN22" t="n">
         <v>6</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP22" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ22" t="n">
         <v>3.6</v>
@@ -6132,7 +6132,7 @@
         <v>27</v>
       </c>
       <c r="BS22" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BT22" t="n">
         <v>9</v>
@@ -6153,14 +6153,14 @@
         <v>4.2</v>
       </c>
       <c r="BZ22" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="CA22" t="n">
         <v>3.8</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
         <v>1.25</v>
       </c>
       <c r="O23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P23" t="n">
         <v>1.25</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6705,7 @@
         <v>2.82</v>
       </c>
       <c r="H25" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I25" t="n">
         <v>2.74</v>
@@ -6732,7 +6732,7 @@
         <v>2.02</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R25" t="n">
         <v>1.4</v>
@@ -6741,7 +6741,7 @@
         <v>3.25</v>
       </c>
       <c r="T25" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U25" t="n">
         <v>2.24</v>
@@ -6753,13 +6753,13 @@
         <v>1.54</v>
       </c>
       <c r="X25" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z25" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AA25" t="n">
         <v>50</v>
@@ -6771,19 +6771,19 @@
         <v>8.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AE25" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF25" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AG25" t="n">
         <v>15.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
         <v>48</v>
@@ -6795,34 +6795,34 @@
         <v>36</v>
       </c>
       <c r="AL25" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM25" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN25" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AO25" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AP25" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="AT25" t="n">
         <v>10.5</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV25" t="n">
         <v>11</v>
@@ -6831,31 +6831,31 @@
         <v>21</v>
       </c>
       <c r="AX25" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AY25" t="n">
         <v>11</v>
       </c>
       <c r="AZ25" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB25" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="BC25" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF25" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BG25" t="n">
         <v>17</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
         <v>3.9</v>
       </c>
       <c r="L26" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
@@ -7004,7 +7004,7 @@
         <v>1.35</v>
       </c>
       <c r="W26" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X26" t="n">
         <v>19.5</v>
@@ -7058,7 +7058,7 @@
         <v>18</v>
       </c>
       <c r="AO26" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AP26" t="n">
         <v>13.5</v>
@@ -7070,7 +7070,7 @@
         <v>19.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT26" t="n">
         <v>9.199999999999999</v>
@@ -7094,7 +7094,7 @@
         <v>14</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB26" t="n">
         <v>19.5</v>
@@ -7103,10 +7103,10 @@
         <v>19</v>
       </c>
       <c r="BD26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF26" t="n">
         <v>11</v>
@@ -7115,16 +7115,16 @@
         <v>4</v>
       </c>
       <c r="BH26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI26" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK26" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BL26" t="n">
         <v>130</v>
@@ -7169,14 +7169,14 @@
         <v>4.2</v>
       </c>
       <c r="BZ26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA26" t="n">
         <v>4</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
         <v>2.22</v>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="J27" t="n">
         <v>3.55</v>
@@ -7231,7 +7231,7 @@
         <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="O27" t="n">
         <v>1.27</v>
@@ -7246,22 +7246,22 @@
         <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="T27" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U27" t="n">
         <v>2.26</v>
       </c>
       <c r="V27" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="W27" t="n">
         <v>1.4</v>
       </c>
       <c r="X27" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="Y27" t="n">
         <v>12</v>
@@ -7270,10 +7270,10 @@
         <v>16.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AB27" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AC27" t="n">
         <v>8.6</v>
@@ -7282,16 +7282,16 @@
         <v>11.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AF27" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AG27" t="n">
         <v>14.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AI27" t="n">
         <v>42</v>
@@ -7315,58 +7315,58 @@
         <v>16.5</v>
       </c>
       <c r="AP27" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AR27" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV27" t="n">
         <v>4.9</v>
       </c>
-      <c r="AU27" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AW27" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX27" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AY27" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BA27" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC27" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BD27" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG27" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BH27" t="n">
         <v>3.7</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
         <v>2.24</v>
       </c>
       <c r="G28" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H28" t="n">
         <v>3.25</v>
@@ -7479,7 +7479,7 @@
         <v>3.8</v>
       </c>
       <c r="L28" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
         <v>1.06</v>
@@ -7494,13 +7494,13 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T28" t="n">
         <v>1.73</v>
@@ -7518,7 +7518,7 @@
         <v>15.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z28" t="n">
         <v>25</v>
@@ -7545,25 +7545,25 @@
         <v>11.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ28" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK28" t="n">
         <v>25</v>
       </c>
       <c r="AL28" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM28" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN28" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO28" t="n">
         <v>36</v>
@@ -7578,7 +7578,7 @@
         <v>21</v>
       </c>
       <c r="AS28" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AT28" t="n">
         <v>9.4</v>
@@ -7590,7 +7590,7 @@
         <v>12.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AX28" t="n">
         <v>13.5</v>
@@ -7602,31 +7602,31 @@
         <v>14.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>36</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB28" t="n">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC28" t="n">
         <v>21</v>
       </c>
       <c r="BD28" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BE28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF28" t="n">
         <v>15.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BJ28" t="n">
         <v>13</v>
@@ -7638,13 +7638,13 @@
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BN28" t="n">
         <v>7</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP28" t="n">
         <v>23</v>
@@ -7665,7 +7665,7 @@
         <v>4.5</v>
       </c>
       <c r="BV28" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW28" t="n">
         <v>1.81</v>
@@ -7674,7 +7674,7 @@
         <v>50</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G29" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H29" t="n">
         <v>2.2</v>
@@ -7727,13 +7727,13 @@
         <v>2.36</v>
       </c>
       <c r="J29" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K29" t="n">
         <v>4.2</v>
       </c>
       <c r="L29" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="M29" t="n">
         <v>1.04</v>
@@ -7748,7 +7748,7 @@
         <v>2.36</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R29" t="n">
         <v>1.55</v>
@@ -7808,10 +7808,10 @@
         <v>65</v>
       </c>
       <c r="AK29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL29" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM29" t="n">
         <v>75</v>
@@ -7826,13 +7826,13 @@
         <v>19</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR29" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AS29" t="n">
-        <v>21</v>
+        <v>3.85</v>
       </c>
       <c r="AT29" t="n">
         <v>15</v>
@@ -7844,19 +7844,19 @@
         <v>10</v>
       </c>
       <c r="AW29" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AX29" t="n">
         <v>3.8</v>
       </c>
       <c r="AY29" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA29" t="n">
-        <v>21</v>
+        <v>3.85</v>
       </c>
       <c r="BB29" t="n">
         <v>4</v>
@@ -7868,10 +7868,10 @@
         <v>3.95</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BF29" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG29" t="n">
         <v>11</v>
@@ -7883,62 +7883,62 @@
         <v>3.25</v>
       </c>
       <c r="BJ29" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BK29" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="BL29" t="n">
         <v>95</v>
       </c>
       <c r="BM29" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="BN29" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BO29" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BP29" t="n">
         <v>27</v>
       </c>
       <c r="BQ29" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BR29" t="n">
         <v>36</v>
       </c>
       <c r="BS29" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BT29" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU29" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BV29" t="n">
         <v>18.5</v>
       </c>
       <c r="BW29" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BX29" t="n">
         <v>29</v>
       </c>
       <c r="BY29" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BZ29" t="n">
         <v>21</v>
       </c>
       <c r="CA29" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -7993,13 +7993,13 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O30" t="n">
         <v>1.37</v>
       </c>
       <c r="P30" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q30" t="n">
         <v>1.37</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8552,7 @@
         <v>23</v>
       </c>
       <c r="AE32" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF32" t="n">
         <v>13.5</v>
@@ -8591,7 +8591,7 @@
         <v>17</v>
       </c>
       <c r="AR32" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS32" t="n">
         <v>5.4</v>
@@ -8630,7 +8630,7 @@
         <v>4.9</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF32" t="n">
         <v>7</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -8800,7 +8800,7 @@
         <v>19</v>
       </c>
       <c r="AC33" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD33" t="n">
         <v>13.5</v>
@@ -8821,7 +8821,7 @@
         <v>34</v>
       </c>
       <c r="AJ33" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK33" t="n">
         <v>38</v>
@@ -8848,7 +8848,7 @@
         <v>12.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT33" t="n">
         <v>12.5</v>
@@ -8872,19 +8872,19 @@
         <v>12</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB33" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC33" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC33" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BD33" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF33" t="n">
         <v>18</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -8988,16 +8988,16 @@
         <v>2.92</v>
       </c>
       <c r="G34" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="H34" t="n">
         <v>2.54</v>
       </c>
       <c r="I34" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="J34" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="K34" t="n">
         <v>3.4</v>
@@ -9009,7 +9009,7 @@
         <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="O34" t="n">
         <v>1.46</v>
@@ -9018,13 +9018,13 @@
         <v>1.58</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="R34" t="n">
         <v>1.21</v>
       </c>
       <c r="S34" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="T34" t="n">
         <v>1.94</v>
@@ -9033,10 +9033,10 @@
         <v>1.84</v>
       </c>
       <c r="V34" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W34" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X34" t="n">
         <v>11.5</v>
@@ -9147,46 +9147,46 @@
         <v>1.01</v>
       </c>
       <c r="BH34" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI34" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BJ34" t="n">
         <v>13</v>
       </c>
       <c r="BK34" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BL34" t="n">
         <v>210</v>
       </c>
       <c r="BM34" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BN34" t="n">
         <v>7.2</v>
       </c>
       <c r="BO34" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BP34" t="n">
         <v>34</v>
       </c>
       <c r="BQ34" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BR34" t="n">
         <v>60</v>
       </c>
       <c r="BS34" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BT34" t="n">
         <v>6.6</v>
       </c>
       <c r="BU34" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BV34" t="n">
         <v>29</v>
@@ -9198,17 +9198,17 @@
         <v>55</v>
       </c>
       <c r="BY34" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BZ34" t="n">
         <v>55</v>
       </c>
       <c r="CA34" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -9239,13 +9239,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="G35" t="n">
         <v>1000</v>
       </c>
       <c r="H35" t="n">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="I35" t="n">
         <v>1000</v>
@@ -9260,25 +9260,25 @@
         <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N35" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="O35" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="P35" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R35" t="n">
         <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>1.46</v>
+        <v>1.05</v>
       </c>
       <c r="T35" t="n">
         <v>1.11</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -9526,13 +9526,13 @@
         <v>2.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="R36" t="n">
         <v>1.69</v>
       </c>
       <c r="S36" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="T36" t="n">
         <v>1.51</v>
@@ -9547,40 +9547,40 @@
         <v>1.76</v>
       </c>
       <c r="X36" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Y36" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z36" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AA36" t="n">
         <v>55</v>
       </c>
       <c r="AB36" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AC36" t="n">
         <v>10.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE36" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI36" t="n">
         <v>32</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>34</v>
       </c>
       <c r="AJ36" t="n">
         <v>32</v>
@@ -9589,43 +9589,43 @@
         <v>21</v>
       </c>
       <c r="AL36" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM36" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN36" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO36" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AP36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ36" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="AS36" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU36" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV36" t="n">
         <v>14</v>
       </c>
       <c r="AW36" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AX36" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY36" t="n">
         <v>11</v>
@@ -9634,31 +9634,31 @@
         <v>13</v>
       </c>
       <c r="BA36" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB36" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BC36" t="n">
         <v>18</v>
       </c>
       <c r="BD36" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BE36" t="n">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="BF36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG36" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH36" t="n">
         <v>1000</v>
       </c>
       <c r="BI36" t="n">
-        <v>1.56</v>
+        <v>2.08</v>
       </c>
       <c r="BJ36" t="n">
         <v>11.5</v>
@@ -9670,25 +9670,25 @@
         <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>1.56</v>
+        <v>2.08</v>
       </c>
       <c r="BN36" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO36" t="n">
-        <v>1.56</v>
+        <v>4.1</v>
       </c>
       <c r="BP36" t="n">
         <v>20</v>
       </c>
       <c r="BQ36" t="n">
-        <v>1.45</v>
+        <v>1.89</v>
       </c>
       <c r="BR36" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS36" t="n">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="BT36" t="n">
         <v>9.6</v>
@@ -9700,23 +9700,23 @@
         <v>29</v>
       </c>
       <c r="BW36" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="BX36" t="n">
         <v>34</v>
       </c>
       <c r="BY36" t="n">
-        <v>1.49</v>
+        <v>1.97</v>
       </c>
       <c r="BZ36" t="n">
         <v>18.5</v>
       </c>
       <c r="CA36" t="n">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
         <v>1.76</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R37" t="n">
         <v>1.29</v>
@@ -9864,7 +9864,7 @@
         <v>9.6</v>
       </c>
       <c r="AS37" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AT37" t="n">
         <v>11</v>
@@ -9885,10 +9885,10 @@
         <v>14</v>
       </c>
       <c r="AZ37" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB37" t="n">
         <v>1.01</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -10166,19 +10166,19 @@
         <v>1000</v>
       </c>
       <c r="BI38" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="BJ38" t="n">
         <v>14.5</v>
       </c>
       <c r="BK38" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="BN38" t="n">
         <v>9</v>
@@ -10190,10 +10190,10 @@
         <v>44</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="BR38" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS38" t="n">
         <v>1.7</v>
@@ -10208,23 +10208,23 @@
         <v>29</v>
       </c>
       <c r="BW38" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="BX38" t="n">
         <v>50</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="BZ38" t="n">
         <v>50</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
         <v>2.98</v>
       </c>
       <c r="G39" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="H39" t="n">
         <v>2.34</v>
@@ -10267,7 +10267,7 @@
         <v>2.68</v>
       </c>
       <c r="J39" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K39" t="n">
         <v>3.75</v>
@@ -10306,7 +10306,7 @@
         <v>1.59</v>
       </c>
       <c r="W39" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
         <v>3.2</v>
       </c>
       <c r="I40" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J40" t="n">
         <v>3.95</v>
@@ -10539,31 +10539,31 @@
         <v>1.19</v>
       </c>
       <c r="P40" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q40" t="n">
         <v>1.57</v>
       </c>
       <c r="R40" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S40" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T40" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U40" t="n">
         <v>2.58</v>
       </c>
       <c r="V40" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W40" t="n">
         <v>1.8</v>
       </c>
       <c r="X40" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y40" t="n">
         <v>23</v>
@@ -10572,19 +10572,19 @@
         <v>34</v>
       </c>
       <c r="AA40" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB40" t="n">
         <v>17.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE40" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF40" t="n">
         <v>21</v>
@@ -10593,10 +10593,10 @@
         <v>14</v>
       </c>
       <c r="AH40" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI40" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ40" t="n">
         <v>34</v>
@@ -10617,58 +10617,58 @@
         <v>26</v>
       </c>
       <c r="AP40" t="n">
-        <v>21</v>
+        <v>3.75</v>
       </c>
       <c r="AQ40" t="n">
         <v>16.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>20</v>
+        <v>3.8</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AT40" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU40" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV40" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AW40" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AX40" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY40" t="n">
         <v>10</v>
       </c>
       <c r="AZ40" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BA40" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE40" t="n">
         <v>4</v>
       </c>
-      <c r="BB40" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF40" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG40" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BH40" t="n">
         <v>1000</v>
@@ -10692,7 +10692,7 @@
         <v>7.4</v>
       </c>
       <c r="BO40" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BP40" t="n">
         <v>19.5</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -10808,7 +10808,7 @@
         <v>1.81</v>
       </c>
       <c r="U41" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="V41" t="n">
         <v>1.01</v>
@@ -10928,65 +10928,65 @@
         <v>1000</v>
       </c>
       <c r="BI41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ41" t="n">
         <v>1000</v>
       </c>
       <c r="BK41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN41" t="n">
         <v>1000</v>
       </c>
       <c r="BO41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP41" t="n">
         <v>1000</v>
       </c>
       <c r="BQ41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR41" t="n">
         <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT41" t="n">
         <v>1000</v>
       </c>
       <c r="BU41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV41" t="n">
         <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ41" t="n">
         <v>1000</v>
       </c>
       <c r="CA41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -11023,13 +11023,13 @@
         <v>1.28</v>
       </c>
       <c r="H42" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K42" t="n">
         <v>9.199999999999999</v>
@@ -11041,37 +11041,37 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>2.92</v>
+        <v>1.1</v>
       </c>
       <c r="O42" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P42" t="n">
         <v>2.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="R42" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S42" t="n">
         <v>2.26</v>
       </c>
       <c r="T42" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="U42" t="n">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="V42" t="n">
         <v>1.05</v>
       </c>
       <c r="W42" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y42" t="n">
         <v>1000</v>
@@ -11110,7 +11110,7 @@
         <v>1000</v>
       </c>
       <c r="AK42" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL42" t="n">
         <v>1000</v>
@@ -11119,7 +11119,7 @@
         <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="AO42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
         <v>2.22</v>
       </c>
       <c r="G43" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="H43" t="n">
         <v>3.55</v>
@@ -11289,7 +11289,7 @@
         <v>3.5</v>
       </c>
       <c r="L43" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M43" t="n">
         <v>1.1</v>
@@ -11298,31 +11298,31 @@
         <v>2.8</v>
       </c>
       <c r="O43" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P43" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R43" t="n">
         <v>1.2</v>
       </c>
       <c r="S43" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T43" t="n">
         <v>1.84</v>
       </c>
       <c r="U43" t="n">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="V43" t="n">
         <v>1.32</v>
       </c>
       <c r="W43" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -11337,7 +11337,7 @@
         <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC43" t="n">
         <v>1000</v>
@@ -11358,7 +11358,7 @@
         <v>1000</v>
       </c>
       <c r="AI43" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ43" t="n">
         <v>1000</v>
@@ -11379,122 +11379,122 @@
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AT43" t="n">
         <v>1.01</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BH43" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI43" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ43" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK43" t="n">
         <v>1.04</v>
       </c>
       <c r="BL43" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="BM43" t="n">
         <v>1.04</v>
       </c>
       <c r="BN43" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO43" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP43" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ43" t="n">
         <v>1.04</v>
       </c>
       <c r="BR43" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS43" t="n">
         <v>1.04</v>
       </c>
       <c r="BT43" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU43" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV43" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW43" t="n">
         <v>1.04</v>
       </c>
       <c r="BX43" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY43" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ43" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA43" t="n">
         <v>1.04</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
         <v>17.5</v>
       </c>
       <c r="G44" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H44" t="n">
         <v>1.14</v>
@@ -11537,19 +11537,19 @@
         <v>1.19</v>
       </c>
       <c r="J44" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K44" t="n">
         <v>12.5</v>
       </c>
       <c r="L44" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="M44" t="n">
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="O44" t="n">
         <v>1.06</v>
@@ -11558,19 +11558,19 @@
         <v>4.9</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="R44" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="S44" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="T44" t="n">
         <v>1.72</v>
       </c>
       <c r="U44" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V44" t="n">
         <v>6.2</v>
@@ -11579,40 +11579,40 @@
         <v>1.04</v>
       </c>
       <c r="X44" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Y44" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Z44" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AB44" t="n">
         <v>120</v>
       </c>
       <c r="AC44" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AD44" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE44" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE44" t="n">
-        <v>14</v>
-      </c>
       <c r="AF44" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AG44" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AH44" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AI44" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ44" t="n">
         <v>1000</v>
@@ -11624,16 +11624,16 @@
         <v>160</v>
       </c>
       <c r="AM44" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN44" t="n">
         <v>200</v>
       </c>
       <c r="AO44" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AP44" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AQ44" t="n">
         <v>17.5</v>
@@ -11645,88 +11645,88 @@
         <v>9</v>
       </c>
       <c r="AT44" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="AU44" t="n">
-        <v>22</v>
+        <v>5.4</v>
       </c>
       <c r="AV44" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW44" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX44" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY44" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="AZ44" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="BA44" t="n">
-        <v>23</v>
+        <v>5.4</v>
       </c>
       <c r="BB44" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="BC44" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD44" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE44" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BF44" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG44" t="n">
         <v>2.04</v>
       </c>
       <c r="BH44" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BI44" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BJ44" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK44" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL44" t="n">
         <v>1000</v>
       </c>
       <c r="BM44" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN44" t="n">
         <v>21</v>
       </c>
       <c r="BO44" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BP44" t="n">
         <v>1000</v>
       </c>
       <c r="BQ44" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS44" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BR44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS44" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BT44" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BU44" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV44" t="n">
         <v>6.4</v>
@@ -11735,20 +11735,20 @@
         <v>4.8</v>
       </c>
       <c r="BX44" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BY44" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ44" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="CA44" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11785,7 @@
         <v>1.26</v>
       </c>
       <c r="H45" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="I45" t="n">
         <v>18.5</v>
@@ -11830,7 +11830,7 @@
         <v>1.05</v>
       </c>
       <c r="W45" t="n">
-        <v>4.8</v>
+        <v>2.38</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -12039,7 +12039,7 @@
         <v>4.2</v>
       </c>
       <c r="H46" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I46" t="n">
         <v>2.42</v>
@@ -12162,7 +12162,7 @@
         <v>10</v>
       </c>
       <c r="AW46" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX46" t="n">
         <v>5.2</v>
@@ -12174,10 +12174,10 @@
         <v>17</v>
       </c>
       <c r="BA46" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB46" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BC46" t="n">
         <v>5.7</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -12311,7 +12311,7 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O47" t="n">
         <v>1.09</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12556,7 @@
         <v>2.9</v>
       </c>
       <c r="K48" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L48" t="n">
         <v>1.44</v>
@@ -12565,7 +12565,7 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O48" t="n">
         <v>1.46</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -12801,16 +12801,16 @@
         <v>2.28</v>
       </c>
       <c r="H49" t="n">
-        <v>3.65</v>
+        <v>1.87</v>
       </c>
       <c r="I49" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="K49" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L49" t="n">
         <v>1.01</v>
@@ -12819,31 +12819,31 @@
         <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O49" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q49" t="n">
         <v>1.03</v>
-      </c>
-      <c r="P49" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>2.02</v>
       </c>
       <c r="R49" t="n">
         <v>1.08</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>1.05</v>
       </c>
       <c r="T49" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="U49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V49" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="W49" t="n">
         <v>1.78</v>
@@ -12852,28 +12852,28 @@
         <v>15.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Z49" t="n">
         <v>50</v>
       </c>
       <c r="AA49" t="n">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="AB49" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AC49" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD49" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE49" t="n">
         <v>270</v>
       </c>
       <c r="AF49" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG49" t="n">
         <v>19.5</v>
@@ -12894,16 +12894,16 @@
         <v>200</v>
       </c>
       <c r="AM49" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AN49" t="n">
         <v>85</v>
       </c>
       <c r="AO49" t="n">
-        <v>760</v>
+        <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AQ49" t="n">
         <v>7.2</v>
@@ -12915,25 +12915,25 @@
         <v>1.01</v>
       </c>
       <c r="AT49" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AU49" t="n">
         <v>6.4</v>
       </c>
       <c r="AV49" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW49" t="n">
         <v>38</v>
       </c>
       <c r="AX49" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AY49" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ49" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA49" t="n">
         <v>1.01</v>
@@ -12942,7 +12942,7 @@
         <v>17</v>
       </c>
       <c r="BC49" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BD49" t="n">
         <v>29</v>
@@ -12951,7 +12951,7 @@
         <v>1.01</v>
       </c>
       <c r="BF49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BG49" t="n">
         <v>36</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -13082,19 +13082,19 @@
         <v>1.25</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R50" t="n">
         <v>1.12</v>
       </c>
       <c r="S50" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="T50" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U50" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V50" t="n">
         <v>1.01</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -13345,10 +13345,10 @@
         <v>1.46</v>
       </c>
       <c r="T51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V51" t="n">
         <v>1.01</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -13560,7 +13560,7 @@
         <v>2.82</v>
       </c>
       <c r="G52" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="H52" t="n">
         <v>2.56</v>
@@ -13575,94 +13575,94 @@
         <v>3.6</v>
       </c>
       <c r="L52" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M52" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N52" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="P52" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R52" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="S52" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="T52" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U52" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V52" t="n">
         <v>1.53</v>
       </c>
       <c r="W52" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="X52" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y52" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z52" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA52" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB52" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC52" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD52" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE52" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF52" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG52" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH52" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI52" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK52" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL52" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM52" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN52" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO52" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP52" t="n">
         <v>1.01</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -13823,7 +13823,7 @@
         <v>1000</v>
       </c>
       <c r="J53" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="K53" t="n">
         <v>1000</v>
@@ -13835,13 +13835,13 @@
         <v>1.01</v>
       </c>
       <c r="N53" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="O53" t="n">
         <v>1.22</v>
       </c>
       <c r="P53" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q53" t="n">
         <v>1.5</v>
@@ -13853,10 +13853,10 @@
         <v>1.5</v>
       </c>
       <c r="T53" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U53" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V53" t="n">
         <v>1.01</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -14065,22 +14065,22 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.91</v>
+        <v>1.04</v>
       </c>
       <c r="G54" t="n">
-        <v>2.34</v>
+        <v>1000</v>
       </c>
       <c r="H54" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="I54" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J54" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="K54" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -14089,34 +14089,34 @@
         <v>1.01</v>
       </c>
       <c r="N54" t="n">
-        <v>4</v>
+        <v>1.26</v>
       </c>
       <c r="O54" t="n">
         <v>1.2</v>
       </c>
       <c r="P54" t="n">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="R54" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="S54" t="n">
-        <v>2.32</v>
+        <v>1.2</v>
       </c>
       <c r="T54" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U54" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V54" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="W54" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="X54" t="n">
         <v>1000</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -14349,7 +14349,7 @@
         <v>1.32</v>
       </c>
       <c r="P55" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q55" t="n">
         <v>1.9</v>
@@ -14484,65 +14484,65 @@
         <v>1000</v>
       </c>
       <c r="BI55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ55" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BK55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL55" t="n">
         <v>1000</v>
       </c>
       <c r="BM55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN55" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO55" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BP55" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR55" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT55" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BU55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV55" t="n">
         <v>1000</v>
       </c>
       <c r="BW55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX55" t="n">
         <v>1000</v>
       </c>
       <c r="BY55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ55" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -14576,16 +14576,16 @@
         <v>3.05</v>
       </c>
       <c r="G56" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="H56" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I56" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="J56" t="n">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="K56" t="n">
         <v>3.4</v>
@@ -14594,145 +14594,145 @@
         <v>1.01</v>
       </c>
       <c r="M56" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N56" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="O56" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P56" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="Q56" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R56" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S56" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="T56" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U56" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="V56" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="W56" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X56" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z56" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA56" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB56" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC56" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD56" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE56" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF56" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG56" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH56" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI56" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK56" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL56" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM56" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN56" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO56" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV56" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA56" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BD56" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG56" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH56" t="n">
         <v>1000</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -14848,13 +14848,13 @@
         <v>1.01</v>
       </c>
       <c r="M57" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N57" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="O57" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P57" t="n">
         <v>2.16</v>
@@ -14863,16 +14863,16 @@
         <v>1.69</v>
       </c>
       <c r="R57" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S57" t="n">
-        <v>2.54</v>
+        <v>2.76</v>
       </c>
       <c r="T57" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="U57" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V57" t="n">
         <v>1.08</v>
@@ -14881,13 +14881,13 @@
         <v>3.7</v>
       </c>
       <c r="X57" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y57" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z57" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA57" t="n">
         <v>1000</v>
@@ -14896,97 +14896,97 @@
         <v>10</v>
       </c>
       <c r="AC57" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AD57" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE57" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AF57" t="n">
         <v>9.4</v>
       </c>
       <c r="AG57" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH57" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI57" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AK57" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL57" t="n">
         <v>55</v>
       </c>
       <c r="AM57" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN57" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AO57" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.28</v>
+        <v>17.5</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.28</v>
+        <v>3.95</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.28</v>
+        <v>4.2</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.28</v>
+        <v>4.3</v>
       </c>
       <c r="AT57" t="n">
         <v>7</v>
       </c>
       <c r="AU57" t="n">
-        <v>1.28</v>
+        <v>11</v>
       </c>
       <c r="AV57" t="n">
-        <v>1.28</v>
+        <v>4</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.28</v>
+        <v>4.3</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.13</v>
+        <v>6.6</v>
       </c>
       <c r="AY57" t="n">
-        <v>1.28</v>
+        <v>9.4</v>
       </c>
       <c r="AZ57" t="n">
-        <v>1.28</v>
+        <v>3.95</v>
       </c>
       <c r="BA57" t="n">
-        <v>1.28</v>
+        <v>4.2</v>
       </c>
       <c r="BB57" t="n">
-        <v>1.28</v>
+        <v>8.6</v>
       </c>
       <c r="BC57" t="n">
-        <v>1.28</v>
+        <v>13</v>
       </c>
       <c r="BD57" t="n">
-        <v>1.26</v>
+        <v>4</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.28</v>
+        <v>4.3</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.28</v>
+        <v>4.2</v>
       </c>
       <c r="BG57" t="n">
-        <v>1.28</v>
+        <v>4.3</v>
       </c>
       <c r="BH57" t="n">
         <v>1000</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -15087,7 +15087,7 @@
         <v>1.16</v>
       </c>
       <c r="H58" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I58" t="n">
         <v>1000</v>
@@ -15105,7 +15105,7 @@
         <v>1.01</v>
       </c>
       <c r="N58" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="O58" t="n">
         <v>1.04</v>
@@ -15117,16 +15117,16 @@
         <v>1.04</v>
       </c>
       <c r="R58" t="n">
-        <v>1.18</v>
+        <v>1.63</v>
       </c>
       <c r="S58" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="T58" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U58" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V58" t="n">
         <v>1.01</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -15335,16 +15335,16 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="G59" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="H59" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I59" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="J59" t="n">
         <v>3.5</v>
@@ -15353,64 +15353,64 @@
         <v>3.85</v>
       </c>
       <c r="L59" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M59" t="n">
         <v>1.1</v>
       </c>
       <c r="N59" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O59" t="n">
         <v>1.45</v>
       </c>
       <c r="P59" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="R59" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S59" t="n">
         <v>4.4</v>
       </c>
       <c r="T59" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U59" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V59" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W59" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="X59" t="n">
         <v>13</v>
       </c>
       <c r="Y59" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z59" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA59" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AB59" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AC59" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD59" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AE59" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF59" t="n">
         <v>11.5</v>
@@ -15431,7 +15431,7 @@
         <v>27</v>
       </c>
       <c r="AL59" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM59" t="n">
         <v>240</v>
@@ -15440,7 +15440,7 @@
         <v>19</v>
       </c>
       <c r="AO59" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AP59" t="n">
         <v>9.199999999999999</v>
@@ -15449,10 +15449,10 @@
         <v>14</v>
       </c>
       <c r="AR59" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AS59" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AT59" t="n">
         <v>5.7</v>
@@ -15464,7 +15464,7 @@
         <v>21</v>
       </c>
       <c r="AW59" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AX59" t="n">
         <v>7.8</v>
@@ -15476,7 +15476,7 @@
         <v>21</v>
       </c>
       <c r="BA59" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BB59" t="n">
         <v>15.5</v>
@@ -15485,16 +15485,16 @@
         <v>18.5</v>
       </c>
       <c r="BD59" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE59" t="n">
         <v>4.4</v>
-      </c>
-      <c r="BE59" t="n">
-        <v>4.7</v>
       </c>
       <c r="BF59" t="n">
         <v>11.5</v>
       </c>
       <c r="BG59" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BH59" t="n">
         <v>1000</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -15598,7 +15598,7 @@
         <v>4.5</v>
       </c>
       <c r="I60" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J60" t="n">
         <v>3.3</v>
@@ -15607,7 +15607,7 @@
         <v>3.5</v>
       </c>
       <c r="L60" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M60" t="n">
         <v>1.09</v>
@@ -15622,13 +15622,13 @@
         <v>1.7</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R60" t="n">
         <v>1.26</v>
       </c>
       <c r="S60" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T60" t="n">
         <v>1.99</v>
@@ -15658,7 +15658,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC60" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AD60" t="n">
         <v>24</v>
@@ -15703,10 +15703,10 @@
         <v>12</v>
       </c>
       <c r="AR60" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AS60" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT60" t="n">
         <v>6.6</v>
@@ -15715,10 +15715,10 @@
         <v>7</v>
       </c>
       <c r="AV60" t="n">
-        <v>3.65</v>
+        <v>16.5</v>
       </c>
       <c r="AW60" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AX60" t="n">
         <v>10</v>
@@ -15727,28 +15727,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ60" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BA60" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BB60" t="n">
         <v>20</v>
       </c>
       <c r="BC60" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BD60" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE60" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF60" t="n">
         <v>13.5</v>
       </c>
       <c r="BG60" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH60" t="n">
         <v>3.5</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -15846,13 +15846,13 @@
         <v>5.4</v>
       </c>
       <c r="G61" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H61" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="I61" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="J61" t="n">
         <v>3.4</v>
@@ -15864,7 +15864,7 @@
         <v>1.01</v>
       </c>
       <c r="M61" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N61" t="n">
         <v>2.88</v>
@@ -15876,7 +15876,7 @@
         <v>1.61</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.02</v>
+        <v>2.18</v>
       </c>
       <c r="R61" t="n">
         <v>1.23</v>
@@ -15885,124 +15885,124 @@
         <v>4.6</v>
       </c>
       <c r="T61" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="U61" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="V61" t="n">
         <v>2.12</v>
       </c>
       <c r="W61" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X61" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y61" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="Z61" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA61" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB61" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC61" t="n">
         <v>8.4</v>
       </c>
       <c r="AD61" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE61" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF61" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG61" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH61" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI61" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ61" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AK61" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL61" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM61" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN61" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AO61" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.13</v>
+        <v>6</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.13</v>
+        <v>8.6</v>
       </c>
       <c r="AS61" t="n">
-        <v>1.13</v>
+        <v>17.5</v>
       </c>
       <c r="AT61" t="n">
-        <v>1.13</v>
+        <v>13</v>
       </c>
       <c r="AU61" t="n">
         <v>7.2</v>
       </c>
       <c r="AV61" t="n">
-        <v>1.13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW61" t="n">
-        <v>1.13</v>
+        <v>20</v>
       </c>
       <c r="AX61" t="n">
-        <v>1.13</v>
+        <v>5</v>
       </c>
       <c r="AY61" t="n">
-        <v>1.13</v>
+        <v>20</v>
       </c>
       <c r="AZ61" t="n">
-        <v>1.13</v>
+        <v>21</v>
       </c>
       <c r="BA61" t="n">
-        <v>1.13</v>
+        <v>5</v>
       </c>
       <c r="BB61" t="n">
-        <v>1.13</v>
+        <v>5.3</v>
       </c>
       <c r="BC61" t="n">
-        <v>1.13</v>
+        <v>5.2</v>
       </c>
       <c r="BD61" t="n">
-        <v>1.13</v>
+        <v>5.2</v>
       </c>
       <c r="BE61" t="n">
-        <v>1.13</v>
+        <v>5.3</v>
       </c>
       <c r="BF61" t="n">
-        <v>1.13</v>
+        <v>5.3</v>
       </c>
       <c r="BG61" t="n">
-        <v>1.13</v>
+        <v>12.5</v>
       </c>
       <c r="BH61" t="n">
         <v>1000</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
         <v>1000</v>
       </c>
       <c r="J62" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K62" t="n">
         <v>1000</v>
@@ -16139,10 +16139,10 @@
         <v>1.53</v>
       </c>
       <c r="T62" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U62" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V62" t="n">
         <v>1.01</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -16363,7 +16363,7 @@
         <v>1000</v>
       </c>
       <c r="J63" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K63" t="n">
         <v>950</v>
@@ -16390,13 +16390,13 @@
         <v>1.18</v>
       </c>
       <c r="S63" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="T63" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U63" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V63" t="n">
         <v>1.01</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -16605,19 +16605,19 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="G64" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H64" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="I64" t="n">
         <v>1000</v>
       </c>
       <c r="J64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K64" t="n">
         <v>1000</v>
@@ -16629,7 +16629,7 @@
         <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O64" t="n">
         <v>1.01</v>
@@ -16644,16 +16644,16 @@
         <v>1.18</v>
       </c>
       <c r="S64" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T64" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U64" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V64" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="W64" t="n">
         <v>1.5</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -16862,28 +16862,28 @@
         <v>1.39</v>
       </c>
       <c r="G65" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="H65" t="n">
-        <v>2.24</v>
+        <v>8.4</v>
       </c>
       <c r="I65" t="n">
         <v>11.5</v>
       </c>
       <c r="J65" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K65" t="n">
         <v>5.6</v>
       </c>
       <c r="L65" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M65" t="n">
         <v>1.01</v>
       </c>
       <c r="N65" t="n">
-        <v>2.08</v>
+        <v>3.05</v>
       </c>
       <c r="O65" t="n">
         <v>1.24</v>
@@ -16898,13 +16898,13 @@
         <v>1.34</v>
       </c>
       <c r="S65" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T65" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U65" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V65" t="n">
         <v>1.09</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -17122,7 +17122,7 @@
         <v>2.58</v>
       </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="J66" t="n">
         <v>3.15</v>
@@ -17137,7 +17137,7 @@
         <v>1.01</v>
       </c>
       <c r="N66" t="n">
-        <v>2.82</v>
+        <v>1.79</v>
       </c>
       <c r="O66" t="n">
         <v>1.34</v>
@@ -17152,7 +17152,7 @@
         <v>1.18</v>
       </c>
       <c r="S66" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="T66" t="n">
         <v>1.01</v>
@@ -17164,52 +17164,52 @@
         <v>1.54</v>
       </c>
       <c r="W66" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="X66" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y66" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z66" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA66" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB66" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC66" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD66" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE66" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF66" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG66" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH66" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI66" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ66" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK66" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL66" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM66" t="n">
         <v>1000</v>
@@ -17221,58 +17221,58 @@
         <v>1000</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="AQ66" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="AR66" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS66" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT66" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="AU66" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="AV66" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW66" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="AX66" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="AY66" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="AZ66" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BA66" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB66" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC66" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BD66" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE66" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF66" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG66" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH66" t="n">
         <v>1000</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -17367,22 +17367,22 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G67" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="H67" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="I67" t="n">
         <v>7.8</v>
       </c>
       <c r="J67" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="K67" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L67" t="n">
         <v>1.01</v>
@@ -17391,94 +17391,94 @@
         <v>1.07</v>
       </c>
       <c r="N67" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="O67" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P67" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="R67" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="S67" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="T67" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U67" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V67" t="n">
         <v>1.14</v>
       </c>
       <c r="W67" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="X67" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y67" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z67" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA67" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB67" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC67" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD67" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE67" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF67" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG67" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH67" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI67" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ67" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK67" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL67" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM67" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN67" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO67" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AR67" t="n">
         <v>1.01</v>
@@ -17487,34 +17487,34 @@
         <v>1.01</v>
       </c>
       <c r="AT67" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU67" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV67" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AW67" t="n">
         <v>1.01</v>
       </c>
       <c r="AX67" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY67" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ67" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA67" t="n">
         <v>1.01</v>
       </c>
       <c r="BB67" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BC67" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD67" t="n">
         <v>1.01</v>
@@ -17523,7 +17523,7 @@
         <v>1.01</v>
       </c>
       <c r="BF67" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG67" t="n">
         <v>1.01</v>
@@ -17532,55 +17532,55 @@
         <v>1000</v>
       </c>
       <c r="BI67" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ67" t="n">
         <v>1000</v>
       </c>
       <c r="BK67" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL67" t="n">
         <v>1000</v>
       </c>
       <c r="BM67" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN67" t="n">
         <v>1000</v>
       </c>
       <c r="BO67" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP67" t="n">
         <v>1000</v>
       </c>
       <c r="BQ67" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR67" t="n">
         <v>1000</v>
       </c>
       <c r="BS67" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT67" t="n">
         <v>1000</v>
       </c>
       <c r="BU67" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV67" t="n">
         <v>1000</v>
       </c>
       <c r="BW67" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX67" t="n">
         <v>1000</v>
       </c>
       <c r="BY67" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ67" t="n">
         <v>0</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -17875,28 +17875,28 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="G69" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="H69" t="n">
         <v>5.1</v>
       </c>
       <c r="I69" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="J69" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K69" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="L69" t="n">
         <v>1.38</v>
       </c>
       <c r="M69" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N69" t="n">
         <v>3.05</v>
@@ -17908,25 +17908,25 @@
         <v>1.71</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R69" t="n">
         <v>1.26</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="T69" t="n">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="U69" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="V69" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W69" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="X69" t="n">
         <v>14.5</v>
@@ -17983,10 +17983,10 @@
         <v>160</v>
       </c>
       <c r="AP69" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AQ69" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR69" t="n">
         <v>4</v>
@@ -17995,22 +17995,22 @@
         <v>4.2</v>
       </c>
       <c r="AT69" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU69" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU69" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AV69" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AW69" t="n">
         <v>4.2</v>
       </c>
       <c r="AX69" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AY69" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AZ69" t="n">
         <v>19</v>
@@ -18019,10 +18019,10 @@
         <v>4.2</v>
       </c>
       <c r="BB69" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC69" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BD69" t="n">
         <v>4</v>
@@ -18046,13 +18046,13 @@
         <v>13.5</v>
       </c>
       <c r="BK69" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BL69" t="n">
         <v>210</v>
       </c>
       <c r="BM69" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN69" t="n">
         <v>5</v>
@@ -18064,41 +18064,41 @@
         <v>16</v>
       </c>
       <c r="BQ69" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR69" t="n">
         <v>40</v>
       </c>
       <c r="BS69" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BT69" t="n">
         <v>10.5</v>
       </c>
       <c r="BU69" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV69" t="n">
         <v>65</v>
       </c>
       <c r="BW69" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BX69" t="n">
         <v>80</v>
       </c>
       <c r="BY69" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BZ69" t="n">
         <v>36</v>
       </c>
       <c r="CA69" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -18129,10 +18129,10 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="G70" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H70" t="n">
         <v>3.95</v>
@@ -18144,25 +18144,25 @@
         <v>3.25</v>
       </c>
       <c r="K70" t="n">
-        <v>110</v>
+        <v>4.4</v>
       </c>
       <c r="L70" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="M70" t="n">
         <v>1.01</v>
       </c>
       <c r="N70" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="O70" t="n">
         <v>1.01</v>
       </c>
       <c r="P70" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.02</v>
+        <v>2.16</v>
       </c>
       <c r="R70" t="n">
         <v>1.18</v>
@@ -18171,61 +18171,61 @@
         <v>3.9</v>
       </c>
       <c r="T70" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U70" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V70" t="n">
         <v>1.19</v>
       </c>
       <c r="W70" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X70" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y70" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z70" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA70" t="n">
         <v>1000</v>
       </c>
       <c r="AB70" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC70" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD70" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE70" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF70" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG70" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH70" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI70" t="n">
         <v>1000</v>
       </c>
       <c r="AJ70" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK70" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL70" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM70" t="n">
         <v>1000</v>
@@ -18237,58 +18237,58 @@
         <v>1000</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="AQ70" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR70" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="AS70" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="AT70" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU70" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV70" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW70" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX70" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="AY70" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ70" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BA70" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BB70" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BC70" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BD70" t="n">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BE70" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BF70" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BG70" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BH70" t="n">
         <v>1000</v>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
         <v>1.43</v>
       </c>
       <c r="G71" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="H71" t="n">
         <v>8.6</v>
@@ -18398,215 +18398,215 @@
         <v>4.7</v>
       </c>
       <c r="K71" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P71" t="n">
         <v>1.93</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI71" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AK71" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AL71" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM71" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AN71" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AO71" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AP71" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AR71" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS71" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU71" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AV71" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AW71" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AX71" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AY71" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ71" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BA71" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BB71" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BC71" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BD71" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE71" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BF71" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BG71" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BH71" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ71" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL71" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN71" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP71" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR71" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT71" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV71" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX71" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ71" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -18637,230 +18637,230 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="G72" t="n">
         <v>3.45</v>
       </c>
       <c r="H72" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I72" t="n">
         <v>2.56</v>
       </c>
       <c r="J72" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K72" t="n">
         <v>4.3</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P72" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q72" t="n">
         <v>1.56</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -18906,19 +18906,19 @@
         <v>3.5</v>
       </c>
       <c r="K73" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P73" t="n">
         <v>1.76</v>
@@ -18927,194 +18927,194 @@
         <v>2.04</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI73" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK73" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL73" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM73" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN73" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AO73" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP73" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR73" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AS73" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AT73" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU73" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV73" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW73" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AX73" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY73" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ73" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA73" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BB73" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BC73" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD73" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE73" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF73" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG73" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BH73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -19163,16 +19163,16 @@
         <v>3.75</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P74" t="n">
         <v>2.06</v>
@@ -19181,194 +19181,194 @@
         <v>1.83</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI74" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK74" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL74" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM74" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP74" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR74" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AS74" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU74" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AV74" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW74" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AX74" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY74" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AZ74" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BA74" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BB74" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BC74" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD74" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BE74" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BF74" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BG74" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BH74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -19399,230 +19399,230 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P75" t="n">
-        <v>1.24</v>
+        <v>1.88</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD75" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI75" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AK75" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL75" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM75" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN75" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AO75" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP75" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR75" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS75" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU75" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV75" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW75" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AX75" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY75" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ75" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BA75" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BB75" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BC75" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BD75" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BE75" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BF75" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG75" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BH75" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BI75" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BJ75" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK75" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BL75" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="BM75" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN75" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BO75" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BP75" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BQ75" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BR75" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS75" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BT75" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU75" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BV75" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BW75" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BX75" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BY75" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BZ75" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="CA75" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-18.xlsx
@@ -899,10 +899,10 @@
         <v>2.86</v>
       </c>
       <c r="T2" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="U2" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="V2" t="n">
         <v>1.2</v>
@@ -926,7 +926,7 @@
         <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD2" t="n">
         <v>24</v>
@@ -938,7 +938,7 @@
         <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
         <v>22</v>
@@ -971,10 +971,10 @@
         <v>17.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT2" t="n">
         <v>8.4</v>
@@ -986,7 +986,7 @@
         <v>17.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX2" t="n">
         <v>9.4</v>
@@ -998,7 +998,7 @@
         <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB2" t="n">
         <v>14.5</v>
@@ -1007,16 +1007,16 @@
         <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
         <v>1.04</v>
@@ -1037,31 +1037,31 @@
         <v>1.04</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
         <v>1.04</v>
       </c>
       <c r="BP2" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
         <v>1.04</v>
       </c>
       <c r="BR2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
         <v>1.04</v>
       </c>
       <c r="BT2" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
         <v>1.04</v>
       </c>
       <c r="BV2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
         <v>1.04</v>
@@ -1073,14 +1073,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
         <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
         <v>1.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R3" t="n">
         <v>1.37</v>
@@ -1153,10 +1153,10 @@
         <v>3.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U3" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="V3" t="n">
         <v>1.56</v>
@@ -1168,13 +1168,13 @@
         <v>18</v>
       </c>
       <c r="Y3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z3" t="n">
         <v>19</v>
       </c>
       <c r="AA3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB3" t="n">
         <v>14.5</v>
@@ -1216,7 +1216,7 @@
         <v>30</v>
       </c>
       <c r="AO3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP3" t="n">
         <v>12</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1389,16 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R4" t="n">
         <v>1.32</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>1.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
@@ -1676,88 +1676,88 @@
         <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP5" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA5" t="n">
         <v>1.01</v>
@@ -1778,7 +1778,7 @@
         <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -1906,19 +1906,19 @@
         <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="R6" t="n">
         <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="V6" t="n">
         <v>1.66</v>
@@ -1945,10 +1945,10 @@
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF6" t="n">
         <v>27</v>
@@ -2029,7 +2029,7 @@
         <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG6" t="n">
         <v>12.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -2151,13 +2151,13 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
         <v>1.32</v>
       </c>
       <c r="P7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q7" t="n">
         <v>1.93</v>
@@ -2205,7 +2205,7 @@
         <v>34</v>
       </c>
       <c r="AF7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
@@ -2241,7 +2241,7 @@
         <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS7" t="n">
         <v>9.199999999999999</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2567,7 @@
         <v>4.9</v>
       </c>
       <c r="BP8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BQ8" t="n">
         <v>4.3</v>
@@ -2588,7 +2588,7 @@
         <v>24</v>
       </c>
       <c r="BW8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BX8" t="n">
         <v>46</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>3.1</v>
       </c>
       <c r="G9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H9" t="n">
         <v>2.58</v>
@@ -2647,37 +2647,37 @@
         <v>2.76</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M9" t="n">
         <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="O9" t="n">
         <v>1.51</v>
       </c>
       <c r="P9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q9" t="n">
         <v>2.52</v>
       </c>
       <c r="R9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
         <v>5.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U9" t="n">
         <v>1.84</v>
@@ -2689,7 +2689,7 @@
         <v>1.42</v>
       </c>
       <c r="X9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y9" t="n">
         <v>8.4</v>
@@ -2698,7 +2698,7 @@
         <v>16.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AB9" t="n">
         <v>9.6</v>
@@ -2716,19 +2716,19 @@
         <v>21</v>
       </c>
       <c r="AG9" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ9" t="n">
         <v>75</v>
       </c>
       <c r="AK9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL9" t="n">
         <v>85</v>
@@ -2752,7 +2752,7 @@
         <v>13.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT9" t="n">
         <v>8.4</v>
@@ -2764,101 +2764,101 @@
         <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX9" t="n">
         <v>17</v>
       </c>
       <c r="AY9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ9" t="n">
         <v>18.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG9" t="n">
         <v>8.4</v>
       </c>
-      <c r="BF9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG9" t="n">
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>42</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BT9" t="n">
         <v>7.4</v>
       </c>
-      <c r="BH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G10" t="n">
         <v>1.97</v>
@@ -2907,7 +2907,7 @@
         <v>3.85</v>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
@@ -2946,7 +2946,7 @@
         <v>14</v>
       </c>
       <c r="Y10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Z10" t="n">
         <v>44</v>
@@ -2973,7 +2973,7 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
         <v>90</v>
@@ -3003,10 +3003,10 @@
         <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT10" t="n">
         <v>7.4</v>
@@ -3018,7 +3018,7 @@
         <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3030,7 +3030,7 @@
         <v>17.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB10" t="n">
         <v>18</v>
@@ -3039,16 +3039,16 @@
         <v>17.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BE10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF10" t="n">
         <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH10" t="n">
         <v>3.8</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>3.65</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L11" t="n">
         <v>1.32</v>
@@ -3182,7 +3182,7 @@
         <v>1.51</v>
       </c>
       <c r="S11" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T11" t="n">
         <v>1.6</v>
@@ -3245,7 +3245,7 @@
         <v>90</v>
       </c>
       <c r="AN11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO11" t="n">
         <v>16</v>
@@ -3257,7 +3257,7 @@
         <v>12</v>
       </c>
       <c r="AR11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS11" t="n">
         <v>28</v>
@@ -3284,16 +3284,16 @@
         <v>13</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB11" t="n">
         <v>30</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE11" t="n">
         <v>9.199999999999999</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
         <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -3427,25 +3427,25 @@
         <v>1.28</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
         <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U12" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W12" t="n">
         <v>1.66</v>
@@ -3466,7 +3466,7 @@
         <v>13.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
         <v>14.5</v>
@@ -3487,7 +3487,7 @@
         <v>48</v>
       </c>
       <c r="AJ12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK12" t="n">
         <v>30</v>
@@ -3511,10 +3511,10 @@
         <v>10.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AT12" t="n">
         <v>9</v>
@@ -3526,7 +3526,7 @@
         <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AX12" t="n">
         <v>12.5</v>
@@ -3538,19 +3538,19 @@
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE12" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.4</v>
       </c>
       <c r="BF12" t="n">
         <v>14</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="G13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H13" t="n">
         <v>2.02</v>
       </c>
       <c r="I13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L13" t="n">
         <v>1.43</v>
@@ -3681,28 +3681,28 @@
         <v>1.35</v>
       </c>
       <c r="P13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.81</v>
       </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.8</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X13" t="n">
         <v>15.5</v>
@@ -3717,7 +3717,7 @@
         <v>32</v>
       </c>
       <c r="AB13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC13" t="n">
         <v>9.6</v>
@@ -3732,10 +3732,10 @@
         <v>36</v>
       </c>
       <c r="AG13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI13" t="n">
         <v>50</v>
@@ -3744,7 +3744,7 @@
         <v>110</v>
       </c>
       <c r="AK13" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL13" t="n">
         <v>80</v>
@@ -3753,64 +3753,64 @@
         <v>140</v>
       </c>
       <c r="AN13" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AO13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH13" t="n">
         <v>3.75</v>
@@ -3831,16 +3831,16 @@
         <v>4.7</v>
       </c>
       <c r="BN13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="BP13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BR13" t="n">
         <v>60</v>
@@ -3849,13 +3849,13 @@
         <v>4.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>2.62</v>
+        <v>3.65</v>
       </c>
       <c r="BV13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW13" t="n">
         <v>3.85</v>
@@ -3870,11 +3870,11 @@
         <v>36</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G14" t="n">
         <v>3.7</v>
@@ -3920,7 +3920,7 @@
         <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
         <v>1.28</v>
@@ -3935,7 +3935,7 @@
         <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
         <v>1.82</v>
@@ -4001,10 +4001,10 @@
         <v>42</v>
       </c>
       <c r="AL14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM14" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN14" t="n">
         <v>36</v>
@@ -4013,58 +4013,58 @@
         <v>16.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -4165,13 +4165,13 @@
         <v>2.42</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="I15" t="n">
         <v>3.85</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
         <v>3.55</v>
@@ -4267,58 +4267,58 @@
         <v>65</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH15" t="n">
         <v>3.45</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -4416,16 +4416,16 @@
         <v>2.32</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H16" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
         <v>4.4</v>
@@ -4434,7 +4434,7 @@
         <v>1.24</v>
       </c>
       <c r="M16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
         <v>6.2</v>
@@ -4443,34 +4443,34 @@
         <v>1.16</v>
       </c>
       <c r="P16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T16" t="n">
         <v>1.49</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.48</v>
-      </c>
       <c r="U16" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="V16" t="n">
         <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X16" t="n">
         <v>36</v>
       </c>
       <c r="Y16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z16" t="n">
         <v>34</v>
@@ -4479,25 +4479,25 @@
         <v>60</v>
       </c>
       <c r="AB16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD16" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE16" t="n">
         <v>34</v>
       </c>
       <c r="AF16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG16" t="n">
         <v>15</v>
       </c>
       <c r="AH16" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI16" t="n">
         <v>38</v>
@@ -4506,7 +4506,7 @@
         <v>38</v>
       </c>
       <c r="AK16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL16" t="n">
         <v>32</v>
@@ -4518,10 +4518,10 @@
         <v>12.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AQ16" t="n">
         <v>17</v>
@@ -4530,7 +4530,7 @@
         <v>19</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AT16" t="n">
         <v>15</v>
@@ -4539,7 +4539,7 @@
         <v>9.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW16" t="n">
         <v>20</v>
@@ -4551,28 +4551,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BC16" t="n">
         <v>18</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BH16" t="n">
         <v>5.6</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -4679,10 +4679,10 @@
         <v>7.8</v>
       </c>
       <c r="J17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L17" t="n">
         <v>1.26</v>
@@ -4694,16 +4694,16 @@
         <v>5.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P17" t="n">
         <v>2.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S17" t="n">
         <v>2.28</v>
@@ -4712,13 +4712,13 @@
         <v>1.73</v>
       </c>
       <c r="U17" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V17" t="n">
         <v>1.15</v>
       </c>
       <c r="W17" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="X17" t="n">
         <v>29</v>
@@ -4781,7 +4781,7 @@
         <v>23</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS17" t="n">
         <v>10.5</v>
@@ -4799,16 +4799,16 @@
         <v>10</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
         <v>17.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB17" t="n">
         <v>12</v>
@@ -4826,7 +4826,7 @@
         <v>4.7</v>
       </c>
       <c r="BG17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH17" t="n">
         <v>5.4</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G18" t="n">
         <v>3.85</v>
@@ -4930,13 +4930,13 @@
         <v>2.24</v>
       </c>
       <c r="I18" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L18" t="n">
         <v>1.43</v>
@@ -4954,19 +4954,19 @@
         <v>1.78</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R18" t="n">
         <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="T18" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V18" t="n">
         <v>1.58</v>
@@ -4975,25 +4975,25 @@
         <v>1.29</v>
       </c>
       <c r="X18" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA18" t="n">
         <v>38</v>
       </c>
       <c r="AB18" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AE18" t="n">
         <v>34</v>
@@ -5002,10 +5002,10 @@
         <v>32</v>
       </c>
       <c r="AG18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH18" t="n">
         <v>19</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>22</v>
       </c>
       <c r="AI18" t="n">
         <v>55</v>
@@ -5023,64 +5023,64 @@
         <v>130</v>
       </c>
       <c r="AN18" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AO18" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AP18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR18" t="n">
         <v>12</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.85</v>
+        <v>6.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX18" t="n">
         <v>21</v>
       </c>
       <c r="AY18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ18" t="n">
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.95</v>
+        <v>7.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="BD18" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BH18" t="n">
         <v>3.7</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -5429,61 +5429,61 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G20" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I20" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
         <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S20" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T20" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U20" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="X20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y20" t="n">
         <v>16</v>
@@ -5495,22 +5495,22 @@
         <v>55</v>
       </c>
       <c r="AB20" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC20" t="n">
         <v>11</v>
       </c>
       <c r="AD20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE20" t="n">
         <v>36</v>
       </c>
       <c r="AF20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
         <v>19.5</v>
@@ -5519,19 +5519,19 @@
         <v>55</v>
       </c>
       <c r="AJ20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK20" t="n">
         <v>24</v>
       </c>
       <c r="AL20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM20" t="n">
         <v>75</v>
       </c>
       <c r="AN20" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AO20" t="n">
         <v>28</v>
@@ -5546,31 +5546,31 @@
         <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV20" t="n">
         <v>12</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX20" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
         <v>13.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -5582,16 +5582,16 @@
         <v>26</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BF20" t="n">
         <v>12.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BH20" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BI20" t="n">
         <v>3.05</v>
@@ -5600,13 +5600,13 @@
         <v>11</v>
       </c>
       <c r="BK20" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BL20" t="n">
         <v>110</v>
       </c>
       <c r="BM20" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BN20" t="n">
         <v>6.4</v>
@@ -5618,13 +5618,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BR20" t="n">
         <v>32</v>
       </c>
       <c r="BS20" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BT20" t="n">
         <v>7.8</v>
@@ -5633,26 +5633,26 @@
         <v>5</v>
       </c>
       <c r="BV20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW20" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BX20" t="n">
         <v>38</v>
       </c>
       <c r="BY20" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BZ20" t="n">
         <v>25</v>
       </c>
       <c r="CA20" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -5686,22 +5686,22 @@
         <v>2.28</v>
       </c>
       <c r="G21" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H21" t="n">
         <v>3.1</v>
       </c>
       <c r="I21" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K21" t="n">
         <v>3.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M21" t="n">
         <v>1.08</v>
@@ -5722,22 +5722,22 @@
         <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="T21" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="V21" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
         <v>1.62</v>
       </c>
       <c r="X21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y21" t="n">
         <v>14.5</v>
@@ -5791,46 +5791,46 @@
         <v>55</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS21" t="n">
         <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW21" t="n">
         <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA21" t="n">
         <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
         <v>1.01</v>
@@ -5839,7 +5839,7 @@
         <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG21" t="n">
         <v>1.01</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -5940,13 +5940,13 @@
         <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H22" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I22" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J22" t="n">
         <v>4.1</v>
@@ -5967,28 +5967,28 @@
         <v>1.21</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
         <v>1.62</v>
       </c>
       <c r="R22" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S22" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T22" t="n">
         <v>1.6</v>
       </c>
       <c r="U22" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V22" t="n">
         <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X22" t="n">
         <v>28</v>
@@ -6093,7 +6093,7 @@
         <v>4.1</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG22" t="n">
         <v>3.85</v>
@@ -6108,19 +6108,19 @@
         <v>10.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BL22" t="n">
         <v>100</v>
       </c>
       <c r="BM22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BN22" t="n">
         <v>6</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="BP22" t="n">
         <v>16</v>
@@ -6132,7 +6132,7 @@
         <v>27</v>
       </c>
       <c r="BS22" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BT22" t="n">
         <v>9</v>
@@ -6153,14 +6153,14 @@
         <v>4.2</v>
       </c>
       <c r="BZ22" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA22" t="n">
         <v>3.8</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -6224,13 +6224,13 @@
         <v>1.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="R23" t="n">
         <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T23" t="n">
         <v>1.11</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -6472,19 +6472,19 @@
         <v>1.24</v>
       </c>
       <c r="O24" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P24" t="n">
         <v>1.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R24" t="n">
         <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T24" t="n">
         <v>1.11</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
         <v>2.76</v>
       </c>
       <c r="G25" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H25" t="n">
         <v>2.68</v>
@@ -6723,28 +6723,28 @@
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
         <v>1.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R25" t="n">
         <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T25" t="n">
         <v>1.73</v>
       </c>
       <c r="U25" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V25" t="n">
         <v>1.57</v>
@@ -6753,7 +6753,7 @@
         <v>1.54</v>
       </c>
       <c r="X25" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y25" t="n">
         <v>13</v>
@@ -6762,52 +6762,52 @@
         <v>23</v>
       </c>
       <c r="AA25" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB25" t="n">
         <v>13</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AE25" t="n">
         <v>36</v>
       </c>
       <c r="AF25" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH25" t="n">
         <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ25" t="n">
         <v>55</v>
       </c>
       <c r="AK25" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL25" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM25" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO25" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AP25" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ25" t="n">
         <v>10.5</v>
@@ -6816,7 +6816,7 @@
         <v>15.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT25" t="n">
         <v>10.5</v>
@@ -6837,22 +6837,22 @@
         <v>11</v>
       </c>
       <c r="AZ25" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="BC25" t="n">
         <v>21</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="BF25" t="n">
         <v>17.5</v>
@@ -6909,20 +6909,20 @@
         <v>1.04</v>
       </c>
       <c r="BX25" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BY25" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ25" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA25" t="n">
         <v>1.04</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
         <v>2.12</v>
       </c>
       <c r="G26" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H26" t="n">
         <v>3.45</v>
@@ -6968,10 +6968,10 @@
         <v>3.65</v>
       </c>
       <c r="K26" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L26" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
@@ -6992,19 +6992,19 @@
         <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T26" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U26" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V26" t="n">
         <v>1.35</v>
       </c>
       <c r="W26" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X26" t="n">
         <v>19.5</v>
@@ -7115,16 +7115,16 @@
         <v>4</v>
       </c>
       <c r="BH26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI26" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BJ26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK26" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BL26" t="n">
         <v>130</v>
@@ -7169,14 +7169,14 @@
         <v>4.2</v>
       </c>
       <c r="BZ26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CA26" t="n">
         <v>4</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>2.86</v>
+        <v>8.4</v>
       </c>
       <c r="BN27" t="n">
         <v>6.8</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -7464,13 +7464,13 @@
         <v>2.24</v>
       </c>
       <c r="G28" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H28" t="n">
         <v>3.25</v>
       </c>
       <c r="I28" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
         <v>3.6</v>
@@ -7500,16 +7500,16 @@
         <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T28" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U28" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V28" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W28" t="n">
         <v>1.72</v>
@@ -7626,7 +7626,7 @@
         <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="BJ28" t="n">
         <v>13</v>
@@ -7638,25 +7638,25 @@
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="BN28" t="n">
         <v>7</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BP28" t="n">
         <v>23</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="BR28" t="n">
         <v>40</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="BT28" t="n">
         <v>9</v>
@@ -7665,7 +7665,7 @@
         <v>4.5</v>
       </c>
       <c r="BV28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW28" t="n">
         <v>1.81</v>
@@ -7674,7 +7674,7 @@
         <v>50</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
         <v>1.21</v>
       </c>
       <c r="P29" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q29" t="n">
         <v>1.62</v>
@@ -7763,7 +7763,7 @@
         <v>2.52</v>
       </c>
       <c r="V29" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W29" t="n">
         <v>1.41</v>
@@ -7886,19 +7886,19 @@
         <v>10.5</v>
       </c>
       <c r="BK29" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BL29" t="n">
         <v>95</v>
       </c>
       <c r="BM29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BN29" t="n">
         <v>8</v>
       </c>
       <c r="BO29" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BP29" t="n">
         <v>27</v>
@@ -7910,35 +7910,35 @@
         <v>36</v>
       </c>
       <c r="BS29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BT29" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU29" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BV29" t="n">
         <v>18.5</v>
       </c>
       <c r="BW29" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BX29" t="n">
         <v>29</v>
       </c>
       <c r="BY29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BZ29" t="n">
         <v>21</v>
       </c>
       <c r="CA29" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
         <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="K30" t="n">
         <v>1000</v>
@@ -7993,22 +7993,22 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="O30" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P30" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T30" t="n">
         <v>1.11</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -8394,13 +8394,13 @@
         <v>10.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BL31" t="n">
         <v>110</v>
       </c>
       <c r="BM31" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BN31" t="n">
         <v>7.6</v>
@@ -8412,16 +8412,16 @@
         <v>28</v>
       </c>
       <c r="BQ31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR31" t="n">
         <v>38</v>
       </c>
       <c r="BS31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BT31" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU31" t="n">
         <v>4.2</v>
@@ -8430,23 +8430,23 @@
         <v>18.5</v>
       </c>
       <c r="BW31" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BX31" t="n">
         <v>32</v>
       </c>
       <c r="BY31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BZ31" t="n">
         <v>24</v>
       </c>
       <c r="CA31" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G32" t="n">
         <v>1.79</v>
@@ -8558,7 +8558,7 @@
         <v>13.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH32" t="n">
         <v>21</v>
@@ -8591,10 +8591,10 @@
         <v>17</v>
       </c>
       <c r="AR32" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT32" t="n">
         <v>8.800000000000001</v>
@@ -8606,7 +8606,7 @@
         <v>16.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX32" t="n">
         <v>10</v>
@@ -8618,7 +8618,7 @@
         <v>15.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB32" t="n">
         <v>15.5</v>
@@ -8627,16 +8627,16 @@
         <v>14.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF32" t="n">
         <v>7</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH32" t="n">
         <v>4.5</v>
@@ -8654,7 +8654,7 @@
         <v>120</v>
       </c>
       <c r="BM32" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BN32" t="n">
         <v>5.2</v>
@@ -8666,7 +8666,7 @@
         <v>13</v>
       </c>
       <c r="BQ32" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BR32" t="n">
         <v>27</v>
@@ -8684,7 +8684,7 @@
         <v>44</v>
       </c>
       <c r="BW32" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BX32" t="n">
         <v>50</v>
@@ -8693,14 +8693,14 @@
         <v>5</v>
       </c>
       <c r="BZ32" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="CA32" t="n">
         <v>4.3</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -8734,7 +8734,7 @@
         <v>3.1</v>
       </c>
       <c r="G33" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H33" t="n">
         <v>2.2</v>
@@ -8776,7 +8776,7 @@
         <v>1.58</v>
       </c>
       <c r="U33" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V33" t="n">
         <v>1.73</v>
@@ -8800,7 +8800,7 @@
         <v>19</v>
       </c>
       <c r="AC33" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD33" t="n">
         <v>13.5</v>
@@ -8881,7 +8881,7 @@
         <v>5.1</v>
       </c>
       <c r="BD33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE33" t="n">
         <v>5.4</v>
@@ -8902,16 +8902,16 @@
         <v>10</v>
       </c>
       <c r="BK33" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BL33" t="n">
         <v>90</v>
       </c>
       <c r="BM33" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BN33" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO33" t="n">
         <v>5.3</v>
@@ -8920,31 +8920,31 @@
         <v>26</v>
       </c>
       <c r="BQ33" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR33" t="n">
         <v>34</v>
       </c>
       <c r="BS33" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BT33" t="n">
         <v>6.2</v>
       </c>
       <c r="BU33" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV33" t="n">
         <v>17.5</v>
       </c>
       <c r="BW33" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BX33" t="n">
         <v>28</v>
       </c>
       <c r="BY33" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BZ33" t="n">
         <v>20</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -8988,61 +8988,61 @@
         <v>2.92</v>
       </c>
       <c r="G34" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="H34" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I34" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="J34" t="n">
-        <v>2.64</v>
+        <v>2.96</v>
       </c>
       <c r="K34" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L34" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M34" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="O34" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="P34" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R34" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S34" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="T34" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="U34" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="V34" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W34" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="X34" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z34" t="n">
         <v>21</v>
@@ -9060,106 +9060,106 @@
         <v>15.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF34" t="n">
         <v>25</v>
       </c>
       <c r="AG34" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH34" t="n">
         <v>25</v>
       </c>
       <c r="AI34" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ34" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK34" t="n">
         <v>55</v>
       </c>
       <c r="AL34" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM34" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN34" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO34" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH34" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BI34" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="BJ34" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK34" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BL34" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="BM34" t="n">
         <v>4.8</v>
@@ -9174,10 +9174,10 @@
         <v>34</v>
       </c>
       <c r="BQ34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BR34" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS34" t="n">
         <v>4.5</v>
@@ -9186,29 +9186,29 @@
         <v>6.6</v>
       </c>
       <c r="BU34" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BV34" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW34" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BX34" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY34" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BZ34" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="CA34" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -9263,16 +9263,16 @@
         <v>1.12</v>
       </c>
       <c r="N35" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O35" t="n">
         <v>1.46</v>
       </c>
       <c r="P35" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="R35" t="n">
         <v>1.18</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -9511,10 +9511,10 @@
         <v>4.4</v>
       </c>
       <c r="L36" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N36" t="n">
         <v>5.9</v>
@@ -9532,7 +9532,7 @@
         <v>1.69</v>
       </c>
       <c r="S36" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="T36" t="n">
         <v>1.51</v>
@@ -9547,7 +9547,7 @@
         <v>1.76</v>
       </c>
       <c r="X36" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y36" t="n">
         <v>20</v>
@@ -9589,13 +9589,13 @@
         <v>21</v>
       </c>
       <c r="AL36" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AM36" t="n">
         <v>50</v>
       </c>
       <c r="AN36" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO36" t="n">
         <v>17.5</v>
@@ -9607,10 +9607,10 @@
         <v>17.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS36" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT36" t="n">
         <v>14</v>
@@ -9676,7 +9676,7 @@
         <v>7.8</v>
       </c>
       <c r="BO36" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BP36" t="n">
         <v>20</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -9780,16 +9780,16 @@
         <v>1.76</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R37" t="n">
         <v>1.29</v>
       </c>
       <c r="S37" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="T37" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U37" t="n">
         <v>1.91</v>
@@ -9870,7 +9870,7 @@
         <v>11</v>
       </c>
       <c r="AU37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV37" t="n">
         <v>8.800000000000001</v>
@@ -9879,7 +9879,7 @@
         <v>18.5</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY37" t="n">
         <v>14</v>
@@ -9888,22 +9888,22 @@
         <v>17</v>
       </c>
       <c r="BA37" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG37" t="n">
         <v>11.5</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
         <v>2.36</v>
       </c>
       <c r="I38" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J38" t="n">
         <v>3.15</v>
@@ -10022,7 +10022,7 @@
         <v>1.35</v>
       </c>
       <c r="M38" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N38" t="n">
         <v>3.1</v>
@@ -10049,7 +10049,7 @@
         <v>1.96</v>
       </c>
       <c r="V38" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W38" t="n">
         <v>1.4</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -10258,16 +10258,16 @@
         <v>2.98</v>
       </c>
       <c r="G39" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="H39" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I39" t="n">
         <v>2.68</v>
       </c>
       <c r="J39" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="K39" t="n">
         <v>3.75</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
         <v>4</v>
       </c>
       <c r="BF40" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG40" t="n">
         <v>15.5</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G41" t="n">
         <v>1.33</v>
@@ -10772,7 +10772,7 @@
         <v>10</v>
       </c>
       <c r="I41" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="J41" t="n">
         <v>6.4</v>
@@ -10805,10 +10805,10 @@
         <v>2.04</v>
       </c>
       <c r="T41" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U41" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V41" t="n">
         <v>1.01</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -11023,7 +11023,7 @@
         <v>1.28</v>
       </c>
       <c r="H42" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="I42" t="n">
         <v>18</v>
@@ -11041,28 +11041,28 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="O42" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P42" t="n">
         <v>2.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R42" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="S42" t="n">
         <v>2.26</v>
       </c>
       <c r="T42" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="U42" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="V42" t="n">
         <v>1.05</v>
@@ -11071,112 +11071,112 @@
         <v>4.4</v>
       </c>
       <c r="X42" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="Y42" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Z42" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AA42" t="n">
         <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AF42" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG42" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AK42" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL42" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN42" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BH42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11292,7 @@
         <v>1.45</v>
       </c>
       <c r="M43" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N43" t="n">
         <v>2.8</v>
@@ -11316,7 +11316,7 @@
         <v>1.84</v>
       </c>
       <c r="U43" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V43" t="n">
         <v>1.32</v>
@@ -11442,13 +11442,13 @@
         <v>12.5</v>
       </c>
       <c r="BK43" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL43" t="n">
         <v>200</v>
       </c>
       <c r="BM43" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BN43" t="n">
         <v>5.6</v>
@@ -11460,13 +11460,13 @@
         <v>22</v>
       </c>
       <c r="BQ43" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BR43" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS43" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BT43" t="n">
         <v>7.8</v>
@@ -11478,23 +11478,23 @@
         <v>40</v>
       </c>
       <c r="BW43" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BX43" t="n">
         <v>60</v>
       </c>
       <c r="BY43" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BZ43" t="n">
         <v>46</v>
       </c>
       <c r="CA43" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
         <v>17.5</v>
       </c>
       <c r="G44" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H44" t="n">
         <v>1.14</v>
@@ -11537,7 +11537,7 @@
         <v>1.19</v>
       </c>
       <c r="J44" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="K44" t="n">
         <v>12.5</v>
@@ -11564,10 +11564,10 @@
         <v>2.54</v>
       </c>
       <c r="S44" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="T44" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U44" t="n">
         <v>2.12</v>
@@ -11582,37 +11582,37 @@
         <v>95</v>
       </c>
       <c r="Y44" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z44" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AA44" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AB44" t="n">
         <v>120</v>
       </c>
       <c r="AC44" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AD44" t="n">
         <v>16.5</v>
       </c>
       <c r="AE44" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AF44" t="n">
         <v>270</v>
       </c>
       <c r="AG44" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AH44" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI44" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ44" t="n">
         <v>1000</v>
@@ -11630,10 +11630,10 @@
         <v>200</v>
       </c>
       <c r="AO44" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AP44" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="AQ44" t="n">
         <v>17.5</v>
@@ -11645,43 +11645,43 @@
         <v>9</v>
       </c>
       <c r="AT44" t="n">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU44" t="n">
-        <v>5.4</v>
+        <v>22</v>
       </c>
       <c r="AV44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW44" t="n">
         <v>10</v>
       </c>
       <c r="AX44" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AY44" t="n">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ44" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA44" t="n">
-        <v>5.4</v>
+        <v>23</v>
       </c>
       <c r="BB44" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC44" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BD44" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BE44" t="n">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF44" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BG44" t="n">
         <v>2.04</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -11782,13 +11782,13 @@
         <v>1.2</v>
       </c>
       <c r="G45" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="H45" t="n">
         <v>1.04</v>
       </c>
       <c r="I45" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="J45" t="n">
         <v>7</v>
@@ -11827,10 +11827,10 @@
         <v>1.79</v>
       </c>
       <c r="V45" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W45" t="n">
-        <v>2.38</v>
+        <v>4.3</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -11845,100 +11845,100 @@
         <v>1000</v>
       </c>
       <c r="AB45" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC45" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD45" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE45" t="n">
         <v>1000</v>
       </c>
       <c r="AF45" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG45" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH45" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI45" t="n">
         <v>1000</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK45" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL45" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM45" t="n">
         <v>1000</v>
       </c>
       <c r="AN45" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="AO45" t="n">
         <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BG45" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BH45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -12075,7 +12075,7 @@
         <v>4.4</v>
       </c>
       <c r="T46" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U46" t="n">
         <v>1.91</v>
@@ -12099,7 +12099,7 @@
         <v>36</v>
       </c>
       <c r="AB46" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC46" t="n">
         <v>7.4</v>
@@ -12114,7 +12114,7 @@
         <v>32</v>
       </c>
       <c r="AG46" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH46" t="n">
         <v>21</v>
@@ -12123,7 +12123,7 @@
         <v>60</v>
       </c>
       <c r="AJ46" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AK46" t="n">
         <v>65</v>
@@ -12150,7 +12150,7 @@
         <v>11.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT46" t="n">
         <v>10</v>
@@ -12162,10 +12162,10 @@
         <v>10</v>
       </c>
       <c r="AW46" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX46" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AY46" t="n">
         <v>14</v>
@@ -12174,22 +12174,22 @@
         <v>17</v>
       </c>
       <c r="BA46" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB46" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC46" t="n">
         <v>5.9</v>
       </c>
-      <c r="BC46" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BD46" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE46" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF46" t="n">
         <v>6</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>5.8</v>
       </c>
       <c r="BG46" t="n">
         <v>19</v>
@@ -12216,7 +12216,7 @@
         <v>9.6</v>
       </c>
       <c r="BO46" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP46" t="n">
         <v>48</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -12287,13 +12287,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G47" t="n">
         <v>1000</v>
       </c>
       <c r="H47" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -12541,22 +12541,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.66</v>
+        <v>2.26</v>
       </c>
       <c r="G48" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H48" t="n">
         <v>3.15</v>
       </c>
-      <c r="H48" t="n">
-        <v>2.82</v>
-      </c>
       <c r="I48" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="J48" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K48" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L48" t="n">
         <v>1.44</v>
@@ -12565,22 +12565,22 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O48" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="P48" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="R48" t="n">
         <v>1.15</v>
       </c>
       <c r="S48" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T48" t="n">
         <v>1.11</v>
@@ -12589,10 +12589,10 @@
         <v>1.11</v>
       </c>
       <c r="V48" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="W48" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -12801,16 +12801,16 @@
         <v>2.28</v>
       </c>
       <c r="H49" t="n">
-        <v>1.87</v>
+        <v>3.45</v>
       </c>
       <c r="I49" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J49" t="n">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="K49" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L49" t="n">
         <v>1.01</v>
@@ -12819,16 +12819,16 @@
         <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O49" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="P49" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="R49" t="n">
         <v>1.08</v>
@@ -12843,25 +12843,25 @@
         <v>1.11</v>
       </c>
       <c r="V49" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W49" t="n">
         <v>1.78</v>
       </c>
       <c r="X49" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Z49" t="n">
         <v>50</v>
       </c>
       <c r="AA49" t="n">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="AB49" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC49" t="n">
         <v>9.800000000000001</v>
@@ -12870,7 +12870,7 @@
         <v>40</v>
       </c>
       <c r="AE49" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AF49" t="n">
         <v>13.5</v>
@@ -12903,7 +12903,7 @@
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AQ49" t="n">
         <v>7.2</v>
@@ -12912,10 +12912,10 @@
         <v>22</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AT49" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AU49" t="n">
         <v>6.4</v>
@@ -12924,7 +12924,7 @@
         <v>13.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>38</v>
+        <v>2.5</v>
       </c>
       <c r="AX49" t="n">
         <v>7.6</v>
@@ -12936,89 +12936,89 @@
         <v>17.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BB49" t="n">
         <v>17</v>
       </c>
       <c r="BC49" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD49" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BF49" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BG49" t="n">
-        <v>36</v>
+        <v>2.52</v>
       </c>
       <c r="BH49" t="n">
         <v>1000</v>
       </c>
       <c r="BI49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ49" t="n">
         <v>1000</v>
       </c>
       <c r="BK49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL49" t="n">
         <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN49" t="n">
         <v>1000</v>
       </c>
       <c r="BO49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP49" t="n">
         <v>1000</v>
       </c>
       <c r="BQ49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR49" t="n">
         <v>1000</v>
       </c>
       <c r="BS49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT49" t="n">
         <v>1000</v>
       </c>
       <c r="BU49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV49" t="n">
         <v>1000</v>
       </c>
       <c r="BW49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX49" t="n">
         <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ49" t="n">
         <v>1000</v>
       </c>
       <c r="CA49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -13049,19 +13049,19 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G50" t="n">
         <v>1000</v>
       </c>
       <c r="H50" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I50" t="n">
         <v>1000</v>
       </c>
       <c r="J50" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K50" t="n">
         <v>1000</v>
@@ -13097,10 +13097,10 @@
         <v>1.11</v>
       </c>
       <c r="V50" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W50" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X50" t="n">
         <v>1000</v>
@@ -13214,65 +13214,65 @@
         <v>1000</v>
       </c>
       <c r="BI50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ50" t="n">
         <v>1000</v>
       </c>
       <c r="BK50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL50" t="n">
         <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN50" t="n">
         <v>1000</v>
       </c>
       <c r="BO50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP50" t="n">
         <v>1000</v>
       </c>
       <c r="BQ50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR50" t="n">
         <v>1000</v>
       </c>
       <c r="BS50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT50" t="n">
         <v>1000</v>
       </c>
       <c r="BU50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV50" t="n">
         <v>1000</v>
       </c>
       <c r="BW50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX50" t="n">
         <v>1000</v>
       </c>
       <c r="BY50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ50" t="n">
         <v>1000</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -13303,19 +13303,19 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G51" t="n">
         <v>1000</v>
       </c>
       <c r="H51" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I51" t="n">
         <v>1000</v>
       </c>
       <c r="J51" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K51" t="n">
         <v>1000</v>
@@ -13351,10 +13351,10 @@
         <v>1.11</v>
       </c>
       <c r="V51" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W51" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X51" t="n">
         <v>1000</v>
@@ -13468,65 +13468,65 @@
         <v>1000</v>
       </c>
       <c r="BI51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ51" t="n">
         <v>1000</v>
       </c>
       <c r="BK51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN51" t="n">
         <v>1000</v>
       </c>
       <c r="BO51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP51" t="n">
         <v>1000</v>
       </c>
       <c r="BQ51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR51" t="n">
         <v>1000</v>
       </c>
       <c r="BS51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT51" t="n">
         <v>1000</v>
       </c>
       <c r="BU51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV51" t="n">
         <v>1000</v>
       </c>
       <c r="BW51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX51" t="n">
         <v>1000</v>
       </c>
       <c r="BY51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ51" t="n">
         <v>1000</v>
       </c>
       <c r="CA51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
         <v>3.6</v>
       </c>
       <c r="L52" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M52" t="n">
         <v>1.08</v>
@@ -13602,7 +13602,7 @@
         <v>1.81</v>
       </c>
       <c r="U52" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="V52" t="n">
         <v>1.53</v>
@@ -13722,55 +13722,55 @@
         <v>1000</v>
       </c>
       <c r="BI52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ52" t="n">
         <v>1000</v>
       </c>
       <c r="BK52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL52" t="n">
         <v>1000</v>
       </c>
       <c r="BM52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN52" t="n">
         <v>1000</v>
       </c>
       <c r="BO52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP52" t="n">
         <v>1000</v>
       </c>
       <c r="BQ52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR52" t="n">
         <v>1000</v>
       </c>
       <c r="BS52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT52" t="n">
         <v>1000</v>
       </c>
       <c r="BU52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV52" t="n">
         <v>1000</v>
       </c>
       <c r="BW52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX52" t="n">
         <v>1000</v>
       </c>
       <c r="BY52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ52" t="n">
         <v>0</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -13811,13 +13811,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G53" t="n">
         <v>1000</v>
       </c>
       <c r="H53" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="I53" t="n">
         <v>1000</v>
@@ -13976,55 +13976,55 @@
         <v>1000</v>
       </c>
       <c r="BI53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ53" t="n">
         <v>1000</v>
       </c>
       <c r="BK53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL53" t="n">
         <v>1000</v>
       </c>
       <c r="BM53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN53" t="n">
         <v>1000</v>
       </c>
       <c r="BO53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP53" t="n">
         <v>1000</v>
       </c>
       <c r="BQ53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR53" t="n">
         <v>1000</v>
       </c>
       <c r="BS53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT53" t="n">
         <v>1000</v>
       </c>
       <c r="BU53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV53" t="n">
         <v>1000</v>
       </c>
       <c r="BW53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX53" t="n">
         <v>1000</v>
       </c>
       <c r="BY53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ53" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -14065,22 +14065,22 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="G54" t="n">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="H54" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="I54" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J54" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="K54" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -14089,22 +14089,22 @@
         <v>1.01</v>
       </c>
       <c r="N54" t="n">
-        <v>1.26</v>
+        <v>2.46</v>
       </c>
       <c r="O54" t="n">
         <v>1.2</v>
       </c>
       <c r="P54" t="n">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.2</v>
+        <v>1.54</v>
       </c>
       <c r="R54" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="S54" t="n">
-        <v>1.2</v>
+        <v>2.32</v>
       </c>
       <c r="T54" t="n">
         <v>1.11</v>
@@ -14113,10 +14113,10 @@
         <v>1.11</v>
       </c>
       <c r="V54" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="W54" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="X54" t="n">
         <v>1000</v>
@@ -14230,65 +14230,65 @@
         <v>1000</v>
       </c>
       <c r="BI54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ54" t="n">
         <v>1000</v>
       </c>
       <c r="BK54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL54" t="n">
         <v>1000</v>
       </c>
       <c r="BM54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN54" t="n">
         <v>1000</v>
       </c>
       <c r="BO54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP54" t="n">
         <v>1000</v>
       </c>
       <c r="BQ54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR54" t="n">
         <v>1000</v>
       </c>
       <c r="BS54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT54" t="n">
         <v>1000</v>
       </c>
       <c r="BU54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV54" t="n">
         <v>1000</v>
       </c>
       <c r="BW54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX54" t="n">
         <v>1000</v>
       </c>
       <c r="BY54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ54" t="n">
         <v>1000</v>
       </c>
       <c r="CA54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
         <v>12.5</v>
       </c>
       <c r="AD55" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AE55" t="n">
         <v>190</v>
@@ -14484,19 +14484,19 @@
         <v>1000</v>
       </c>
       <c r="BI55" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BJ55" t="n">
         <v>17</v>
       </c>
       <c r="BK55" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="BL55" t="n">
         <v>1000</v>
       </c>
       <c r="BM55" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BN55" t="n">
         <v>5</v>
@@ -14508,41 +14508,41 @@
         <v>12.5</v>
       </c>
       <c r="BQ55" t="n">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="BR55" t="n">
         <v>38</v>
       </c>
       <c r="BS55" t="n">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="BT55" t="n">
         <v>17</v>
       </c>
       <c r="BU55" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="BV55" t="n">
         <v>1000</v>
       </c>
       <c r="BW55" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BX55" t="n">
         <v>1000</v>
       </c>
       <c r="BY55" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BZ55" t="n">
         <v>24</v>
       </c>
       <c r="CA55" t="n">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -14612,13 +14612,13 @@
         <v>1.27</v>
       </c>
       <c r="S56" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="T56" t="n">
         <v>1.83</v>
       </c>
       <c r="U56" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V56" t="n">
         <v>1.59</v>
@@ -14633,7 +14633,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z56" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA56" t="n">
         <v>44</v>
@@ -14690,7 +14690,7 @@
         <v>12</v>
       </c>
       <c r="AS56" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AT56" t="n">
         <v>9.6</v>
@@ -14702,10 +14702,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW56" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX56" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY56" t="n">
         <v>10.5</v>
@@ -14714,22 +14714,22 @@
         <v>14</v>
       </c>
       <c r="BA56" t="n">
-        <v>36</v>
+        <v>4.9</v>
       </c>
       <c r="BB56" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE56" t="n">
         <v>5.2</v>
       </c>
-      <c r="BC56" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BF56" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BG56" t="n">
         <v>20</v>
@@ -14738,65 +14738,65 @@
         <v>1000</v>
       </c>
       <c r="BI56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ56" t="n">
         <v>1000</v>
       </c>
       <c r="BK56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL56" t="n">
         <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN56" t="n">
         <v>1000</v>
       </c>
       <c r="BO56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP56" t="n">
         <v>1000</v>
       </c>
       <c r="BQ56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR56" t="n">
         <v>1000</v>
       </c>
       <c r="BS56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT56" t="n">
         <v>1000</v>
       </c>
       <c r="BU56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV56" t="n">
         <v>1000</v>
       </c>
       <c r="BW56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX56" t="n">
         <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ56" t="n">
         <v>1000</v>
       </c>
       <c r="CA56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -14836,7 +14836,7 @@
         <v>11</v>
       </c>
       <c r="I57" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J57" t="n">
         <v>5.5</v>
@@ -14875,7 +14875,7 @@
         <v>1.69</v>
       </c>
       <c r="V57" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W57" t="n">
         <v>3.7</v>
@@ -14887,13 +14887,13 @@
         <v>42</v>
       </c>
       <c r="Z57" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AA57" t="n">
         <v>1000</v>
       </c>
       <c r="AB57" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC57" t="n">
         <v>16.5</v>
@@ -14902,10 +14902,10 @@
         <v>55</v>
       </c>
       <c r="AE57" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AF57" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG57" t="n">
         <v>13.5</v>
@@ -14914,7 +14914,7 @@
         <v>42</v>
       </c>
       <c r="AI57" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AJ57" t="n">
         <v>12.5</v>
@@ -14932,19 +14932,19 @@
         <v>6.6</v>
       </c>
       <c r="AO57" t="n">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="AP57" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ57" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AR57" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AS57" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AT57" t="n">
         <v>7</v>
@@ -14953,10 +14953,10 @@
         <v>11</v>
       </c>
       <c r="AV57" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AW57" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AX57" t="n">
         <v>6.6</v>
@@ -14965,10 +14965,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ57" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BA57" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB57" t="n">
         <v>8.6</v>
@@ -14977,80 +14977,80 @@
         <v>13</v>
       </c>
       <c r="BD57" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BE57" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BF57" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BG57" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BH57" t="n">
         <v>1000</v>
       </c>
       <c r="BI57" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ57" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BK57" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL57" t="n">
         <v>1000</v>
       </c>
       <c r="BM57" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN57" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO57" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BP57" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ57" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BR57" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS57" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT57" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BU57" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV57" t="n">
         <v>1000</v>
       </c>
       <c r="BW57" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX57" t="n">
         <v>1000</v>
       </c>
       <c r="BY57" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ57" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA57" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
         <v>1.01</v>
       </c>
       <c r="N58" t="n">
-        <v>1.65</v>
+        <v>1.1</v>
       </c>
       <c r="O58" t="n">
         <v>1.04</v>
@@ -15117,7 +15117,7 @@
         <v>1.04</v>
       </c>
       <c r="R58" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="S58" t="n">
         <v>1.05</v>
@@ -15246,55 +15246,55 @@
         <v>1000</v>
       </c>
       <c r="BI58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ58" t="n">
         <v>1000</v>
       </c>
       <c r="BK58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL58" t="n">
         <v>1000</v>
       </c>
       <c r="BM58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN58" t="n">
         <v>1000</v>
       </c>
       <c r="BO58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP58" t="n">
         <v>1000</v>
       </c>
       <c r="BQ58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR58" t="n">
         <v>1000</v>
       </c>
       <c r="BS58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT58" t="n">
         <v>1000</v>
       </c>
       <c r="BU58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV58" t="n">
         <v>1000</v>
       </c>
       <c r="BW58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX58" t="n">
         <v>1000</v>
       </c>
       <c r="BY58" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ58" t="n">
         <v>0</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -15335,16 +15335,16 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="G59" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H59" t="n">
         <v>5.8</v>
       </c>
       <c r="I59" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="J59" t="n">
         <v>3.5</v>
@@ -15368,7 +15368,7 @@
         <v>1.65</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="R59" t="n">
         <v>1.23</v>
@@ -15377,16 +15377,16 @@
         <v>4.4</v>
       </c>
       <c r="T59" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U59" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V59" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W59" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X59" t="n">
         <v>13</v>
@@ -15398,7 +15398,7 @@
         <v>60</v>
       </c>
       <c r="AA59" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB59" t="n">
         <v>7.8</v>
@@ -15413,7 +15413,7 @@
         <v>140</v>
       </c>
       <c r="AF59" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG59" t="n">
         <v>12.5</v>
@@ -15431,13 +15431,13 @@
         <v>27</v>
       </c>
       <c r="AL59" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM59" t="n">
         <v>240</v>
       </c>
       <c r="AN59" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO59" t="n">
         <v>230</v>
@@ -15446,13 +15446,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ59" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR59" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AS59" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AT59" t="n">
         <v>5.7</v>
@@ -15464,7 +15464,7 @@
         <v>21</v>
       </c>
       <c r="AW59" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AX59" t="n">
         <v>7.8</v>
@@ -15476,7 +15476,7 @@
         <v>21</v>
       </c>
       <c r="BA59" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB59" t="n">
         <v>15.5</v>
@@ -15485,80 +15485,80 @@
         <v>18.5</v>
       </c>
       <c r="BD59" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE59" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF59" t="n">
         <v>11.5</v>
       </c>
       <c r="BG59" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH59" t="n">
         <v>1000</v>
       </c>
       <c r="BI59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ59" t="n">
         <v>1000</v>
       </c>
       <c r="BK59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL59" t="n">
         <v>1000</v>
       </c>
       <c r="BM59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN59" t="n">
         <v>1000</v>
       </c>
       <c r="BO59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP59" t="n">
         <v>1000</v>
       </c>
       <c r="BQ59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR59" t="n">
         <v>1000</v>
       </c>
       <c r="BS59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT59" t="n">
         <v>1000</v>
       </c>
       <c r="BU59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV59" t="n">
         <v>1000</v>
       </c>
       <c r="BW59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX59" t="n">
         <v>1000</v>
       </c>
       <c r="BY59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ59" t="n">
         <v>1000</v>
       </c>
       <c r="CA59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -15592,7 +15592,7 @@
         <v>1.94</v>
       </c>
       <c r="G60" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H60" t="n">
         <v>4.5</v>
@@ -15607,7 +15607,7 @@
         <v>3.5</v>
       </c>
       <c r="L60" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M60" t="n">
         <v>1.09</v>
@@ -15628,7 +15628,7 @@
         <v>1.26</v>
       </c>
       <c r="S60" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T60" t="n">
         <v>1.99</v>
@@ -15640,7 +15640,7 @@
         <v>1.24</v>
       </c>
       <c r="W60" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="X60" t="n">
         <v>13.5</v>
@@ -15652,7 +15652,7 @@
         <v>42</v>
       </c>
       <c r="AA60" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB60" t="n">
         <v>9.199999999999999</v>
@@ -15664,7 +15664,7 @@
         <v>24</v>
       </c>
       <c r="AE60" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF60" t="n">
         <v>14</v>
@@ -15736,7 +15736,7 @@
         <v>20</v>
       </c>
       <c r="BC60" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD60" t="n">
         <v>4.4</v>
@@ -15760,13 +15760,13 @@
         <v>13</v>
       </c>
       <c r="BK60" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BL60" t="n">
         <v>200</v>
       </c>
       <c r="BM60" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BN60" t="n">
         <v>5.3</v>
@@ -15778,41 +15778,41 @@
         <v>18</v>
       </c>
       <c r="BQ60" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BR60" t="n">
         <v>42</v>
       </c>
       <c r="BS60" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BT60" t="n">
         <v>9.4</v>
       </c>
       <c r="BU60" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BV60" t="n">
         <v>55</v>
       </c>
       <c r="BW60" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BX60" t="n">
         <v>70</v>
       </c>
       <c r="BY60" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ60" t="n">
         <v>40</v>
       </c>
       <c r="CA60" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -15885,7 +15885,7 @@
         <v>4.6</v>
       </c>
       <c r="T61" t="n">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="U61" t="n">
         <v>1.77</v>
@@ -15909,7 +15909,7 @@
         <v>25</v>
       </c>
       <c r="AB61" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC61" t="n">
         <v>8.4</v>
@@ -15984,22 +15984,22 @@
         <v>21</v>
       </c>
       <c r="BA61" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB61" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC61" t="n">
         <v>5.3</v>
       </c>
-      <c r="BC61" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BD61" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE61" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF61" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG61" t="n">
         <v>12.5</v>
@@ -16008,65 +16008,65 @@
         <v>1000</v>
       </c>
       <c r="BI61" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ61" t="n">
         <v>1000</v>
       </c>
       <c r="BK61" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL61" t="n">
         <v>1000</v>
       </c>
       <c r="BM61" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN61" t="n">
         <v>1000</v>
       </c>
       <c r="BO61" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP61" t="n">
         <v>1000</v>
       </c>
       <c r="BQ61" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR61" t="n">
         <v>1000</v>
       </c>
       <c r="BS61" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT61" t="n">
         <v>1000</v>
       </c>
       <c r="BU61" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV61" t="n">
         <v>1000</v>
       </c>
       <c r="BW61" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX61" t="n">
         <v>1000</v>
       </c>
       <c r="BY61" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ61" t="n">
         <v>1000</v>
       </c>
       <c r="CA61" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -16097,19 +16097,19 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G62" t="n">
         <v>1000</v>
       </c>
       <c r="H62" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I62" t="n">
         <v>1000</v>
       </c>
       <c r="J62" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K62" t="n">
         <v>1000</v>
@@ -16130,13 +16130,13 @@
         <v>1.25</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R62" t="n">
         <v>1.18</v>
       </c>
       <c r="S62" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="T62" t="n">
         <v>1.11</v>
@@ -16145,10 +16145,10 @@
         <v>1.11</v>
       </c>
       <c r="V62" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W62" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X62" t="n">
         <v>1000</v>
@@ -16205,52 +16205,52 @@
         <v>1000</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF62" t="n">
         <v>1.01</v>
@@ -16262,65 +16262,65 @@
         <v>1000</v>
       </c>
       <c r="BI62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ62" t="n">
         <v>1000</v>
       </c>
       <c r="BK62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL62" t="n">
         <v>1000</v>
       </c>
       <c r="BM62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN62" t="n">
         <v>1000</v>
       </c>
       <c r="BO62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP62" t="n">
         <v>1000</v>
       </c>
       <c r="BQ62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR62" t="n">
         <v>1000</v>
       </c>
       <c r="BS62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT62" t="n">
         <v>1000</v>
       </c>
       <c r="BU62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV62" t="n">
         <v>1000</v>
       </c>
       <c r="BW62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX62" t="n">
         <v>1000</v>
       </c>
       <c r="BY62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ62" t="n">
         <v>1000</v>
       </c>
       <c r="CA62" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -16351,19 +16351,19 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G63" t="n">
         <v>1000</v>
       </c>
       <c r="H63" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I63" t="n">
         <v>1000</v>
       </c>
       <c r="J63" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K63" t="n">
         <v>950</v>
@@ -16399,10 +16399,10 @@
         <v>1.11</v>
       </c>
       <c r="V63" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W63" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X63" t="n">
         <v>1000</v>
@@ -16459,52 +16459,52 @@
         <v>1000</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF63" t="n">
         <v>1.01</v>
@@ -16516,65 +16516,65 @@
         <v>1000</v>
       </c>
       <c r="BI63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ63" t="n">
         <v>1000</v>
       </c>
       <c r="BK63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL63" t="n">
         <v>1000</v>
       </c>
       <c r="BM63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN63" t="n">
         <v>1000</v>
       </c>
       <c r="BO63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP63" t="n">
         <v>1000</v>
       </c>
       <c r="BQ63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR63" t="n">
         <v>1000</v>
       </c>
       <c r="BS63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT63" t="n">
         <v>1000</v>
       </c>
       <c r="BU63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV63" t="n">
         <v>1000</v>
       </c>
       <c r="BW63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX63" t="n">
         <v>1000</v>
       </c>
       <c r="BY63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ63" t="n">
         <v>1000</v>
       </c>
       <c r="CA63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="G64" t="n">
         <v>600</v>
       </c>
       <c r="H64" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="I64" t="n">
         <v>1000</v>
@@ -16653,7 +16653,7 @@
         <v>1.11</v>
       </c>
       <c r="V64" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W64" t="n">
         <v>1.5</v>
@@ -16713,52 +16713,52 @@
         <v>1000</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE64" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF64" t="n">
         <v>1.01</v>
@@ -16770,65 +16770,65 @@
         <v>1000</v>
       </c>
       <c r="BI64" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ64" t="n">
         <v>1000</v>
       </c>
       <c r="BK64" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL64" t="n">
         <v>1000</v>
       </c>
       <c r="BM64" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN64" t="n">
         <v>1000</v>
       </c>
       <c r="BO64" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP64" t="n">
         <v>1000</v>
       </c>
       <c r="BQ64" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR64" t="n">
         <v>1000</v>
       </c>
       <c r="BS64" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT64" t="n">
         <v>1000</v>
       </c>
       <c r="BU64" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV64" t="n">
         <v>1000</v>
       </c>
       <c r="BW64" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX64" t="n">
         <v>1000</v>
       </c>
       <c r="BY64" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ64" t="n">
         <v>1000</v>
       </c>
       <c r="CA64" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -16886,7 +16886,7 @@
         <v>3.05</v>
       </c>
       <c r="O65" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P65" t="n">
         <v>2.06</v>
@@ -17024,65 +17024,65 @@
         <v>1000</v>
       </c>
       <c r="BI65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ65" t="n">
         <v>1000</v>
       </c>
       <c r="BK65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL65" t="n">
         <v>1000</v>
       </c>
       <c r="BM65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN65" t="n">
         <v>1000</v>
       </c>
       <c r="BO65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP65" t="n">
         <v>1000</v>
       </c>
       <c r="BQ65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR65" t="n">
         <v>1000</v>
       </c>
       <c r="BS65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT65" t="n">
         <v>1000</v>
       </c>
       <c r="BU65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV65" t="n">
         <v>1000</v>
       </c>
       <c r="BW65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX65" t="n">
         <v>1000</v>
       </c>
       <c r="BY65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ65" t="n">
         <v>1000</v>
       </c>
       <c r="CA65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -17116,7 +17116,7 @@
         <v>2.7</v>
       </c>
       <c r="G66" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="H66" t="n">
         <v>2.58</v>
@@ -17137,7 +17137,7 @@
         <v>1.01</v>
       </c>
       <c r="N66" t="n">
-        <v>1.79</v>
+        <v>2.8</v>
       </c>
       <c r="O66" t="n">
         <v>1.34</v>
@@ -17146,70 +17146,70 @@
         <v>1.78</v>
       </c>
       <c r="Q66" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R66" t="n">
         <v>1.18</v>
       </c>
       <c r="S66" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="T66" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="U66" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V66" t="n">
         <v>1.54</v>
       </c>
       <c r="W66" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="X66" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y66" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z66" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA66" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB66" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC66" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD66" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE66" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF66" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG66" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH66" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI66" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ66" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK66" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL66" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM66" t="n">
         <v>1000</v>
@@ -17221,122 +17221,122 @@
         <v>1000</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS66" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="AU66" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="AV66" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW66" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="AX66" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="AY66" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="AZ66" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BA66" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BB66" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BC66" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BD66" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BE66" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BF66" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BG66" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BH66" t="n">
         <v>1000</v>
       </c>
       <c r="BI66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ66" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL66" t="n">
         <v>1000</v>
       </c>
       <c r="BM66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN66" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO66" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP66" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR66" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT66" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU66" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV66" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX66" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ66" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA66" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -17367,61 +17367,61 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G67" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="H67" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I67" t="n">
         <v>7.8</v>
       </c>
       <c r="J67" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K67" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L67" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M67" t="n">
         <v>1.07</v>
       </c>
       <c r="N67" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O67" t="n">
         <v>1.33</v>
       </c>
       <c r="P67" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="R67" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S67" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T67" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="U67" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="V67" t="n">
         <v>1.14</v>
       </c>
       <c r="W67" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="X67" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y67" t="n">
         <v>23</v>
@@ -17430,76 +17430,76 @@
         <v>65</v>
       </c>
       <c r="AA67" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AB67" t="n">
         <v>8.6</v>
       </c>
       <c r="AC67" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF67" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>11</v>
       </c>
       <c r="AG67" t="n">
         <v>11.5</v>
       </c>
       <c r="AH67" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI67" t="n">
         <v>120</v>
       </c>
       <c r="AJ67" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK67" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL67" t="n">
         <v>48</v>
       </c>
       <c r="AM67" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN67" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AO67" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AP67" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ67" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR67" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT67" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW67" t="n">
         <v>5.9</v>
       </c>
-      <c r="AU67" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV67" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW67" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AX67" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AY67" t="n">
         <v>7.8</v>
@@ -17508,25 +17508,25 @@
         <v>18</v>
       </c>
       <c r="BA67" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BB67" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC67" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD67" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE67" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF67" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BG67" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH67" t="n">
         <v>1000</v>
@@ -17535,7 +17535,7 @@
         <v>1.04</v>
       </c>
       <c r="BJ67" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK67" t="n">
         <v>1.04</v>
@@ -17553,19 +17553,19 @@
         <v>1.04</v>
       </c>
       <c r="BP67" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ67" t="n">
         <v>1.04</v>
       </c>
       <c r="BR67" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS67" t="n">
         <v>1.04</v>
       </c>
       <c r="BT67" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BU67" t="n">
         <v>1.04</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -17645,7 +17645,7 @@
         <v>1.02</v>
       </c>
       <c r="N68" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O68" t="n">
         <v>1.07</v>
@@ -17663,10 +17663,10 @@
         <v>1.07</v>
       </c>
       <c r="T68" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U68" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V68" t="n">
         <v>1.01</v>
@@ -17786,55 +17786,55 @@
         <v>1000</v>
       </c>
       <c r="BI68" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ68" t="n">
         <v>1000</v>
       </c>
       <c r="BK68" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL68" t="n">
         <v>1000</v>
       </c>
       <c r="BM68" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN68" t="n">
         <v>1000</v>
       </c>
       <c r="BO68" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP68" t="n">
         <v>1000</v>
       </c>
       <c r="BQ68" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR68" t="n">
         <v>1000</v>
       </c>
       <c r="BS68" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT68" t="n">
         <v>1000</v>
       </c>
       <c r="BU68" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV68" t="n">
         <v>1000</v>
       </c>
       <c r="BW68" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX68" t="n">
         <v>1000</v>
       </c>
       <c r="BY68" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ68" t="n">
         <v>0</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -17878,22 +17878,22 @@
         <v>1.74</v>
       </c>
       <c r="G69" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="H69" t="n">
         <v>5.1</v>
       </c>
       <c r="I69" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J69" t="n">
         <v>3.4</v>
       </c>
       <c r="K69" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="L69" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="M69" t="n">
         <v>1.08</v>
@@ -17908,7 +17908,7 @@
         <v>1.71</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="R69" t="n">
         <v>1.26</v>
@@ -17917,16 +17917,16 @@
         <v>3.55</v>
       </c>
       <c r="T69" t="n">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="U69" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="V69" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W69" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="X69" t="n">
         <v>14.5</v>
@@ -17995,7 +17995,7 @@
         <v>4.2</v>
       </c>
       <c r="AT69" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AU69" t="n">
         <v>6.2</v>
@@ -18010,10 +18010,10 @@
         <v>7.6</v>
       </c>
       <c r="AY69" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ69" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BA69" t="n">
         <v>4.2</v>
@@ -18046,13 +18046,13 @@
         <v>13.5</v>
       </c>
       <c r="BK69" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BL69" t="n">
         <v>210</v>
       </c>
       <c r="BM69" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BN69" t="n">
         <v>5</v>
@@ -18064,41 +18064,41 @@
         <v>16</v>
       </c>
       <c r="BQ69" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BR69" t="n">
         <v>40</v>
       </c>
       <c r="BS69" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BT69" t="n">
         <v>10.5</v>
       </c>
       <c r="BU69" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV69" t="n">
         <v>65</v>
       </c>
       <c r="BW69" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BX69" t="n">
         <v>80</v>
       </c>
       <c r="BY69" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BZ69" t="n">
         <v>36</v>
       </c>
       <c r="CA69" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -18129,10 +18129,10 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="G70" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H70" t="n">
         <v>3.95</v>
@@ -18144,7 +18144,7 @@
         <v>3.25</v>
       </c>
       <c r="K70" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="L70" t="n">
         <v>1.01</v>
@@ -18153,13 +18153,13 @@
         <v>1.01</v>
       </c>
       <c r="N70" t="n">
-        <v>1.1</v>
+        <v>2.32</v>
       </c>
       <c r="O70" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P70" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="Q70" t="n">
         <v>2.16</v>
@@ -18177,10 +18177,10 @@
         <v>1.11</v>
       </c>
       <c r="V70" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="W70" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X70" t="n">
         <v>1000</v>
@@ -18294,65 +18294,65 @@
         <v>1000</v>
       </c>
       <c r="BI70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ70" t="n">
         <v>1000</v>
       </c>
       <c r="BK70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL70" t="n">
         <v>1000</v>
       </c>
       <c r="BM70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN70" t="n">
         <v>1000</v>
       </c>
       <c r="BO70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP70" t="n">
         <v>1000</v>
       </c>
       <c r="BQ70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR70" t="n">
         <v>1000</v>
       </c>
       <c r="BS70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT70" t="n">
         <v>1000</v>
       </c>
       <c r="BU70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV70" t="n">
         <v>1000</v>
       </c>
       <c r="BW70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX70" t="n">
         <v>1000</v>
       </c>
       <c r="BY70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ70" t="n">
         <v>1000</v>
       </c>
       <c r="CA70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -18404,7 +18404,7 @@
         <v>1.01</v>
       </c>
       <c r="M71" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N71" t="n">
         <v>3.65</v>
@@ -18416,7 +18416,7 @@
         <v>1.93</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R71" t="n">
         <v>1.34</v>
@@ -18428,7 +18428,7 @@
         <v>2.1</v>
       </c>
       <c r="U71" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V71" t="n">
         <v>1.11</v>
@@ -18449,7 +18449,7 @@
         <v>420</v>
       </c>
       <c r="AB71" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC71" t="n">
         <v>11</v>
@@ -18464,7 +18464,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AG71" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH71" t="n">
         <v>30</v>
@@ -18497,10 +18497,10 @@
         <v>22</v>
       </c>
       <c r="AR71" t="n">
-        <v>10.5</v>
+        <v>65</v>
       </c>
       <c r="AS71" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AT71" t="n">
         <v>6.4</v>
@@ -18512,7 +18512,7 @@
         <v>30</v>
       </c>
       <c r="AW71" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AX71" t="n">
         <v>7</v>
@@ -18524,7 +18524,7 @@
         <v>25</v>
       </c>
       <c r="BA71" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BB71" t="n">
         <v>11</v>
@@ -18536,77 +18536,77 @@
         <v>36</v>
       </c>
       <c r="BE71" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BF71" t="n">
         <v>7.2</v>
       </c>
       <c r="BG71" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BH71" t="n">
         <v>1000</v>
       </c>
       <c r="BI71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ71" t="n">
         <v>1000</v>
       </c>
       <c r="BK71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL71" t="n">
         <v>1000</v>
       </c>
       <c r="BM71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN71" t="n">
         <v>1000</v>
       </c>
       <c r="BO71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP71" t="n">
         <v>1000</v>
       </c>
       <c r="BQ71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR71" t="n">
         <v>1000</v>
       </c>
       <c r="BS71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT71" t="n">
         <v>1000</v>
       </c>
       <c r="BU71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV71" t="n">
         <v>1000</v>
       </c>
       <c r="BW71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX71" t="n">
         <v>1000</v>
       </c>
       <c r="BY71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ71" t="n">
         <v>1000</v>
       </c>
       <c r="CA71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -18802,65 +18802,65 @@
         <v>1000</v>
       </c>
       <c r="BI72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ72" t="n">
         <v>1000</v>
       </c>
       <c r="BK72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL72" t="n">
         <v>1000</v>
       </c>
       <c r="BM72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN72" t="n">
         <v>1000</v>
       </c>
       <c r="BO72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP72" t="n">
         <v>1000</v>
       </c>
       <c r="BQ72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR72" t="n">
         <v>1000</v>
       </c>
       <c r="BS72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT72" t="n">
         <v>1000</v>
       </c>
       <c r="BU72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV72" t="n">
         <v>1000</v>
       </c>
       <c r="BW72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX72" t="n">
         <v>1000</v>
       </c>
       <c r="BY72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ72" t="n">
         <v>1000</v>
       </c>
       <c r="CA72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -18894,7 +18894,7 @@
         <v>1.78</v>
       </c>
       <c r="G73" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H73" t="n">
         <v>4.6</v>
@@ -18903,19 +18903,19 @@
         <v>5.5</v>
       </c>
       <c r="J73" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K73" t="n">
         <v>4</v>
       </c>
       <c r="L73" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M73" t="n">
         <v>1.08</v>
       </c>
       <c r="N73" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O73" t="n">
         <v>1.36</v>
@@ -18933,10 +18933,10 @@
         <v>3.75</v>
       </c>
       <c r="T73" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U73" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V73" t="n">
         <v>1.22</v>
@@ -18999,7 +18999,7 @@
         <v>120</v>
       </c>
       <c r="AP73" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ73" t="n">
         <v>11.5</v>
@@ -19056,65 +19056,65 @@
         <v>1000</v>
       </c>
       <c r="BI73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ73" t="n">
         <v>1000</v>
       </c>
       <c r="BK73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL73" t="n">
         <v>1000</v>
       </c>
       <c r="BM73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN73" t="n">
         <v>1000</v>
       </c>
       <c r="BO73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP73" t="n">
         <v>1000</v>
       </c>
       <c r="BQ73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR73" t="n">
         <v>1000</v>
       </c>
       <c r="BS73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT73" t="n">
         <v>1000</v>
       </c>
       <c r="BU73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV73" t="n">
         <v>1000</v>
       </c>
       <c r="BW73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX73" t="n">
         <v>1000</v>
       </c>
       <c r="BY73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ73" t="n">
         <v>1000</v>
       </c>
       <c r="CA73" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -19145,7 +19145,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G74" t="n">
         <v>2.56</v>
@@ -19154,7 +19154,7 @@
         <v>2.96</v>
       </c>
       <c r="I74" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J74" t="n">
         <v>3.55</v>
@@ -19169,7 +19169,7 @@
         <v>1.01</v>
       </c>
       <c r="N74" t="n">
-        <v>2.06</v>
+        <v>1.1</v>
       </c>
       <c r="O74" t="n">
         <v>1.28</v>
@@ -19181,19 +19181,19 @@
         <v>1.83</v>
       </c>
       <c r="R74" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S74" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T74" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U74" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V74" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W74" t="n">
         <v>1.64</v>
@@ -19247,128 +19247,128 @@
         <v>100</v>
       </c>
       <c r="AN74" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO74" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP74" t="n">
-        <v>2.48</v>
+        <v>2.96</v>
       </c>
       <c r="AQ74" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR74" t="n">
-        <v>2.54</v>
+        <v>3.05</v>
       </c>
       <c r="AS74" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="AT74" t="n">
-        <v>2.38</v>
+        <v>2.84</v>
       </c>
       <c r="AU74" t="n">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="AV74" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW74" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AX74" t="n">
         <v>12</v>
       </c>
       <c r="AY74" t="n">
-        <v>2.38</v>
+        <v>2.84</v>
       </c>
       <c r="AZ74" t="n">
-        <v>2.48</v>
+        <v>2.98</v>
       </c>
       <c r="BA74" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="BB74" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="BC74" t="n">
         <v>18</v>
       </c>
       <c r="BD74" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="BE74" t="n">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="BF74" t="n">
-        <v>2.8</v>
+        <v>12</v>
       </c>
       <c r="BG74" t="n">
-        <v>2.8</v>
+        <v>17.5</v>
       </c>
       <c r="BH74" t="n">
         <v>1000</v>
       </c>
       <c r="BI74" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ74" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK74" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL74" t="n">
         <v>1000</v>
       </c>
       <c r="BM74" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN74" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO74" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP74" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ74" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR74" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS74" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT74" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU74" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV74" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW74" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX74" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY74" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ74" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA74" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -19417,10 +19417,10 @@
         <v>4.4</v>
       </c>
       <c r="L75" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="M75" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N75" t="n">
         <v>3.55</v>
@@ -19441,61 +19441,61 @@
         <v>3.5</v>
       </c>
       <c r="T75" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U75" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V75" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W75" t="n">
         <v>2.16</v>
       </c>
       <c r="X75" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y75" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="Z75" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AA75" t="n">
         <v>170</v>
       </c>
       <c r="AB75" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AC75" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD75" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE75" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AF75" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AG75" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH75" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AI75" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ75" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AK75" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AL75" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AM75" t="n">
         <v>150</v>
@@ -19513,10 +19513,10 @@
         <v>15</v>
       </c>
       <c r="AR75" t="n">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="AS75" t="n">
-        <v>9.6</v>
+        <v>4.2</v>
       </c>
       <c r="AT75" t="n">
         <v>7.2</v>
@@ -19528,7 +19528,7 @@
         <v>18</v>
       </c>
       <c r="AW75" t="n">
-        <v>9</v>
+        <v>4.1</v>
       </c>
       <c r="AX75" t="n">
         <v>9.4</v>
@@ -19537,28 +19537,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ75" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="BA75" t="n">
-        <v>9</v>
+        <v>4.1</v>
       </c>
       <c r="BB75" t="n">
-        <v>6.6</v>
+        <v>3.65</v>
       </c>
       <c r="BC75" t="n">
-        <v>6.6</v>
+        <v>3.7</v>
       </c>
       <c r="BD75" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BE75" t="n">
-        <v>9.6</v>
+        <v>4.2</v>
       </c>
       <c r="BF75" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG75" t="n">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="BH75" t="n">
         <v>3.9</v>
@@ -19570,13 +19570,13 @@
         <v>12.5</v>
       </c>
       <c r="BK75" t="n">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="BL75" t="n">
         <v>170</v>
       </c>
       <c r="BM75" t="n">
-        <v>21</v>
+        <v>4.7</v>
       </c>
       <c r="BN75" t="n">
         <v>5.1</v>
@@ -19588,41 +19588,41 @@
         <v>15</v>
       </c>
       <c r="BQ75" t="n">
-        <v>9</v>
+        <v>3.65</v>
       </c>
       <c r="BR75" t="n">
         <v>34</v>
       </c>
       <c r="BS75" t="n">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="BT75" t="n">
         <v>10.5</v>
       </c>
       <c r="BU75" t="n">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="BV75" t="n">
         <v>60</v>
       </c>
       <c r="BW75" t="n">
-        <v>32</v>
+        <v>4.5</v>
       </c>
       <c r="BX75" t="n">
         <v>70</v>
       </c>
       <c r="BY75" t="n">
-        <v>38</v>
+        <v>4.5</v>
       </c>
       <c r="BZ75" t="n">
         <v>29</v>
       </c>
       <c r="CA75" t="n">
-        <v>17</v>
+        <v>4.1</v>
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-18.xlsx
@@ -875,212 +875,212 @@
         <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T2" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U2" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W2" t="n">
         <v>2.32</v>
       </c>
       <c r="X2" t="n">
-        <v>18.5</v>
+        <v>950</v>
       </c>
       <c r="Y2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA2" t="n">
         <v>140</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AF2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG2" t="n">
         <v>9.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AJ2" t="n">
         <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>19.5</v>
+        <v>870</v>
       </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AM2" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AP2" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR2" t="n">
         <v>17</v>
       </c>
-      <c r="AR2" t="n">
-        <v>32</v>
-      </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV2" t="n">
         <v>17</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="AX2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY2" t="n">
         <v>9</v>
       </c>
-      <c r="AY2" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC2" t="n">
         <v>14.5</v>
       </c>
-      <c r="BC2" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BD2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BI2" t="n">
         <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="BK2" t="n">
         <v>1.04</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>75</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO2" t="n">
         <v>1.04</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="BQ2" t="n">
         <v>1.04</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BS2" t="n">
         <v>1.04</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="BU2" t="n">
         <v>1.04</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="BW2" t="n">
         <v>1.04</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BY2" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="CA2" t="n">
         <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.68</v>
+        <v>3.4</v>
       </c>
       <c r="G3" t="n">
         <v>22</v>
@@ -1120,22 +1120,22 @@
         <v>1.61</v>
       </c>
       <c r="I3" t="n">
-        <v>2.98</v>
+        <v>2.28</v>
       </c>
       <c r="J3" t="n">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="K3" t="n">
         <v>8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O3" t="n">
         <v>1.46</v>
@@ -1159,7 +1159,7 @@
         <v>1.45</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="W3" t="n">
         <v>1.17</v>
@@ -1273,68 +1273,68 @@
         <v>1.26</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BI3" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="BK3" t="n">
         <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BM3" t="n">
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO3" t="n">
         <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BQ3" t="n">
         <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="BS3" t="n">
         <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BU3" t="n">
         <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BW3" t="n">
         <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="BY3" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="CA3" t="n">
         <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>3.25</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I4" t="n">
         <v>2.76</v>
@@ -1386,19 +1386,19 @@
         <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O4" t="n">
         <v>1.55</v>
       </c>
       <c r="P4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="R4" t="n">
         <v>1.19</v>
@@ -1410,7 +1410,7 @@
         <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V4" t="n">
         <v>1.56</v>
@@ -1419,13 +1419,13 @@
         <v>1.44</v>
       </c>
       <c r="X4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA4" t="n">
         <v>50</v>
@@ -1473,7 +1473,7 @@
         <v>46</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
         <v>7.6</v>
@@ -1494,13 +1494,13 @@
         <v>12</v>
       </c>
       <c r="AW4" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AX4" t="n">
         <v>17</v>
       </c>
       <c r="AY4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ4" t="n">
         <v>21</v>
@@ -1521,7 +1521,7 @@
         <v>70</v>
       </c>
       <c r="BF4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BG4" t="n">
         <v>34</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G5" t="n">
         <v>3.55</v>
@@ -1628,7 +1628,7 @@
         <v>2.44</v>
       </c>
       <c r="I5" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
         <v>3.2</v>
@@ -1643,16 +1643,16 @@
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P5" t="n">
         <v>1.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
         <v>1.23</v>
@@ -1664,10 +1664,10 @@
         <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="V5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W5" t="n">
         <v>1.39</v>
@@ -1679,7 +1679,7 @@
         <v>8.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA5" t="n">
         <v>36</v>
@@ -1691,7 +1691,7 @@
         <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE5" t="n">
         <v>34</v>
@@ -1712,7 +1712,7 @@
         <v>75</v>
       </c>
       <c r="AK5" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AL5" t="n">
         <v>80</v>
@@ -1724,10 +1724,10 @@
         <v>65</v>
       </c>
       <c r="AO5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.8</v>
@@ -1742,10 +1742,10 @@
         <v>9.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
         <v>27</v>
@@ -1760,10 +1760,10 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC5" t="n">
         <v>40</v>
@@ -1775,10 +1775,10 @@
         <v>48</v>
       </c>
       <c r="BF5" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BG5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -1876,22 +1876,22 @@
         <v>2.56</v>
       </c>
       <c r="G6" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H6" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I6" t="n">
         <v>3.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1900,7 +1900,7 @@
         <v>3.85</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P6" t="n">
         <v>1.92</v>
@@ -1912,16 +1912,16 @@
         <v>1.37</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
         <v>1.61</v>
@@ -1939,7 +1939,7 @@
         <v>55</v>
       </c>
       <c r="AB6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
         <v>7.6</v>
@@ -1951,7 +1951,7 @@
         <v>34</v>
       </c>
       <c r="AF6" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG6" t="n">
         <v>12</v>
@@ -1996,7 +1996,7 @@
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
         <v>12</v>
@@ -2029,10 +2029,10 @@
         <v>36</v>
       </c>
       <c r="BF6" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>1.88</v>
       </c>
       <c r="G7" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="H7" t="n">
         <v>4.6</v>
@@ -2148,43 +2148,43 @@
         <v>1.17</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
         <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="U7" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="V7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
         <v>2.04</v>
       </c>
       <c r="X7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z7" t="n">
         <v>48</v>
@@ -2196,22 +2196,22 @@
         <v>8.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
         <v>310</v>
       </c>
       <c r="AF7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG7" t="n">
         <v>11</v>
       </c>
-      <c r="AG7" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
         <v>310</v>
@@ -2235,7 +2235,7 @@
         <v>260</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
         <v>13</v>
@@ -2244,16 +2244,16 @@
         <v>23</v>
       </c>
       <c r="AS7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW7" t="n">
         <v>44</v>
@@ -2265,25 +2265,25 @@
         <v>9.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA7" t="n">
         <v>46</v>
       </c>
       <c r="BB7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC7" t="n">
         <v>17.5</v>
       </c>
-      <c r="BC7" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BD7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BE7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG7" t="n">
         <v>46</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.68</v>
+        <v>1.93</v>
       </c>
       <c r="G8" t="n">
         <v>5.2</v>
@@ -2390,13 +2390,13 @@
         <v>2.36</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="J8" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="K8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2429,10 +2429,10 @@
         <v>1.57</v>
       </c>
       <c r="V8" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="G9" t="n">
-        <v>4.3</v>
+        <v>15.5</v>
       </c>
       <c r="H9" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="I9" t="n">
         <v>2.58</v>
@@ -2653,7 +2653,7 @@
         <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
@@ -2677,16 +2677,16 @@
         <v>1.05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
         <v>1.63</v>
       </c>
       <c r="W9" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
         <v>2.44</v>
       </c>
       <c r="I11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J11" t="n">
         <v>2.92</v>
@@ -3185,7 +3185,7 @@
         <v>1.05</v>
       </c>
       <c r="T11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="U11" t="n">
         <v>1.83</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="H12" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L12" t="n">
         <v>1.11</v>
@@ -3421,142 +3421,142 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>2.18</v>
+        <v>4.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.26</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>1.05</v>
+        <v>2.96</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U12" t="n">
         <v>2.38</v>
       </c>
       <c r="V12" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="AB12" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
-        <v>210</v>
+        <v>65</v>
       </c>
       <c r="AF12" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>290</v>
+        <v>130</v>
       </c>
       <c r="AJ12" t="n">
-        <v>900</v>
+        <v>44</v>
       </c>
       <c r="AK12" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AL12" t="n">
-        <v>290</v>
+        <v>70</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.34</v>
+        <v>13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.26</v>
+        <v>12.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.32</v>
+        <v>16.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.33</v>
+        <v>28</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.34</v>
+        <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.31</v>
+        <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.32</v>
+        <v>27</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.32</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.27</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.33</v>
+        <v>32</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.33</v>
+        <v>23</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.31</v>
+        <v>18.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.32</v>
+        <v>27</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.34</v>
+        <v>34</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.55</v>
+        <v>13</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.55</v>
+        <v>20</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G13" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="H13" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J13" t="n">
         <v>3.75</v>
@@ -3675,13 +3675,13 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O13" t="n">
         <v>1.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="Q13" t="n">
         <v>1.72</v>
@@ -3690,28 +3690,28 @@
         <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T13" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U13" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W13" t="n">
         <v>1.51</v>
       </c>
       <c r="X13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y13" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA13" t="n">
         <v>55</v>
@@ -3720,43 +3720,43 @@
         <v>16</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF13" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AG13" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI13" t="n">
         <v>50</v>
       </c>
       <c r="AJ13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM13" t="n">
         <v>150</v>
       </c>
-      <c r="AK13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>190</v>
-      </c>
       <c r="AN13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AP13" t="n">
         <v>17</v>
@@ -3765,52 +3765,52 @@
         <v>11.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AT13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU13" t="n">
         <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BB13" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BC13" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BE13" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BF13" t="n">
         <v>16</v>
       </c>
       <c r="BG13" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -3944,10 +3944,10 @@
         <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U14" t="n">
         <v>1.24</v>
@@ -4016,10 +4016,10 @@
         <v>1.16</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AS14" t="n">
         <v>1.14</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="G15" t="n">
         <v>19</v>
@@ -4168,7 +4168,7 @@
         <v>1.67</v>
       </c>
       <c r="I15" t="n">
-        <v>2.74</v>
+        <v>2.46</v>
       </c>
       <c r="J15" t="n">
         <v>2.66</v>
@@ -4204,13 +4204,13 @@
         <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V15" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X15" t="n">
         <v>970</v>
@@ -4225,7 +4225,7 @@
         <v>140</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC15" t="n">
         <v>1000</v>
@@ -4276,43 +4276,43 @@
         <v>5.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AT15" t="n">
         <v>1.3</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AV15" t="n">
         <v>6.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AX15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>1.28</v>
       </c>
-      <c r="AY15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.27</v>
-      </c>
       <c r="BA15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BF15" t="n">
         <v>1.55</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>1.76</v>
       </c>
       <c r="G16" t="n">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="H16" t="n">
         <v>1.64</v>
@@ -4425,7 +4425,7 @@
         <v>3.7</v>
       </c>
       <c r="J16" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="K16" t="n">
         <v>7</v>
@@ -4437,7 +4437,7 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>2.16</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.26</v>
@@ -4446,25 +4446,25 @@
         <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="R16" t="n">
         <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="T16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="U16" t="n">
         <v>1.87</v>
       </c>
       <c r="V16" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -4497,7 +4497,7 @@
         <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>970</v>
+        <v>200</v>
       </c>
       <c r="AI16" t="n">
         <v>300</v>
@@ -4521,52 +4521,52 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AZ16" t="n">
         <v>1.11</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="BF16" t="n">
         <v>1.55</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="G17" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I17" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J17" t="n">
         <v>3.25</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.17</v>
@@ -4700,13 +4700,13 @@
         <v>1.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R17" t="n">
         <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="T17" t="n">
         <v>1.43</v>
@@ -4715,10 +4715,10 @@
         <v>1.72</v>
       </c>
       <c r="V17" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="W17" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X17" t="n">
         <v>970</v>
@@ -4778,49 +4778,49 @@
         <v>5.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AT17" t="n">
         <v>4.9</v>
       </c>
       <c r="AU17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AV17" t="n">
         <v>1.3</v>
       </c>
-      <c r="AV17" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AW17" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AX17" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="AY17" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BA17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BC17" t="n">
         <v>1.3</v>
       </c>
-      <c r="BB17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.28</v>
-      </c>
       <c r="BD17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="BF17" t="n">
         <v>1.55</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="G18" t="n">
         <v>2.38</v>
       </c>
       <c r="H18" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="I18" t="n">
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>2.14</v>
+        <v>2.58</v>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -4945,7 +4945,7 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="O18" t="n">
         <v>1.44</v>
@@ -4960,7 +4960,7 @@
         <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>1.05</v>
+        <v>1.83</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -4972,7 +4972,7 @@
         <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="X18" t="n">
         <v>970</v>
@@ -5005,7 +5005,7 @@
         <v>970</v>
       </c>
       <c r="AH18" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
@@ -5065,7 +5065,7 @@
         <v>1.24</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.23</v>
+        <v>2.5</v>
       </c>
       <c r="BC18" t="n">
         <v>1.22</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="G19" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="H19" t="n">
         <v>2.84</v>
@@ -5187,10 +5187,10 @@
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="K19" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5199,13 +5199,13 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.02</v>
       </c>
       <c r="P19" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Q19" t="n">
         <v>1.46</v>
@@ -5214,19 +5214,19 @@
         <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
         <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -5241,7 +5241,7 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AC19" t="n">
         <v>1000</v>
@@ -5253,88 +5253,88 @@
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -5429,19 +5429,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>4.5</v>
+        <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>2.14</v>
+        <v>2.66</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="K20" t="n">
         <v>5</v>
@@ -5453,13 +5453,13 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O20" t="n">
         <v>1.48</v>
       </c>
       <c r="P20" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
         <v>1.48</v>
@@ -5468,13 +5468,13 @@
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
         <v>1.23</v>
@@ -5486,46 +5486,46 @@
         <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AC20" t="n">
         <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
@@ -5537,52 +5537,52 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BF20" t="n">
         <v>1.55</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -5683,16 +5683,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G21" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H21" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I21" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J21" t="n">
         <v>4</v>
@@ -5716,28 +5716,28 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="R21" t="n">
         <v>1.78</v>
       </c>
       <c r="S21" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T21" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="U21" t="n">
         <v>3.05</v>
       </c>
       <c r="V21" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W21" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X21" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="Y21" t="n">
         <v>28</v>
@@ -5746,49 +5746,49 @@
         <v>38</v>
       </c>
       <c r="AA21" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AB21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC21" t="n">
         <v>12</v>
       </c>
       <c r="AD21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI21" t="n">
         <v>42</v>
       </c>
       <c r="AJ21" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
         <v>34</v>
       </c>
       <c r="AM21" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AN21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AP21" t="n">
         <v>25</v>
@@ -5803,13 +5803,13 @@
         <v>25</v>
       </c>
       <c r="AT21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU21" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW21" t="n">
         <v>17.5</v>
@@ -5818,16 +5818,16 @@
         <v>16</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ21" t="n">
         <v>11</v>
       </c>
       <c r="BA21" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BB21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC21" t="n">
         <v>15.5</v>
@@ -5839,7 +5839,7 @@
         <v>25</v>
       </c>
       <c r="BF21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG21" t="n">
         <v>12</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G22" t="n">
         <v>1.58</v>
@@ -5970,13 +5970,13 @@
         <v>2.78</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="R22" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S22" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="T22" t="n">
         <v>1.62</v>
@@ -6045,40 +6045,40 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AX22" t="n">
         <v>8.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="BB22" t="n">
         <v>10.5</v>
@@ -6087,16 +6087,16 @@
         <v>10</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -6194,16 +6194,16 @@
         <v>1.82</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>2.64</v>
       </c>
       <c r="H23" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="I23" t="n">
-        <v>870</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="K23" t="n">
         <v>6.6</v>
@@ -6215,7 +6215,7 @@
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>1.87</v>
+        <v>1.1</v>
       </c>
       <c r="O23" t="n">
         <v>1.3</v>
@@ -6227,16 +6227,16 @@
         <v>1.52</v>
       </c>
       <c r="R23" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S23" t="n">
-        <v>1.52</v>
+        <v>2.58</v>
       </c>
       <c r="T23" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U23" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="V23" t="n">
         <v>1.2</v>
@@ -6293,7 +6293,7 @@
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>970</v>
+        <v>600</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
@@ -6302,7 +6302,7 @@
         <v>1.34</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.26</v>
+        <v>2.5</v>
       </c>
       <c r="AR23" t="n">
         <v>1.33</v>
@@ -6311,7 +6311,7 @@
         <v>1.34</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU23" t="n">
         <v>1.34</v>
@@ -6323,10 +6323,10 @@
         <v>1.34</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.31</v>
+        <v>6.4</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.29</v>
+        <v>7</v>
       </c>
       <c r="AZ23" t="n">
         <v>1.31</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -6457,10 +6457,10 @@
         <v>3.75</v>
       </c>
       <c r="J24" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -6475,7 +6475,7 @@
         <v>1.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q24" t="n">
         <v>1.61</v>
@@ -6484,13 +6484,13 @@
         <v>1.59</v>
       </c>
       <c r="S24" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T24" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="U24" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V24" t="n">
         <v>1.37</v>
@@ -6511,10 +6511,10 @@
         <v>150</v>
       </c>
       <c r="AB24" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AD24" t="n">
         <v>17.5</v>
@@ -6547,10 +6547,10 @@
         <v>65</v>
       </c>
       <c r="AN24" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AP24" t="n">
         <v>19</v>
@@ -6559,10 +6559,10 @@
         <v>17.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AS24" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AT24" t="n">
         <v>12.5</v>
@@ -6592,19 +6592,19 @@
         <v>23</v>
       </c>
       <c r="BC24" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD24" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BE24" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BF24" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
         <v>3.45</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M25" t="n">
         <v>1.07</v>
@@ -6729,7 +6729,7 @@
         <v>1.35</v>
       </c>
       <c r="P25" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q25" t="n">
         <v>2.04</v>
@@ -6741,7 +6741,7 @@
         <v>3.85</v>
       </c>
       <c r="T25" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U25" t="n">
         <v>2.12</v>
@@ -6753,7 +6753,7 @@
         <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y25" t="n">
         <v>9.800000000000001</v>
@@ -6783,7 +6783,7 @@
         <v>16.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
         <v>80</v>
@@ -6804,13 +6804,13 @@
         <v>85</v>
       </c>
       <c r="AO25" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP25" t="n">
         <v>11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR25" t="n">
         <v>12</v>
@@ -6831,34 +6831,34 @@
         <v>21</v>
       </c>
       <c r="AX25" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AY25" t="n">
         <v>14</v>
       </c>
       <c r="AZ25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA25" t="n">
         <v>34</v>
       </c>
       <c r="BB25" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BC25" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="BD25" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BE25" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BF25" t="n">
         <v>40</v>
       </c>
       <c r="BG25" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -6959,16 +6959,16 @@
         <v>9.6</v>
       </c>
       <c r="H26" t="n">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="I26" t="n">
-        <v>110</v>
+        <v>5.3</v>
       </c>
       <c r="J26" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="K26" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6977,10 +6977,10 @@
         <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O26" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P26" t="n">
         <v>1.46</v>
@@ -6989,22 +6989,22 @@
         <v>1.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S26" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T26" t="n">
         <v>1.41</v>
       </c>
       <c r="U26" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V26" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="W26" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -7067,7 +7067,7 @@
         <v>1.14</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AS26" t="n">
         <v>1.15</v>
@@ -7088,13 +7088,13 @@
         <v>1.14</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AZ26" t="n">
         <v>1.14</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BB26" t="n">
         <v>1.15</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -7210,64 +7210,64 @@
         <v>2.32</v>
       </c>
       <c r="G27" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H27" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I27" t="n">
         <v>3.35</v>
       </c>
       <c r="J27" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K27" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M27" t="n">
         <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O27" t="n">
         <v>1.25</v>
       </c>
       <c r="P27" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="R27" t="n">
         <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="T27" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U27" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V27" t="n">
         <v>1.43</v>
       </c>
       <c r="W27" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y27" t="n">
         <v>16</v>
       </c>
       <c r="Z27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA27" t="n">
         <v>210</v>
@@ -7276,34 +7276,34 @@
         <v>13.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG27" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI27" t="n">
         <v>95</v>
       </c>
       <c r="AJ27" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK27" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL27" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM27" t="n">
         <v>190</v>
@@ -7312,61 +7312,61 @@
         <v>15.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AP27" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV27" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV27" t="n">
+      <c r="AW27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>12.5</v>
       </c>
-      <c r="AW27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>12</v>
-      </c>
       <c r="BA27" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BB27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC27" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BE27" t="n">
         <v>46</v>
       </c>
       <c r="BF27" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -7470,13 +7470,13 @@
         <v>3.2</v>
       </c>
       <c r="I28" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="J28" t="n">
         <v>2.52</v>
       </c>
       <c r="K28" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="L28" t="n">
         <v>1.15</v>
@@ -7485,7 +7485,7 @@
         <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>1.48</v>
+        <v>1.1</v>
       </c>
       <c r="O28" t="n">
         <v>1.35</v>
@@ -7497,10 +7497,10 @@
         <v>1.63</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="T28" t="n">
         <v>1.53</v>
@@ -7518,7 +7518,7 @@
         <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z28" t="n">
         <v>140</v>
@@ -7569,52 +7569,52 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.15</v>
       </c>
       <c r="AR28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AX28" t="n">
         <v>1.14</v>
       </c>
-      <c r="AS28" t="n">
+      <c r="AY28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BB28" t="n">
         <v>1.15</v>
       </c>
-      <c r="AT28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AU28" t="n">
+      <c r="BC28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BD28" t="n">
         <v>1.15</v>
       </c>
-      <c r="AV28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BE28" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BF28" t="n">
         <v>1.55</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -7715,22 +7715,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="G29" t="n">
         <v>12.5</v>
       </c>
       <c r="H29" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="I29" t="n">
-        <v>110</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J29" t="n">
         <v>2.5</v>
       </c>
       <c r="K29" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -7739,7 +7739,7 @@
         <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="O29" t="n">
         <v>1.34</v>
@@ -7754,7 +7754,7 @@
         <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T29" t="n">
         <v>1.11</v>
@@ -7766,7 +7766,7 @@
         <v>1.44</v>
       </c>
       <c r="W29" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X29" t="n">
         <v>970</v>
@@ -7823,13 +7823,13 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.17</v>
+        <v>6.2</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.22</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.22</v>
+        <v>2.5</v>
       </c>
       <c r="AS29" t="n">
         <v>1.23</v>
@@ -7841,7 +7841,7 @@
         <v>1.24</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.22</v>
+        <v>2.5</v>
       </c>
       <c r="AW29" t="n">
         <v>1.23</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -7969,16 +7969,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="G30" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="H30" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I30" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="J30" t="n">
         <v>3.6</v>
@@ -7987,46 +7987,46 @@
         <v>3.65</v>
       </c>
       <c r="L30" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
         <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O30" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="P30" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="R30" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T30" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U30" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V30" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W30" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X30" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z30" t="n">
         <v>18.5</v>
@@ -8035,34 +8035,34 @@
         <v>42</v>
       </c>
       <c r="AB30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC30" t="n">
         <v>8</v>
       </c>
       <c r="AD30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AF30" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG30" t="n">
         <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AJ30" t="n">
         <v>50</v>
       </c>
       <c r="AK30" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AL30" t="n">
         <v>44</v>
@@ -8071,13 +8071,13 @@
         <v>95</v>
       </c>
       <c r="AN30" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AO30" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AP30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ30" t="n">
         <v>11</v>
@@ -8086,10 +8086,10 @@
         <v>16</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AT30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU30" t="n">
         <v>7.4</v>
@@ -8101,7 +8101,7 @@
         <v>25</v>
       </c>
       <c r="AX30" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY30" t="n">
         <v>11.5</v>
@@ -8113,22 +8113,22 @@
         <v>32</v>
       </c>
       <c r="BB30" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BC30" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD30" t="n">
         <v>32</v>
       </c>
       <c r="BE30" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BF30" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BG30" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BH30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -8229,37 +8229,37 @@
         <v>2.52</v>
       </c>
       <c r="H31" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I31" t="n">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="J31" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K31" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="M31" t="n">
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="O31" t="n">
         <v>1.26</v>
       </c>
       <c r="P31" t="n">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="R31" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="S31" t="n">
         <v>1.05</v>
@@ -8268,13 +8268,13 @@
         <v>1.11</v>
       </c>
       <c r="U31" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V31" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W31" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -8477,22 +8477,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.04</v>
+        <v>1.77</v>
       </c>
       <c r="G32" t="n">
         <v>1000</v>
       </c>
       <c r="H32" t="n">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="I32" t="n">
         <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="K32" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L32" t="n">
         <v>1.24</v>
@@ -8525,55 +8525,55 @@
         <v>1.11</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC32" t="n">
         <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AM32" t="n">
         <v>1000</v>
@@ -8585,55 +8585,55 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG32" t="n">
         <v>1.55</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -8731,22 +8731,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G33" t="n">
         <v>3.4</v>
       </c>
       <c r="H33" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I33" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J33" t="n">
         <v>3.7</v>
       </c>
       <c r="K33" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
@@ -8755,37 +8755,37 @@
         <v>1.04</v>
       </c>
       <c r="N33" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O33" t="n">
         <v>1.2</v>
       </c>
       <c r="P33" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R33" t="n">
         <v>1.58</v>
       </c>
       <c r="S33" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="T33" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U33" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V33" t="n">
         <v>1.74</v>
       </c>
       <c r="W33" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X33" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y33" t="n">
         <v>18.5</v>
@@ -8797,10 +8797,10 @@
         <v>48</v>
       </c>
       <c r="AB33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD33" t="n">
         <v>13</v>
@@ -8809,13 +8809,13 @@
         <v>29</v>
       </c>
       <c r="AF33" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG33" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH33" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>17.5</v>
       </c>
       <c r="AI33" t="n">
         <v>50</v>
@@ -8824,10 +8824,10 @@
         <v>210</v>
       </c>
       <c r="AK33" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL33" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM33" t="n">
         <v>190</v>
@@ -8839,7 +8839,7 @@
         <v>14.5</v>
       </c>
       <c r="AP33" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ33" t="n">
         <v>12</v>
@@ -8851,16 +8851,16 @@
         <v>21</v>
       </c>
       <c r="AT33" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU33" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX33" t="n">
         <v>18</v>
@@ -8869,7 +8869,7 @@
         <v>11</v>
       </c>
       <c r="AZ33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA33" t="n">
         <v>21</v>
@@ -8878,13 +8878,13 @@
         <v>40</v>
       </c>
       <c r="BC33" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BD33" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BE33" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="BF33" t="n">
         <v>16.5</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -8991,10 +8991,10 @@
         <v>3.45</v>
       </c>
       <c r="H34" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I34" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J34" t="n">
         <v>3.65</v>
@@ -9003,31 +9003,31 @@
         <v>3.8</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M34" t="n">
         <v>1.05</v>
       </c>
       <c r="N34" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O34" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P34" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q34" t="n">
         <v>1.8</v>
       </c>
       <c r="R34" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S34" t="n">
         <v>2.98</v>
       </c>
       <c r="T34" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U34" t="n">
         <v>2.32</v>
@@ -9039,40 +9039,40 @@
         <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y34" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z34" t="n">
         <v>18</v>
       </c>
       <c r="AA34" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AB34" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD34" t="n">
         <v>13</v>
       </c>
       <c r="AE34" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF34" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG34" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ34" t="n">
         <v>220</v>
@@ -9081,22 +9081,22 @@
         <v>65</v>
       </c>
       <c r="AL34" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM34" t="n">
         <v>190</v>
       </c>
       <c r="AN34" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AO34" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AP34" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR34" t="n">
         <v>12</v>
@@ -9117,34 +9117,34 @@
         <v>17</v>
       </c>
       <c r="AX34" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY34" t="n">
         <v>11</v>
       </c>
       <c r="AZ34" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA34" t="n">
         <v>24</v>
       </c>
       <c r="BB34" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BC34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD34" t="n">
         <v>25</v>
       </c>
       <c r="BE34" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BF34" t="n">
         <v>19.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -9242,10 +9242,10 @@
         <v>1.87</v>
       </c>
       <c r="G35" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="I35" t="n">
         <v>6</v>
@@ -9275,7 +9275,7 @@
         <v>1.04</v>
       </c>
       <c r="R35" t="n">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="S35" t="n">
         <v>1.05</v>
@@ -9287,7 +9287,7 @@
         <v>1.11</v>
       </c>
       <c r="V35" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W35" t="n">
         <v>1.3</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -9493,31 +9493,31 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="G36" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H36" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K36" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M36" t="n">
         <v>1.04</v>
       </c>
       <c r="N36" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="O36" t="n">
         <v>1.23</v>
@@ -9529,16 +9529,16 @@
         <v>1.04</v>
       </c>
       <c r="R36" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="S36" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="T36" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="U36" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
@@ -9601,55 +9601,55 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ36" t="n">
         <v>1.38</v>
       </c>
-      <c r="AQ36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU36" t="n">
+      <c r="BA36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BC36" t="n">
         <v>1.37</v>
       </c>
-      <c r="AV36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>1.35</v>
-      </c>
       <c r="BD36" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BG36" t="n">
         <v>1.55</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -9747,10 +9747,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="G37" t="n">
-        <v>8.6</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
         <v>2</v>
@@ -9759,10 +9759,10 @@
         <v>2.84</v>
       </c>
       <c r="J37" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K37" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -9771,34 +9771,34 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.27</v>
+        <v>1.89</v>
       </c>
       <c r="O37" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P37" t="n">
-        <v>1.25</v>
+        <v>1.89</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="R37" t="n">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="S37" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="T37" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="U37" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V37" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W37" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -10001,19 +10001,19 @@
         </is>
       </c>
       <c r="F38" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G38" t="n">
         <v>3.25</v>
       </c>
-      <c r="G38" t="n">
-        <v>3.35</v>
-      </c>
       <c r="H38" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="I38" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K38" t="n">
         <v>4.1</v>
@@ -10025,142 +10025,142 @@
         <v>1.04</v>
       </c>
       <c r="N38" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="O38" t="n">
         <v>1.19</v>
       </c>
       <c r="P38" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="R38" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="S38" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="T38" t="n">
         <v>1.58</v>
       </c>
       <c r="U38" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="V38" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="W38" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X38" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="Y38" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF38" t="n">
         <v>36</v>
       </c>
-      <c r="Z38" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA38" t="n">
+      <c r="AG38" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL38" t="n">
         <v>40</v>
       </c>
-      <c r="AB38" t="n">
-        <v>46</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>25</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE38" t="n">
+      <c r="AM38" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS38" t="n">
         <v>28</v>
       </c>
-      <c r="AF38" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH38" t="n">
+      <c r="AT38" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX38" t="n">
         <v>20</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>19</v>
       </c>
       <c r="AY38" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.36</v>
+        <v>24</v>
       </c>
       <c r="BB38" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BC38" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BD38" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.44</v>
+        <v>44</v>
       </c>
       <c r="BF38" t="n">
-        <v>7.6</v>
+        <v>18.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>2.24</v>
+        <v>11</v>
       </c>
       <c r="BH38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G39" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H39" t="n">
         <v>3.3</v>
@@ -10270,7 +10270,7 @@
         <v>3.65</v>
       </c>
       <c r="K39" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -10279,10 +10279,10 @@
         <v>1.06</v>
       </c>
       <c r="N39" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O39" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P39" t="n">
         <v>2.04</v>
@@ -10291,106 +10291,106 @@
         <v>1.86</v>
       </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S39" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T39" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="U39" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V39" t="n">
         <v>1.4</v>
       </c>
       <c r="W39" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X39" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Y39" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA39" t="n">
         <v>220</v>
       </c>
       <c r="AB39" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC39" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD39" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF39" t="n">
         <v>18</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>17.5</v>
       </c>
       <c r="AG39" t="n">
         <v>12.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI39" t="n">
         <v>140</v>
       </c>
       <c r="AJ39" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AK39" t="n">
         <v>30</v>
       </c>
       <c r="AL39" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM39" t="n">
         <v>190</v>
       </c>
       <c r="AN39" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO39" t="n">
         <v>55</v>
       </c>
       <c r="AP39" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ39" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR39" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AS39" t="n">
         <v>40</v>
       </c>
       <c r="AT39" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU39" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV39" t="n">
         <v>11.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AX39" t="n">
         <v>11.5</v>
       </c>
       <c r="AY39" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ39" t="n">
         <v>13.5</v>
@@ -10399,16 +10399,16 @@
         <v>32</v>
       </c>
       <c r="BB39" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BC39" t="n">
         <v>15.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BE39" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BF39" t="n">
         <v>12.5</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G40" t="n">
         <v>13</v>
@@ -10518,13 +10518,13 @@
         <v>1.68</v>
       </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>2.98</v>
       </c>
       <c r="J40" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="K40" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -10539,16 +10539,16 @@
         <v>1.23</v>
       </c>
       <c r="P40" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="Q40" t="n">
         <v>1.23</v>
       </c>
       <c r="R40" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="S40" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T40" t="n">
         <v>1.29</v>
@@ -10557,10 +10557,10 @@
         <v>1.92</v>
       </c>
       <c r="V40" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="W40" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -10647,7 +10647,7 @@
         <v>1.04</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BA40" t="n">
         <v>1.05</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -10766,19 +10766,19 @@
         <v>1.33</v>
       </c>
       <c r="G41" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="H41" t="n">
         <v>3.15</v>
       </c>
       <c r="I41" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="J41" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="K41" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -10799,10 +10799,10 @@
         <v>1.06</v>
       </c>
       <c r="R41" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="S41" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="T41" t="n">
         <v>1.11</v>
@@ -10814,7 +10814,7 @@
         <v>1.11</v>
       </c>
       <c r="W41" t="n">
-        <v>1.72</v>
+        <v>2.16</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -10829,7 +10829,7 @@
         <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AC41" t="n">
         <v>1000</v>
@@ -10847,7 +10847,7 @@
         <v>970</v>
       </c>
       <c r="AH41" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AI41" t="n">
         <v>1000</v>
@@ -10871,55 +10871,55 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BG41" t="n">
         <v>1.55</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -11020,16 +11020,16 @@
         <v>1.82</v>
       </c>
       <c r="G42" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="H42" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I42" t="n">
         <v>1000</v>
       </c>
       <c r="J42" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="K42" t="n">
         <v>1000</v>
@@ -11068,7 +11068,7 @@
         <v>1.18</v>
       </c>
       <c r="W42" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -11280,10 +11280,10 @@
         <v>1.4</v>
       </c>
       <c r="I43" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="J43" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="K43" t="n">
         <v>500</v>
@@ -11319,7 +11319,7 @@
         <v>1.11</v>
       </c>
       <c r="V43" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="W43" t="n">
         <v>1.11</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -11525,22 +11525,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="G44" t="n">
-        <v>3.85</v>
+        <v>2.58</v>
       </c>
       <c r="H44" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="I44" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J44" t="n">
         <v>3.55</v>
       </c>
       <c r="K44" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
@@ -11561,34 +11561,34 @@
         <v>1.13</v>
       </c>
       <c r="R44" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S44" t="n">
-        <v>1.13</v>
+        <v>1.8</v>
       </c>
       <c r="T44" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="U44" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="V44" t="n">
         <v>1.2</v>
       </c>
       <c r="W44" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
       </c>
       <c r="Y44" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z44" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA44" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AB44" t="n">
         <v>970</v>
@@ -11597,10 +11597,10 @@
         <v>1000</v>
       </c>
       <c r="AD44" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE44" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AF44" t="n">
         <v>970</v>
@@ -11612,7 +11612,7 @@
         <v>970</v>
       </c>
       <c r="AI44" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AJ44" t="n">
         <v>900</v>
@@ -11633,52 +11633,52 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AT44" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AY44" t="n">
-        <v>6.4</v>
+        <v>1.12</v>
       </c>
       <c r="AZ44" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BA44" t="n">
         <v>1.14</v>
       </c>
-      <c r="BA44" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BB44" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BF44" t="n">
         <v>1.55</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -11779,16 +11779,16 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.24</v>
+        <v>2.56</v>
       </c>
       <c r="G45" t="n">
-        <v>15</v>
+        <v>3.85</v>
       </c>
       <c r="H45" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="I45" t="n">
-        <v>6.4</v>
+        <v>3.25</v>
       </c>
       <c r="J45" t="n">
         <v>3.3</v>
@@ -11803,7 +11803,7 @@
         <v>1.08</v>
       </c>
       <c r="N45" t="n">
-        <v>1.71</v>
+        <v>2.98</v>
       </c>
       <c r="O45" t="n">
         <v>1.39</v>
@@ -11815,7 +11815,7 @@
         <v>2.18</v>
       </c>
       <c r="R45" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S45" t="n">
         <v>2.18</v>
@@ -11824,13 +11824,13 @@
         <v>1.11</v>
       </c>
       <c r="U45" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V45" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W45" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -11842,7 +11842,7 @@
         <v>970</v>
       </c>
       <c r="AA45" t="n">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AB45" t="n">
         <v>970</v>
@@ -11863,13 +11863,13 @@
         <v>970</v>
       </c>
       <c r="AH45" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AI45" t="n">
         <v>230</v>
       </c>
       <c r="AJ45" t="n">
-        <v>340</v>
+        <v>900</v>
       </c>
       <c r="AK45" t="n">
         <v>340</v>
@@ -11887,7 +11887,7 @@
         <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AQ45" t="n">
         <v>5.1</v>
@@ -11902,7 +11902,7 @@
         <v>5.8</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AV45" t="n">
         <v>6.4</v>
@@ -11914,7 +11914,7 @@
         <v>1.13</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AZ45" t="n">
         <v>1.12</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12057,7 @@
         <v>1.07</v>
       </c>
       <c r="N46" t="n">
-        <v>1.1</v>
+        <v>1.98</v>
       </c>
       <c r="O46" t="n">
         <v>1.35</v>
@@ -12069,7 +12069,7 @@
         <v>1.82</v>
       </c>
       <c r="R46" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S46" t="n">
         <v>1.83</v>
@@ -12087,16 +12087,16 @@
         <v>1.19</v>
       </c>
       <c r="X46" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y46" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z46" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA46" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB46" t="n">
         <v>1000</v>
@@ -12105,22 +12105,22 @@
         <v>1000</v>
       </c>
       <c r="AD46" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE46" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF46" t="n">
         <v>1000</v>
       </c>
       <c r="AG46" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH46" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI46" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ46" t="n">
         <v>1000</v>
@@ -12141,58 +12141,58 @@
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH46" t="n">
         <v>1000</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -12290,16 +12290,16 @@
         <v>1.29</v>
       </c>
       <c r="G47" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="H47" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="I47" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J47" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="K47" t="n">
         <v>7.2</v>
@@ -12320,19 +12320,19 @@
         <v>3.15</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="R47" t="n">
         <v>1.89</v>
       </c>
       <c r="S47" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T47" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="U47" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V47" t="n">
         <v>1.01</v>
@@ -12344,7 +12344,7 @@
         <v>40</v>
       </c>
       <c r="Y47" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="Z47" t="n">
         <v>140</v>
@@ -12353,10 +12353,10 @@
         <v>500</v>
       </c>
       <c r="AB47" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AC47" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AD47" t="n">
         <v>46</v>
@@ -12365,7 +12365,7 @@
         <v>170</v>
       </c>
       <c r="AF47" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG47" t="n">
         <v>11.5</v>
@@ -12377,7 +12377,7 @@
         <v>130</v>
       </c>
       <c r="AJ47" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AK47" t="n">
         <v>13</v>
@@ -12398,13 +12398,13 @@
         <v>30</v>
       </c>
       <c r="AQ47" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR47" t="n">
         <v>40</v>
       </c>
       <c r="AS47" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AT47" t="n">
         <v>11</v>
@@ -12419,10 +12419,10 @@
         <v>42</v>
       </c>
       <c r="AX47" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY47" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ47" t="n">
         <v>22</v>
@@ -12440,10 +12440,10 @@
         <v>23</v>
       </c>
       <c r="BE47" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF47" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BG47" t="n">
         <v>42</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -12541,10 +12541,10 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G48" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="H48" t="n">
         <v>2.02</v>
@@ -12556,7 +12556,7 @@
         <v>2.74</v>
       </c>
       <c r="K48" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
@@ -12583,10 +12583,10 @@
         <v>2</v>
       </c>
       <c r="T48" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="U48" t="n">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="V48" t="n">
         <v>1.7</v>
@@ -12595,7 +12595,7 @@
         <v>1.27</v>
       </c>
       <c r="X48" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y48" t="n">
         <v>1000</v>
@@ -12649,7 +12649,7 @@
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AQ48" t="n">
         <v>1.01</v>
@@ -12697,10 +12697,10 @@
         <v>1.01</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG48" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH48" t="n">
         <v>1000</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
         <v>1000</v>
       </c>
       <c r="AH49" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI49" t="n">
         <v>1000</v>
@@ -12951,10 +12951,10 @@
         <v>1.01</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG49" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH49" t="n">
         <v>1000</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -13049,19 +13049,19 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G50" t="n">
-        <v>7.6</v>
+        <v>2.86</v>
       </c>
       <c r="H50" t="n">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="I50" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="K50" t="n">
         <v>3.35</v>
@@ -13073,7 +13073,7 @@
         <v>1.09</v>
       </c>
       <c r="N50" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O50" t="n">
         <v>1.43</v>
@@ -13100,28 +13100,28 @@
         <v>1.21</v>
       </c>
       <c r="W50" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X50" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y50" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z50" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA50" t="n">
         <v>1000</v>
       </c>
       <c r="AB50" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC50" t="n">
         <v>1000</v>
       </c>
       <c r="AD50" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE50" t="n">
         <v>1000</v>
@@ -13130,7 +13130,7 @@
         <v>1000</v>
       </c>
       <c r="AG50" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH50" t="n">
         <v>1000</v>
@@ -13139,13 +13139,13 @@
         <v>1000</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK50" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL50" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM50" t="n">
         <v>1000</v>
@@ -13157,58 +13157,58 @@
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AT50" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AV50" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BG50" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH50" t="n">
         <v>1000</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -13342,13 +13342,13 @@
         <v>1.66</v>
       </c>
       <c r="S51" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T51" t="n">
         <v>1.53</v>
       </c>
       <c r="U51" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V51" t="n">
         <v>1.41</v>
@@ -13363,7 +13363,7 @@
         <v>22</v>
       </c>
       <c r="Z51" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA51" t="n">
         <v>70</v>
@@ -13387,19 +13387,19 @@
         <v>11.5</v>
       </c>
       <c r="AH51" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI51" t="n">
         <v>36</v>
       </c>
       <c r="AJ51" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK51" t="n">
         <v>25</v>
       </c>
       <c r="AL51" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM51" t="n">
         <v>60</v>
@@ -13462,7 +13462,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG51" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH51" t="n">
         <v>1000</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -13569,7 +13569,7 @@
         <v>1000</v>
       </c>
       <c r="J52" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K52" t="n">
         <v>1000</v>
@@ -13596,7 +13596,7 @@
         <v>1.18</v>
       </c>
       <c r="S52" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="T52" t="n">
         <v>1.01</v>
@@ -13605,7 +13605,7 @@
         <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W52" t="n">
         <v>1.01</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -13841,7 +13841,7 @@
         <v>1.17</v>
       </c>
       <c r="P53" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q53" t="n">
         <v>1.17</v>
@@ -13856,7 +13856,7 @@
         <v>1.75</v>
       </c>
       <c r="U53" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V53" t="n">
         <v>1.05</v>
@@ -13913,64 +13913,64 @@
         <v>1000</v>
       </c>
       <c r="AN53" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO53" t="n">
         <v>1000</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF53" t="n">
         <v>1.01</v>
       </c>
       <c r="BG53" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH53" t="n">
         <v>1000</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -14077,7 +14077,7 @@
         <v>1000</v>
       </c>
       <c r="J54" t="n">
-        <v>1.02</v>
+        <v>4.6</v>
       </c>
       <c r="K54" t="n">
         <v>1000</v>
@@ -14110,13 +14110,13 @@
         <v>1.62</v>
       </c>
       <c r="U54" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="V54" t="n">
         <v>1.01</v>
       </c>
       <c r="W54" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="X54" t="n">
         <v>1000</v>
@@ -14167,64 +14167,64 @@
         <v>1000</v>
       </c>
       <c r="AN54" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO54" t="n">
         <v>1000</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AU54" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AV54" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BC54" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BD54" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BG54" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH54" t="n">
         <v>1000</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
         <v>1.23</v>
       </c>
       <c r="J55" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="K55" t="n">
         <v>1000</v>
@@ -14475,7 +14475,7 @@
         <v>1.01</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG55" t="n">
         <v>1.01</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -14657,7 +14657,7 @@
         <v>1000</v>
       </c>
       <c r="AH56" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI56" t="n">
         <v>1000</v>
@@ -14678,7 +14678,7 @@
         <v>1000</v>
       </c>
       <c r="AO56" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP56" t="n">
         <v>1.01</v>
@@ -14729,10 +14729,10 @@
         <v>1.01</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG56" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BH56" t="n">
         <v>1000</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -14851,19 +14851,19 @@
         <v>1.01</v>
       </c>
       <c r="N57" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="O57" t="n">
         <v>1.05</v>
       </c>
       <c r="P57" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q57" t="n">
         <v>1.04</v>
       </c>
       <c r="R57" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S57" t="n">
         <v>1.05</v>
@@ -14929,64 +14929,64 @@
         <v>1000</v>
       </c>
       <c r="AN57" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO57" t="n">
         <v>1000</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AT57" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AU57" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AV57" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AY57" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AZ57" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BA57" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BB57" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BC57" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BD57" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BG57" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH57" t="n">
         <v>1000</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -15081,22 +15081,22 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="G58" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H58" t="n">
         <v>2.16</v>
       </c>
       <c r="I58" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="J58" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K58" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
@@ -15105,13 +15105,13 @@
         <v>1.09</v>
       </c>
       <c r="N58" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="O58" t="n">
         <v>1.4</v>
       </c>
       <c r="P58" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Q58" t="n">
         <v>1.43</v>
@@ -15129,7 +15129,7 @@
         <v>1.11</v>
       </c>
       <c r="V58" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W58" t="n">
         <v>1.32</v>
@@ -15138,46 +15138,46 @@
         <v>1000</v>
       </c>
       <c r="Y58" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z58" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA58" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB58" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC58" t="n">
         <v>1000</v>
       </c>
       <c r="AD58" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE58" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF58" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AG58" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH58" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI58" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ58" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AK58" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AL58" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AM58" t="n">
         <v>1000</v>
@@ -15189,58 +15189,58 @@
         <v>1000</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AU58" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AV58" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AW58" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BC58" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BD58" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BF58" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG58" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH58" t="n">
         <v>1000</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -15380,7 +15380,7 @@
         <v>1.23</v>
       </c>
       <c r="U59" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V59" t="n">
         <v>1.01</v>
@@ -15419,7 +15419,7 @@
         <v>1000</v>
       </c>
       <c r="AH59" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI59" t="n">
         <v>1000</v>
@@ -15443,58 +15443,58 @@
         <v>1000</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AT59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AU59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AV59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AW59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AX59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AY59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AZ59" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BA59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BB59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BD59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BE59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BF59" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BG59" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH59" t="n">
         <v>1000</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -15595,7 +15595,7 @@
         <v>2.68</v>
       </c>
       <c r="H60" t="n">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="I60" t="n">
         <v>5.6</v>
@@ -15637,55 +15637,55 @@
         <v>1.53</v>
       </c>
       <c r="V60" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W60" t="n">
         <v>1.6</v>
       </c>
       <c r="X60" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y60" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z60" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA60" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB60" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC60" t="n">
         <v>1000</v>
       </c>
       <c r="AD60" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE60" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF60" t="n">
         <v>1000</v>
       </c>
       <c r="AG60" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH60" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI60" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AJ60" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK60" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AL60" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM60" t="n">
         <v>1000</v>
@@ -15697,58 +15697,58 @@
         <v>1000</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AT60" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AU60" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AV60" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AW60" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AX60" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AY60" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AZ60" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BA60" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BB60" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BC60" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BD60" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BE60" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BF60" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG60" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH60" t="n">
         <v>1000</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -15843,22 +15843,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="G61" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="H61" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="I61" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="J61" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="K61" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
@@ -15891,70 +15891,70 @@
         <v>1.98</v>
       </c>
       <c r="V61" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="W61" t="n">
         <v>1.23</v>
       </c>
       <c r="X61" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y61" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z61" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA61" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB61" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC61" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD61" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG61" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH61" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP61" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AR61" t="n">
         <v>1.01</v>
@@ -15966,7 +15966,7 @@
         <v>1.01</v>
       </c>
       <c r="AU61" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV61" t="n">
         <v>1.01</v>
@@ -15999,10 +15999,10 @@
         <v>1.01</v>
       </c>
       <c r="BF61" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG61" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BH61" t="n">
         <v>1000</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -16100,7 +16100,7 @@
         <v>1.68</v>
       </c>
       <c r="G62" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H62" t="n">
         <v>2.44</v>
@@ -16148,7 +16148,7 @@
         <v>1.17</v>
       </c>
       <c r="W62" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="X62" t="n">
         <v>1000</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -16384,13 +16384,13 @@
         <v>1.25</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="R63" t="n">
         <v>1.12</v>
       </c>
       <c r="S63" t="n">
-        <v>1.05</v>
+        <v>1.51</v>
       </c>
       <c r="T63" t="n">
         <v>1.11</v>
@@ -16402,7 +16402,7 @@
         <v>1.28</v>
       </c>
       <c r="W63" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="X63" t="n">
         <v>1000</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
         <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O64" t="n">
         <v>1.01</v>
@@ -16644,7 +16644,7 @@
         <v>1.12</v>
       </c>
       <c r="S64" t="n">
-        <v>1.05</v>
+        <v>1.58</v>
       </c>
       <c r="T64" t="n">
         <v>1.11</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -16862,10 +16862,10 @@
         <v>2</v>
       </c>
       <c r="G65" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H65" t="n">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="I65" t="n">
         <v>1000</v>
@@ -16883,13 +16883,13 @@
         <v>1.01</v>
       </c>
       <c r="N65" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P65" t="n">
         <v>1.25</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P65" t="n">
-        <v>1.24</v>
       </c>
       <c r="Q65" t="n">
         <v>1.01</v>
@@ -16898,7 +16898,7 @@
         <v>1.12</v>
       </c>
       <c r="S65" t="n">
-        <v>1.05</v>
+        <v>1.67</v>
       </c>
       <c r="T65" t="n">
         <v>1.9</v>
@@ -16910,7 +16910,7 @@
         <v>1.3</v>
       </c>
       <c r="W65" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X65" t="n">
         <v>1000</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -17137,7 +17137,7 @@
         <v>1.01</v>
       </c>
       <c r="N66" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O66" t="n">
         <v>1.01</v>
@@ -17146,16 +17146,16 @@
         <v>1.25</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R66" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S66" t="n">
-        <v>1.05</v>
+        <v>1.53</v>
       </c>
       <c r="T66" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U66" t="n">
         <v>1.24</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -17376,7 +17376,7 @@
         <v>1.5</v>
       </c>
       <c r="I67" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="J67" t="n">
         <v>1.9</v>
@@ -17391,13 +17391,13 @@
         <v>1.01</v>
       </c>
       <c r="N67" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P67" t="n">
         <v>1.25</v>
-      </c>
-      <c r="O67" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P67" t="n">
-        <v>1.24</v>
       </c>
       <c r="Q67" t="n">
         <v>1.01</v>
@@ -17406,7 +17406,7 @@
         <v>1.12</v>
       </c>
       <c r="S67" t="n">
-        <v>1.05</v>
+        <v>1.61</v>
       </c>
       <c r="T67" t="n">
         <v>1.8</v>
@@ -17415,7 +17415,7 @@
         <v>1.39</v>
       </c>
       <c r="V67" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W67" t="n">
         <v>1.05</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -17633,7 +17633,7 @@
         <v>1000</v>
       </c>
       <c r="J68" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K68" t="n">
         <v>1000</v>
@@ -17663,16 +17663,16 @@
         <v>1.61</v>
       </c>
       <c r="T68" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U68" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V68" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W68" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X68" t="n">
         <v>1000</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -17887,7 +17887,7 @@
         <v>1000</v>
       </c>
       <c r="J69" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="K69" t="n">
         <v>1000</v>
@@ -17905,7 +17905,7 @@
         <v>1.41</v>
       </c>
       <c r="P69" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q69" t="n">
         <v>1.41</v>
@@ -17914,7 +17914,7 @@
         <v>1.12</v>
       </c>
       <c r="S69" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T69" t="n">
         <v>1.11</v>
@@ -17926,7 +17926,7 @@
         <v>1.28</v>
       </c>
       <c r="W69" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="X69" t="n">
         <v>1000</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -18138,7 +18138,7 @@
         <v>1.27</v>
       </c>
       <c r="I70" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="J70" t="n">
         <v>3.2</v>
@@ -18153,7 +18153,7 @@
         <v>1.04</v>
       </c>
       <c r="N70" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O70" t="n">
         <v>1.21</v>
@@ -18165,7 +18165,7 @@
         <v>1.37</v>
       </c>
       <c r="R70" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S70" t="n">
         <v>1.37</v>
@@ -18177,7 +18177,7 @@
         <v>1.84</v>
       </c>
       <c r="V70" t="n">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="W70" t="n">
         <v>1.08</v>
@@ -18234,61 +18234,61 @@
         <v>1000</v>
       </c>
       <c r="AO70" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AS70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AT70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AU70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AV70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AW70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AX70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AY70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AZ70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BA70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BB70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BC70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BD70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BE70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BF70" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG70" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BH70" t="n">
         <v>1000</v>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
         <v>1.47</v>
       </c>
       <c r="G71" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="H71" t="n">
         <v>2.28</v>
@@ -18434,7 +18434,7 @@
         <v>1.01</v>
       </c>
       <c r="W71" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="X71" t="n">
         <v>1000</v>
@@ -18449,7 +18449,7 @@
         <v>1000</v>
       </c>
       <c r="AB71" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC71" t="n">
         <v>1000</v>
@@ -18461,10 +18461,10 @@
         <v>1000</v>
       </c>
       <c r="AF71" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG71" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH71" t="n">
         <v>1000</v>
@@ -18473,19 +18473,19 @@
         <v>1000</v>
       </c>
       <c r="AJ71" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK71" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL71" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM71" t="n">
         <v>1000</v>
       </c>
       <c r="AN71" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO71" t="n">
         <v>1000</v>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -18661,22 +18661,22 @@
         <v>1.01</v>
       </c>
       <c r="N72" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O72" t="n">
         <v>1.02</v>
       </c>
       <c r="P72" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="R72" t="n">
         <v>1.12</v>
       </c>
       <c r="S72" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="T72" t="n">
         <v>1.7</v>
@@ -18691,112 +18691,112 @@
         <v>1.43</v>
       </c>
       <c r="X72" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y72" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z72" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA72" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB72" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC72" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD72" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE72" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF72" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG72" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH72" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI72" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ72" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK72" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL72" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM72" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN72" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO72" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BG72" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BH72" t="n">
         <v>1000</v>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -18921,7 +18921,7 @@
         <v>1.01</v>
       </c>
       <c r="P73" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q73" t="n">
         <v>1.01</v>
@@ -18930,10 +18930,10 @@
         <v>1.12</v>
       </c>
       <c r="S73" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="T73" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U73" t="n">
         <v>1.3</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -19148,7 +19148,7 @@
         <v>1.44</v>
       </c>
       <c r="G74" t="n">
-        <v>1000</v>
+        <v>2.28</v>
       </c>
       <c r="H74" t="n">
         <v>3.25</v>
@@ -19175,7 +19175,7 @@
         <v>1.09</v>
       </c>
       <c r="P74" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q74" t="n">
         <v>1.09</v>
@@ -19184,7 +19184,7 @@
         <v>1.12</v>
       </c>
       <c r="S74" t="n">
-        <v>1.09</v>
+        <v>1.46</v>
       </c>
       <c r="T74" t="n">
         <v>1.11</v>
@@ -19196,7 +19196,7 @@
         <v>1.11</v>
       </c>
       <c r="W74" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="X74" t="n">
         <v>1000</v>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -19405,7 +19405,7 @@
         <v>2.26</v>
       </c>
       <c r="H75" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="I75" t="n">
         <v>22</v>
@@ -19414,7 +19414,7 @@
         <v>2.52</v>
       </c>
       <c r="K75" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="L75" t="n">
         <v>1.01</v>
@@ -19423,22 +19423,22 @@
         <v>1.01</v>
       </c>
       <c r="N75" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="O75" t="n">
         <v>1.03</v>
       </c>
       <c r="P75" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="R75" t="n">
         <v>1.07</v>
       </c>
       <c r="S75" t="n">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="T75" t="n">
         <v>1.77</v>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -19656,13 +19656,13 @@
         <v>1.86</v>
       </c>
       <c r="G76" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="H76" t="n">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="I76" t="n">
-        <v>970</v>
+        <v>870</v>
       </c>
       <c r="J76" t="n">
         <v>2.2</v>
@@ -19698,13 +19698,13 @@
         <v>1.27</v>
       </c>
       <c r="U76" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V76" t="n">
         <v>1.27</v>
       </c>
       <c r="W76" t="n">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="X76" t="n">
         <v>1000</v>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="CB76" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
         <v>1.51</v>
       </c>
       <c r="R77" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S77" t="n">
         <v>1.86</v>
@@ -19973,7 +19973,7 @@
         <v>1000</v>
       </c>
       <c r="AB77" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC77" t="n">
         <v>1000</v>
@@ -19985,10 +19985,10 @@
         <v>1000</v>
       </c>
       <c r="AF77" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG77" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH77" t="n">
         <v>1000</v>
@@ -19997,76 +19997,76 @@
         <v>1000</v>
       </c>
       <c r="AJ77" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK77" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL77" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM77" t="n">
         <v>1000</v>
       </c>
       <c r="AN77" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO77" t="n">
         <v>1000</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AS77" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AT77" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AU77" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AV77" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AW77" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AX77" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY77" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ77" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BA77" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BB77" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BC77" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BD77" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BE77" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BF77" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BG77" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BH77" t="n">
         <v>1000</v>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="CB77" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -20164,16 +20164,16 @@
         <v>1.2</v>
       </c>
       <c r="G78" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="H78" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="I78" t="n">
         <v>1000</v>
       </c>
       <c r="J78" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K78" t="n">
         <v>500</v>
@@ -20185,25 +20185,25 @@
         <v>1.03</v>
       </c>
       <c r="N78" t="n">
-        <v>1.1</v>
+        <v>1.46</v>
       </c>
       <c r="O78" t="n">
         <v>1.22</v>
       </c>
       <c r="P78" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="Q78" t="n">
         <v>1.22</v>
       </c>
       <c r="R78" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S78" t="n">
-        <v>1.22</v>
+        <v>2.24</v>
       </c>
       <c r="T78" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="U78" t="n">
         <v>1.11</v>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="CB78" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -20415,7 +20415,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1.4</v>
+        <v>2.88</v>
       </c>
       <c r="G79" t="n">
         <v>600</v>
@@ -20430,7 +20430,7 @@
         <v>1.62</v>
       </c>
       <c r="K79" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L79" t="n">
         <v>1.01</v>
@@ -20454,7 +20454,7 @@
         <v>1.18</v>
       </c>
       <c r="S79" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T79" t="n">
         <v>1.45</v>
@@ -20638,7 +20638,7 @@
       </c>
       <c r="CB79" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
         <v>8</v>
       </c>
       <c r="J80" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K80" t="n">
         <v>4.5</v>
@@ -20892,7 +20892,7 @@
       </c>
       <c r="CB80" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -20935,7 +20935,7 @@
         <v>1000</v>
       </c>
       <c r="J81" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K81" t="n">
         <v>1000</v>
@@ -20956,13 +20956,13 @@
         <v>1.25</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="R81" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="S81" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="T81" t="n">
         <v>1.11</v>
@@ -20971,7 +20971,7 @@
         <v>1.76</v>
       </c>
       <c r="V81" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W81" t="n">
         <v>1.01</v>
@@ -21146,7 +21146,7 @@
       </c>
       <c r="CB81" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -21177,22 +21177,22 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G82" t="n">
         <v>1.73</v>
       </c>
       <c r="H82" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I82" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J82" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K82" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L82" t="n">
         <v>1.41</v>
@@ -21201,7 +21201,7 @@
         <v>1.08</v>
       </c>
       <c r="N82" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="O82" t="n">
         <v>1.44</v>
@@ -21210,16 +21210,16 @@
         <v>1.64</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R82" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S82" t="n">
         <v>4.5</v>
       </c>
       <c r="T82" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U82" t="n">
         <v>1.72</v>
@@ -21400,7 +21400,7 @@
       </c>
       <c r="CB82" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -21431,22 +21431,22 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G83" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="H83" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I83" t="n">
         <v>5.7</v>
       </c>
       <c r="J83" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K83" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L83" t="n">
         <v>1.41</v>
@@ -21455,7 +21455,7 @@
         <v>1.08</v>
       </c>
       <c r="N83" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="O83" t="n">
         <v>1.4</v>
@@ -21470,7 +21470,7 @@
         <v>1.2</v>
       </c>
       <c r="S83" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T83" t="n">
         <v>1.11</v>
@@ -21482,7 +21482,7 @@
         <v>1.21</v>
       </c>
       <c r="W83" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="X83" t="n">
         <v>1000</v>
@@ -21654,7 +21654,7 @@
       </c>
       <c r="CB83" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -21688,7 +21688,7 @@
         <v>5.1</v>
       </c>
       <c r="G84" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="H84" t="n">
         <v>1.84</v>
@@ -21724,7 +21724,7 @@
         <v>1.22</v>
       </c>
       <c r="S84" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="T84" t="n">
         <v>2.1</v>
@@ -21908,7 +21908,7 @@
       </c>
       <c r="CB84" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -21942,7 +21942,7 @@
         <v>1.63</v>
       </c>
       <c r="G85" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="H85" t="n">
         <v>2.04</v>
@@ -21969,16 +21969,16 @@
         <v>1.39</v>
       </c>
       <c r="P85" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R85" t="n">
         <v>1.17</v>
       </c>
       <c r="S85" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="T85" t="n">
         <v>1.11</v>
@@ -21990,7 +21990,7 @@
         <v>1.25</v>
       </c>
       <c r="W85" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="X85" t="n">
         <v>1000</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="CB85" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -22196,13 +22196,13 @@
         <v>1.81</v>
       </c>
       <c r="G86" t="n">
-        <v>100</v>
+        <v>5.1</v>
       </c>
       <c r="H86" t="n">
         <v>2.48</v>
       </c>
       <c r="I86" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J86" t="n">
         <v>2.48</v>
@@ -22217,22 +22217,22 @@
         <v>1.01</v>
       </c>
       <c r="N86" t="n">
-        <v>1.26</v>
+        <v>2.28</v>
       </c>
       <c r="O86" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="P86" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q86" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="R86" t="n">
         <v>1.18</v>
       </c>
       <c r="S86" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="T86" t="n">
         <v>1.73</v>
@@ -22244,7 +22244,7 @@
         <v>1.22</v>
       </c>
       <c r="W86" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="X86" t="n">
         <v>1000</v>
@@ -22416,7 +22416,7 @@
       </c>
       <c r="CB86" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -22450,10 +22450,10 @@
         <v>1.72</v>
       </c>
       <c r="G87" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H87" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="I87" t="n">
         <v>1000</v>
@@ -22471,22 +22471,22 @@
         <v>1.01</v>
       </c>
       <c r="N87" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P87" t="n">
         <v>1.25</v>
       </c>
-      <c r="O87" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P87" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q87" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R87" t="n">
         <v>1.18</v>
       </c>
       <c r="S87" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T87" t="n">
         <v>1.78</v>
@@ -22498,7 +22498,7 @@
         <v>1.07</v>
       </c>
       <c r="W87" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="X87" t="n">
         <v>1000</v>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="CB87" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -22924,7 +22924,7 @@
       </c>
       <c r="CB88" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -22997,10 +22997,10 @@
         <v>1.83</v>
       </c>
       <c r="T89" t="n">
-        <v>1.11</v>
+        <v>1.48</v>
       </c>
       <c r="U89" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="V89" t="n">
         <v>1.36</v>
@@ -23178,7 +23178,7 @@
       </c>
       <c r="CB89" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -23233,7 +23233,7 @@
         <v>1.02</v>
       </c>
       <c r="N90" t="n">
-        <v>1.1</v>
+        <v>1.95</v>
       </c>
       <c r="O90" t="n">
         <v>1.07</v>
@@ -23245,16 +23245,16 @@
         <v>1.07</v>
       </c>
       <c r="R90" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="S90" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="T90" t="n">
         <v>1.12</v>
       </c>
       <c r="U90" t="n">
-        <v>2</v>
+        <v>2.66</v>
       </c>
       <c r="V90" t="n">
         <v>1.01</v>
@@ -23432,7 +23432,7 @@
       </c>
       <c r="CB90" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -23463,22 +23463,22 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="G91" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="H91" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I91" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="J91" t="n">
         <v>3.1</v>
       </c>
       <c r="K91" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L91" t="n">
         <v>1.01</v>
@@ -23502,7 +23502,7 @@
         <v>1.17</v>
       </c>
       <c r="S91" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T91" t="n">
         <v>1.57</v>
@@ -23514,16 +23514,16 @@
         <v>1.13</v>
       </c>
       <c r="W91" t="n">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="X91" t="n">
         <v>44</v>
       </c>
       <c r="Y91" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z91" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AA91" t="n">
         <v>1000</v>
@@ -23532,97 +23532,97 @@
         <v>22</v>
       </c>
       <c r="AC91" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD91" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AE91" t="n">
         <v>1000</v>
       </c>
       <c r="AF91" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG91" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AH91" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AI91" t="n">
         <v>1000</v>
       </c>
       <c r="AJ91" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK91" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL91" t="n">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="AM91" t="n">
         <v>1000</v>
       </c>
       <c r="AN91" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO91" t="n">
         <v>1000</v>
       </c>
       <c r="AP91" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ91" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR91" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS91" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AT91" t="n">
         <v>1.41</v>
-      </c>
-      <c r="AQ91" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR91" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS91" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AT91" t="n">
-        <v>1.37</v>
       </c>
       <c r="AU91" t="n">
         <v>7.2</v>
       </c>
       <c r="AV91" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AW91" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AX91" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AY91" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ91" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="BA91" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="BB91" t="n">
-        <v>1.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC91" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BD91" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="BE91" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="BF91" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BG91" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BH91" t="n">
         <v>1000</v>
@@ -23686,7 +23686,7 @@
       </c>
       <c r="CB91" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -23717,7 +23717,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="G92" t="n">
         <v>2.04</v>
@@ -23744,19 +23744,19 @@
         <v>1.6</v>
       </c>
       <c r="O92" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P92" t="n">
         <v>1.25</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.09</v>
+        <v>1.47</v>
       </c>
       <c r="R92" t="n">
         <v>1.17</v>
       </c>
       <c r="S92" t="n">
-        <v>1.05</v>
+        <v>3.45</v>
       </c>
       <c r="T92" t="n">
         <v>1.68</v>
@@ -23940,7 +23940,7 @@
       </c>
       <c r="CB92" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -23971,10 +23971,10 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G93" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H93" t="n">
         <v>8.199999999999999</v>
@@ -23983,7 +23983,7 @@
         <v>1000</v>
       </c>
       <c r="J93" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="K93" t="n">
         <v>4.9</v>
@@ -24010,7 +24010,7 @@
         <v>1.18</v>
       </c>
       <c r="S93" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T93" t="n">
         <v>1.11</v>
@@ -24019,118 +24019,118 @@
         <v>1.11</v>
       </c>
       <c r="V93" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W93" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X93" t="n">
         <v>50</v>
       </c>
       <c r="Y93" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Z93" t="n">
+        <v>220</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>120</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>130</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL93" t="n">
         <v>240</v>
       </c>
-      <c r="AA93" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB93" t="n">
+      <c r="AM93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN93" t="n">
         <v>21</v>
       </c>
-      <c r="AC93" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD93" t="n">
-        <v>130</v>
-      </c>
-      <c r="AE93" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF93" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG93" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH93" t="n">
-        <v>140</v>
-      </c>
-      <c r="AI93" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ93" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AK93" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL93" t="n">
-        <v>270</v>
-      </c>
-      <c r="AM93" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN93" t="n">
-        <v>23</v>
-      </c>
       <c r="AO93" t="n">
         <v>1000</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AQ93" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AS93" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AT93" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AU93" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AV93" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AW93" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AX93" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AY93" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ93" t="n">
-        <v>1.63</v>
+        <v>15</v>
       </c>
       <c r="BA93" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="BB93" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BC93" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="BD93" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="BE93" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="BF93" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="BG93" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH93" t="n">
         <v>1000</v>
@@ -24194,7 +24194,7 @@
       </c>
       <c r="CB93" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -24225,7 +24225,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="G94" t="n">
         <v>2.32</v>
@@ -24237,7 +24237,7 @@
         <v>1000</v>
       </c>
       <c r="J94" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="K94" t="n">
         <v>1000</v>
@@ -24273,7 +24273,7 @@
         <v>1.62</v>
       </c>
       <c r="V94" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W94" t="n">
         <v>1.75</v>
@@ -24448,7 +24448,7 @@
       </c>
       <c r="CB94" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -24485,7 +24485,7 @@
         <v>1000</v>
       </c>
       <c r="H95" t="n">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="I95" t="n">
         <v>1000</v>
@@ -24494,37 +24494,37 @@
         <v>1.03</v>
       </c>
       <c r="K95" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="L95" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="M95" t="n">
         <v>1.05</v>
       </c>
       <c r="N95" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="O95" t="n">
         <v>1.26</v>
       </c>
       <c r="P95" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="Q95" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="R95" t="n">
         <v>1.22</v>
       </c>
       <c r="S95" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="T95" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="U95" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="V95" t="n">
         <v>1.11</v>
@@ -24702,7 +24702,7 @@
       </c>
       <c r="CB95" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -24745,7 +24745,7 @@
         <v>3.2</v>
       </c>
       <c r="J96" t="n">
-        <v>1.1</v>
+        <v>1.76</v>
       </c>
       <c r="K96" t="n">
         <v>1000</v>
@@ -24781,7 +24781,7 @@
         <v>1.95</v>
       </c>
       <c r="V96" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W96" t="n">
         <v>1.13</v>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="CB96" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -24993,13 +24993,13 @@
         <v>1000</v>
       </c>
       <c r="H97" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="I97" t="n">
         <v>2.28</v>
       </c>
       <c r="J97" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="K97" t="n">
         <v>1000</v>
@@ -25210,7 +25210,7 @@
       </c>
       <c r="CB97" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -25464,7 +25464,7 @@
       </c>
       <c r="CB98" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -25495,19 +25495,19 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="G99" t="n">
-        <v>17</v>
+        <v>1.81</v>
       </c>
       <c r="H99" t="n">
-        <v>1.73</v>
+        <v>4.9</v>
       </c>
       <c r="I99" t="n">
         <v>1000</v>
       </c>
       <c r="J99" t="n">
-        <v>1.23</v>
+        <v>3.15</v>
       </c>
       <c r="K99" t="n">
         <v>4</v>
@@ -25522,7 +25522,7 @@
         <v>1.11</v>
       </c>
       <c r="O99" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P99" t="n">
         <v>1.35</v>
@@ -25534,19 +25534,19 @@
         <v>1.18</v>
       </c>
       <c r="S99" t="n">
-        <v>1.05</v>
+        <v>1.98</v>
       </c>
       <c r="T99" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="U99" t="n">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="V99" t="n">
         <v>1.01</v>
       </c>
       <c r="W99" t="n">
-        <v>1.06</v>
+        <v>2.22</v>
       </c>
       <c r="X99" t="n">
         <v>1000</v>
@@ -25718,7 +25718,7 @@
       </c>
       <c r="CB99" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -25752,7 +25752,7 @@
         <v>1.08</v>
       </c>
       <c r="G100" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H100" t="n">
         <v>1.04</v>
@@ -25779,7 +25779,7 @@
         <v>1.28</v>
       </c>
       <c r="P100" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q100" t="n">
         <v>1.28</v>
@@ -25797,7 +25797,7 @@
         <v>1.43</v>
       </c>
       <c r="V100" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W100" t="n">
         <v>3.25</v>
@@ -25972,7 +25972,7 @@
       </c>
       <c r="CB100" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -26003,10 +26003,10 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="G101" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H101" t="n">
         <v>4.4</v>
@@ -26015,10 +26015,10 @@
         <v>110</v>
       </c>
       <c r="J101" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K101" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="L101" t="n">
         <v>1.01</v>
@@ -26051,7 +26051,7 @@
         <v>1.11</v>
       </c>
       <c r="V101" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="W101" t="n">
         <v>2.8</v>
@@ -26063,10 +26063,10 @@
         <v>65</v>
       </c>
       <c r="Z101" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AA101" t="n">
-        <v>560</v>
+        <v>680</v>
       </c>
       <c r="AB101" t="n">
         <v>26</v>
@@ -26075,10 +26075,10 @@
         <v>18.5</v>
       </c>
       <c r="AD101" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AE101" t="n">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="AF101" t="n">
         <v>19.5</v>
@@ -26087,10 +26087,10 @@
         <v>13.5</v>
       </c>
       <c r="AH101" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AI101" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="AJ101" t="n">
         <v>22</v>
@@ -26102,40 +26102,40 @@
         <v>95</v>
       </c>
       <c r="AM101" t="n">
-        <v>550</v>
+        <v>620</v>
       </c>
       <c r="AN101" t="n">
         <v>20</v>
       </c>
       <c r="AO101" t="n">
-        <v>740</v>
+        <v>930</v>
       </c>
       <c r="AP101" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT101" t="n">
         <v>1.77</v>
       </c>
-      <c r="AQ101" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AR101" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS101" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AT101" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AU101" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AV101" t="n">
         <v>20</v>
       </c>
       <c r="AW101" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AX101" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AY101" t="n">
         <v>9.199999999999999</v>
@@ -26147,7 +26147,7 @@
         <v>34</v>
       </c>
       <c r="BB101" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="BC101" t="n">
         <v>10.5</v>
@@ -26159,7 +26159,7 @@
         <v>38</v>
       </c>
       <c r="BF101" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BG101" t="n">
         <v>19.5</v>
@@ -26226,7 +26226,7 @@
       </c>
       <c r="CB101" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -26266,13 +26266,13 @@
         <v>6</v>
       </c>
       <c r="I102" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="J102" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="K102" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L102" t="n">
         <v>1.01</v>
@@ -26296,7 +26296,7 @@
         <v>1.34</v>
       </c>
       <c r="S102" t="n">
-        <v>1.35</v>
+        <v>1.91</v>
       </c>
       <c r="T102" t="n">
         <v>1.31</v>
@@ -26305,10 +26305,10 @@
         <v>1.88</v>
       </c>
       <c r="V102" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W102" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="X102" t="n">
         <v>1000</v>
@@ -26480,7 +26480,7 @@
       </c>
       <c r="CB102" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
@@ -26511,19 +26511,19 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="G103" t="n">
         <v>1000</v>
       </c>
       <c r="H103" t="n">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="I103" t="n">
         <v>1000</v>
       </c>
       <c r="J103" t="n">
-        <v>1.03</v>
+        <v>1.73</v>
       </c>
       <c r="K103" t="n">
         <v>1000</v>
@@ -26535,7 +26535,7 @@
         <v>1.04</v>
       </c>
       <c r="N103" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="O103" t="n">
         <v>1.22</v>
@@ -26550,19 +26550,19 @@
         <v>1.18</v>
       </c>
       <c r="S103" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T103" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="U103" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="V103" t="n">
         <v>1.01</v>
       </c>
       <c r="W103" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="X103" t="n">
         <v>1000</v>
@@ -26734,7 +26734,7 @@
       </c>
       <c r="CB103" t="inlineStr">
         <is>
-          <t>2026-07-17 20:53:41</t>
+          <t>2026-07-17 23:15:15</t>
         </is>
       </c>
     </row>
